--- a/DarazNP - QA/Daraz_Nepal_QA_TestPlan.xlsx
+++ b/DarazNP - QA/Daraz_Nepal_QA_TestPlan.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\QA\DarazNP - QA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68332FD1-7F72-4E17-B685-9196705601CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DDE6732A-62F1-43A2-A048-E5821CF26FEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" tabRatio="500" firstSheet="7" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" tabRatio="500" firstSheet="4" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Test Scenario" sheetId="1" r:id="rId1"/>
     <sheet name="Register" sheetId="2" r:id="rId2"/>
     <sheet name="Log In" sheetId="3" r:id="rId3"/>
     <sheet name="Log Out" sheetId="4" r:id="rId4"/>
-    <sheet name="Forgot Password" sheetId="5" r:id="rId5"/>
+    <sheet name="Forgot Password" sheetId="14" r:id="rId5"/>
     <sheet name="Home Page" sheetId="6" r:id="rId6"/>
     <sheet name="Search" sheetId="7" r:id="rId7"/>
     <sheet name="Product Page" sheetId="9" r:id="rId8"/>
@@ -27,16 +27,12 @@
     <sheet name="Summary" sheetId="13" r:id="rId12"/>
   </sheets>
   <calcPr calcId="0" iterateDelta="1E-4"/>
-  <extLst>
-    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
-      <loext:extCalcPr stringRefSyntax="ExcelA1"/>
-    </ext>
-  </extLst>
+  <fileRecoveryPr repairLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="666" uniqueCount="402">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="802" uniqueCount="468">
   <si>
     <t>Project Name</t>
   </si>
@@ -1242,247 +1238,455 @@
     <t>BUG_001</t>
   </si>
   <si>
-    <t>TC 2
-(Log In)</t>
-  </si>
-  <si>
     <t>Log In</t>
   </si>
   <si>
-    <t>Empty search shows all products</t>
-  </si>
-  <si>
-    <t>Searching with empty keyword displays all product listings instead of showing a prompt</t>
+    <t>High</t>
+  </si>
+  <si>
+    <t>Open</t>
+  </si>
+  <si>
+    <t>BUG_002</t>
+  </si>
+  <si>
+    <t>BUG_003</t>
+  </si>
+  <si>
+    <t>BUG_004</t>
+  </si>
+  <si>
+    <t>BUG_005</t>
+  </si>
+  <si>
+    <t>Daraz Nepal QA Project</t>
+  </si>
+  <si>
+    <t>Application Under Test</t>
+  </si>
+  <si>
+    <t>daraz.com.np (Desktop Website)</t>
+  </si>
+  <si>
+    <t>Test Environment</t>
+  </si>
+  <si>
+    <t>Production</t>
+  </si>
+  <si>
+    <t>Tester Name</t>
+  </si>
+  <si>
+    <t>Test Start Date</t>
+  </si>
+  <si>
+    <t>Test End Date</t>
+  </si>
+  <si>
+    <t>Total Test Cases</t>
+  </si>
+  <si>
+    <t>Total Bugs Found</t>
+  </si>
+  <si>
+    <t>Total Executed</t>
+  </si>
+  <si>
+    <t>Critical</t>
+  </si>
+  <si>
+    <t>Pass</t>
+  </si>
+  <si>
+    <t>Fail</t>
+  </si>
+  <si>
+    <t>Medium</t>
+  </si>
+  <si>
+    <t>Blocked</t>
+  </si>
+  <si>
+    <t>Low</t>
+  </si>
+  <si>
+    <t>Not Executed</t>
+  </si>
+  <si>
+    <t>Pass Rate (%)</t>
+  </si>
+  <si>
+    <t>Fixed / Closed</t>
+  </si>
+  <si>
+    <t>Total TCs</t>
+  </si>
+  <si>
+    <t>Pass Rate</t>
+  </si>
+  <si>
+    <t>Register</t>
+  </si>
+  <si>
+    <t>Log Out</t>
+  </si>
+  <si>
+    <t>Forgot Password</t>
+  </si>
+  <si>
+    <t>Home Page</t>
+  </si>
+  <si>
+    <t>Search</t>
+  </si>
+  <si>
+    <t>Product Page</t>
+  </si>
+  <si>
+    <t>Add to Cart</t>
+  </si>
+  <si>
+    <t>Shopping Cart</t>
+  </si>
+  <si>
+    <t>Daraz Nepal (daraz.com.np)</t>
+  </si>
+  <si>
+    <t>Sabhyata Aryal</t>
+  </si>
+  <si>
+    <t>TS 001 
+ (Register)</t>
+  </si>
+  <si>
+    <t>TS 003
+(Logout Functionality)</t>
+  </si>
+  <si>
+    <t>TS 002  
+(Login Functionality)</t>
+  </si>
+  <si>
+    <t>TS 004  
+(Forgot Password)</t>
+  </si>
+  <si>
+    <t>TS 006  
+(Search Functionality)</t>
+  </si>
+  <si>
+    <t>TS 005  
+(Home Page)</t>
+  </si>
+  <si>
+    <t>Enter missing field' or 'Password is required' message is displayed</t>
+  </si>
+  <si>
+    <t>TS 002
+(Login Functionality)</t>
+  </si>
+  <si>
+    <t>TS 006
+(Search Functionality)</t>
+  </si>
+  <si>
+    <t>TS 007  
+(Product Display)</t>
+  </si>
+  <si>
+    <t>TS 008  
+(Add to Cart)</t>
+  </si>
+  <si>
+    <t>TS 009  
+(Shopping Cart)</t>
+  </si>
+  <si>
+    <t>TS 007
+(Product Display)</t>
+  </si>
+  <si>
+    <t>TS 008
+(Add to Cart)</t>
+  </si>
+  <si>
+    <t>TS 009
+(Shopping Cart)</t>
+  </si>
+  <si>
+    <t>Your cart is empty' message shown with link to continue shopping</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> PROJECT INFORMATION</t>
+  </si>
+  <si>
+    <t>EXECUTION METRICS</t>
+  </si>
+  <si>
+    <t>MODULE COVERAGE</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> BUG SUMMARY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DARAZ NEPAL QA — TEST SUMMARY </t>
+  </si>
+  <si>
+    <t>TC 3 (Search)</t>
+  </si>
+  <si>
+    <t>Special characters search causes no-results but no user-friendly message</t>
+  </si>
+  <si>
+    <t>Entering special characters (@#$%^&amp;) in the search bar returns an empty results page without a clear user-facing "No results found" message in all scenarios.</t>
   </si>
   <si>
     <t>1. Open daraz.com.np
 2. Click search bar
-3. Press Enter without typing</t>
-  </si>
-  <si>
-    <t>No products or prompt to enter a keyword</t>
-  </si>
-  <si>
-    <t>All products displayed</t>
-  </si>
-  <si>
-    <t>High</t>
-  </si>
-  <si>
-    <t>Open</t>
-  </si>
-  <si>
-    <t>Add screenshot here</t>
-  </si>
-  <si>
-    <t>BUG_002</t>
-  </si>
-  <si>
-    <t>BUG_003</t>
-  </si>
-  <si>
-    <t>BUG_004</t>
-  </si>
-  <si>
-    <t>BUG_005</t>
-  </si>
-  <si>
-    <t>BUG_006</t>
-  </si>
-  <si>
-    <t>BUG_007</t>
-  </si>
-  <si>
-    <t>BUG_008</t>
-  </si>
-  <si>
-    <t>DARAZ NEPAL QA — TEST SUMMARY DASHBOARD</t>
-  </si>
-  <si>
-    <t>Daraz Nepal QA Project</t>
-  </si>
-  <si>
-    <t>Application Under Test</t>
-  </si>
-  <si>
-    <t>daraz.com.np (Desktop Website)</t>
-  </si>
-  <si>
-    <t>Test Environment</t>
-  </si>
-  <si>
-    <t>Production</t>
-  </si>
-  <si>
-    <t>Browser &amp; Version</t>
-  </si>
-  <si>
-    <t>Google Chrome (latest)</t>
-  </si>
-  <si>
-    <t>Tester Name</t>
-  </si>
-  <si>
-    <t>Test Start Date</t>
-  </si>
-  <si>
-    <t>Test End Date</t>
-  </si>
-  <si>
-    <t>🐛 BUG SUMMARY</t>
-  </si>
-  <si>
-    <t>Total Test Cases</t>
-  </si>
-  <si>
-    <t>Total Bugs Found</t>
-  </si>
-  <si>
-    <t>Total Executed</t>
-  </si>
-  <si>
-    <t>Critical</t>
-  </si>
-  <si>
-    <t>Pass</t>
-  </si>
-  <si>
-    <t>Fail</t>
-  </si>
-  <si>
-    <t>Medium</t>
-  </si>
-  <si>
-    <t>Blocked</t>
-  </si>
-  <si>
-    <t>Low</t>
-  </si>
-  <si>
-    <t>Not Executed</t>
-  </si>
-  <si>
-    <t>Pass Rate (%)</t>
-  </si>
-  <si>
-    <t>Fixed / Closed</t>
-  </si>
-  <si>
-    <t>Total TCs</t>
-  </si>
-  <si>
-    <t>Pass Rate</t>
-  </si>
-  <si>
-    <t>Register</t>
-  </si>
-  <si>
-    <t>Log Out</t>
-  </si>
-  <si>
-    <t>Forgot Password</t>
-  </si>
-  <si>
-    <t>Home Page</t>
-  </si>
-  <si>
-    <t>Search</t>
-  </si>
-  <si>
-    <t>Search &amp; Filter</t>
-  </si>
-  <si>
-    <t>Product Page</t>
-  </si>
-  <si>
-    <t>Add to Cart</t>
-  </si>
-  <si>
-    <t>Shopping Cart</t>
-  </si>
-  <si>
-    <t>Daraz Nepal (daraz.com.np)</t>
-  </si>
-  <si>
-    <t>Sabhyata Aryal</t>
-  </si>
-  <si>
-    <t>TS 001 
- (Register)</t>
-  </si>
-  <si>
-    <t>TS 003
-(Logout Functionality)</t>
-  </si>
-  <si>
-    <t>TS 002  
-(Login Functionality)</t>
-  </si>
-  <si>
-    <t>TS 004  
-(Forgot Password)</t>
-  </si>
-  <si>
-    <t>TS 006  
-(Search Functionality)</t>
-  </si>
-  <si>
-    <t>TS 005  
-(Home Page)</t>
-  </si>
-  <si>
-    <t>Enter missing field' or 'Password is required' message is displayed</t>
-  </si>
-  <si>
-    <t>TS 002
-(Login Functionality)</t>
-  </si>
-  <si>
-    <t>TS 006
-(Search Functionality)</t>
-  </si>
-  <si>
-    <t>TS 007  
-(Product Display)</t>
-  </si>
-  <si>
-    <t>TS 008  
-(Add to Cart)</t>
-  </si>
-  <si>
-    <t>TS 009  
-(Shopping Cart)</t>
-  </si>
-  <si>
-    <t>TS 007
-(Product Display)</t>
-  </si>
-  <si>
-    <t>TS 008
-(Add to Cart)</t>
-  </si>
-  <si>
-    <t>TS 009
-(Shopping Cart)</t>
-  </si>
-  <si>
-    <t>Your cart is empty' message shown with link to continue shopping</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> PROJECT INFORMATION</t>
-  </si>
-  <si>
-    <t>EXECUTION METRICS</t>
-  </si>
-  <si>
-    <t>MODULE COVERAGE</t>
+3. Type "@#$%^&amp;"
+4. Press Enter</t>
+  </si>
+  <si>
+    <t>"No results found" message displayed gracefully</t>
+  </si>
+  <si>
+    <t>TC 4 (Search)</t>
+  </si>
+  <si>
+    <t>Search bar accepts 300+ character input without truncation notice</t>
+  </si>
+  <si>
+    <t>The search input field accepts strings exceeding 300 characters without providing the user any truncation notification or character limit warning.</t>
+  </si>
+  <si>
+    <t>1. Open daraz.com.np
+2. Paste a 300+ character string into the search bar
+3. Press Enter</t>
+  </si>
+  <si>
+    <t>Input truncated or user notified of character limit</t>
+  </si>
+  <si>
+    <t>Input accepted silently; no truncation notice shown</t>
+  </si>
+  <si>
+    <t>TC 4 (Add to Cart)</t>
+  </si>
+  <si>
+    <t>Guest users not shown clear message when adding to cart without login</t>
+  </si>
+  <si>
+    <t>When a non-logged-in user clicks "Add to Cart", the login modal appears but does not clearly state that login is required to add items to the cart.</t>
+  </si>
+  <si>
+    <t>1. Open daraz.com.np without logging in
+2. Open any product page
+3. Click "Add to Cart"</t>
+  </si>
+  <si>
+    <t>Clear message: "Please log in to add items to your cart"</t>
+  </si>
+  <si>
+    <t>Generic login modal appears without cart-specific context message</t>
+  </si>
+  <si>
+    <t>TC 2 (Register)</t>
+  </si>
+  <si>
+    <t>Duplicate email registration error message not specific enough</t>
+  </si>
+  <si>
+    <t>When registering with an already-registered email, the error message shown is generic and does not guide the user to login or use "Forgot Password".</t>
+  </si>
+  <si>
+    <t>TC 2 (Log Out)</t>
+  </si>
+  <si>
+    <t>Browser back button after logout may briefly show cached protected page</t>
+  </si>
+  <si>
+    <t>After logout, pressing the browser back button briefly shows a cached version of the account/orders page before redirecting to the login page.</t>
+  </si>
+  <si>
+    <t>1. Login to daraz.com.np
+2. Navigate to My Orders page
+3. Click Logout
+4. Press browser Back button</t>
+  </si>
+  <si>
+    <t>Immediately redirected to login page; no protected content shown</t>
+  </si>
+  <si>
+    <t>Cached account page briefly visible before redirect to login</t>
+  </si>
+  <si>
+    <t>Random products are shown</t>
+  </si>
+  <si>
+    <t>1. Navigate to daraz.com.np
+2. Click Sign Up
+3. Enter an already-registered email/phone number
+4. Click Create Account</t>
+  </si>
+  <si>
+    <t>Error: "This email/phone number is already registered. Try logging in or reset your password."</t>
+  </si>
+  <si>
+    <t>"Please enter a valid phone number" shown without further guidance</t>
+  </si>
+  <si>
+    <t>All added items displayed in cart with correct name, image, price and quantity.</t>
+  </si>
+  <si>
+    <t>Quantity updates to 3 via the + button. Subtotal recalculates correctly.</t>
+  </si>
+  <si>
+    <t>Item is removed from cart. Total price recalculates correctly. Remaining items are intact.</t>
+  </si>
+  <si>
+    <t>'Your cart is empty' message is displayed with a 'Continue Shopping' link.</t>
+  </si>
+  <si>
+    <t>Subtotal shows NPR 1,300. Calculation is correct (500×2 + 300×1 = 1300).</t>
+  </si>
+  <si>
+    <t>Cart items are retained after page refresh. All quantities and products remain unchanged.</t>
+  </si>
+  <si>
+    <t>Item added to cart. Cart icon count increases by 1. Confirmation toast message is shown.</t>
+  </si>
+  <si>
+    <t>Both products appear in cart with correct names, quantities and prices.</t>
+  </si>
+  <si>
+    <t>Quantity increases to 2 in the cart. No duplicate error shown.</t>
+  </si>
+  <si>
+    <t>Login prompt appears asking user to sign in before adding to cart. Guest cart is not supported.</t>
+  </si>
+  <si>
+    <t>Warning 'Please select a size/color' is displayed. Item is not added to cart until variant is selected.</t>
+  </si>
+  <si>
+    <t>Product images load correctly. Clicking thumbnail images changes the main product image as expected.</t>
+  </si>
+  <si>
+    <t>Original price, discounted price and percentage off badge are all displayed correctly on the product page.</t>
+  </si>
+  <si>
+    <t>Item added to cart. Cart icon count updates correctly. Success toast confirmation is shown.</t>
+  </si>
+  <si>
+    <t>'Add to Cart' button is disabled/greyed out and 'Out of Stock' label is clearly displayed.</t>
+  </si>
+  <si>
+    <t>Customer reviews section displays star ratings, reviewer names, dates and comment text correctly.</t>
+  </si>
+  <si>
+    <t>Seller name, store rating and link to store page are visible and functional.</t>
+  </si>
+  <si>
+    <t>Product specifications are displayed in a structured, organized format with correct information.</t>
+  </si>
+  <si>
+    <t>Search results page loads with products relevant to 'laptop'. Multiple listings with prices and ratings shown.</t>
+  </si>
+  <si>
+    <t>All products are displayed instead of showing a 'Please enter a keyword' prompt. No crash occurs.</t>
+  </si>
+  <si>
+    <t>'No results found' message is displayed. Application does not crash.</t>
+  </si>
+  <si>
+    <t>Input is accepted and results page loads without crash. Query is truncated gracefully.</t>
+  </si>
+  <si>
+    <t>Autocomplete dropdown suggestions appear below the search bar as user types. Suggestions are relevant.</t>
+  </si>
+  <si>
+    <t>Homepage loads within 3 seconds. Logo, banner, navbar and all main sections are fully visible.</t>
+  </si>
+  <si>
+    <t>Dropdown appears on hover over navigation items. Clicking each category link navigates to the correct category page.</t>
+  </si>
+  <si>
+    <t>Banner auto-slides every ~4 seconds. Left/right arrow navigation works correctly for manual control.</t>
+  </si>
+  <si>
+    <t>Product cards display image, name and price correctly. Clicking a card opens the correct product detail page.</t>
+  </si>
+  <si>
+    <t>All footer links (About Us, Contact, Help, etc.) navigate to the correct pages. No 404 errors observed.</t>
+  </si>
+  <si>
+    <t>Password reset email is sent. Confirmation message 'A reset link has been sent to your email' is displayed.</t>
+  </si>
+  <si>
+    <t>Error message 'This email address is not associated with any account' is displayed. No email is sent.</t>
+  </si>
+  <si>
+    <t>Validation error 'Please enter your email address' is displayed. Form is not submitted.</t>
+  </si>
+  <si>
+    <t>Password is changed successfully. Login with the new password works correctly.</t>
+  </si>
+  <si>
+    <t>User is logged out successfully. Session is terminated and 'Sign In' button is visible on homepage.</t>
+  </si>
+  <si>
+    <t>Cart items are retained after logout and re-login. Items appear correctly in cart upon logging back in.</t>
+  </si>
+  <si>
+    <t>User is redirected to the login page when trying to access protected account pages after logout. Back button does not restore session.</t>
+  </si>
+  <si>
+    <t>User is successfully logged in and redirected to homepage. 'Welcome' message is displayed.</t>
+  </si>
+  <si>
+    <t>'Incorrect email or password' error message displayed. User remains on login page.</t>
+  </si>
+  <si>
+    <t>Validation error 'Please enter your email/phone number' is displayed. Login not attempted.</t>
+  </si>
+  <si>
+    <t>Validation error 'Please enter your password' is displayed. Login not attempted.</t>
+  </si>
+  <si>
+    <t>Validation errors displayed for both empty fields: 'Please enter your email' and 'Please enter your password'.</t>
+  </si>
+  <si>
+    <t>Account is created successfully. User is redirected to homepage and receives a confirmation email.</t>
+  </si>
+  <si>
+    <t>Error message 'This email address is already registered' is displayed. User remains on registration page.</t>
+  </si>
+  <si>
+    <t>Validation error 'Please enter a valid email address' is displayed inline below the email field.</t>
+  </si>
+  <si>
+    <t>Password strength indicator shows 'Too weak'. Error message prompts minimum password requirements.</t>
+  </si>
+  <si>
+    <t>Validation errors displayed for all required empty fields. Form is not submitted.</t>
+  </si>
+  <si>
+    <t>'Password is required' error message is displayed. User remains on registration page.</t>
+  </si>
+  <si>
+    <t>Brave</t>
+  </si>
+  <si>
+    <t>Browser</t>
+  </si>
+  <si>
+    <t>S</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1517,8 +1721,22 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
   </fonts>
-  <fills count="15">
+  <fills count="16">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1603,28 +1821,19 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor theme="4"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="5">
+  <borders count="6">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFBFBFBF"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFBFBFBF"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFBFBFBF"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFBFBFBF"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -1666,46 +1875,46 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="3" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1713,18 +1922,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1738,184 +1935,78 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="146">
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+  <dxfs count="164">
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <font>
@@ -1928,181 +2019,144 @@
       </fill>
     </dxf>
     <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -2172,25 +2226,707 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color theme="4"/>
+        </left>
+        <right style="thin">
+          <color theme="4"/>
+        </right>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4"/>
+          <bgColor theme="4"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -2273,231 +3009,463 @@
 </styleSheet>
 </file>
 
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>116973</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>61913</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>1596073</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>718354</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="Picture 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D6685349-AF00-8CFD-1C2A-5E1E06AC574E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="17833473" y="1509713"/>
+          <a:ext cx="1479100" cy="656441"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>290512</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>66677</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>1495425</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>653357</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="7" name="Picture 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CBDC2E56-96DC-B089-5D99-8976B394C901}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="18007012" y="2238377"/>
+          <a:ext cx="1204913" cy="586680"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>371475</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>76201</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>1295401</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>682876</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="8" name="Picture 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C1396355-E0ED-86BD-F8E9-3C3565C41E70}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="18087975" y="2428876"/>
+          <a:ext cx="923926" cy="606675"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>195262</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>112121</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>1626111</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>571500</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="9" name="Picture 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B565CD08-7DB3-6D37-AECF-DB07172D1897}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill rotWithShape="1">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:srcRect l="36455" t="-2685" b="-1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="17911762" y="3188696"/>
+          <a:ext cx="1430849" cy="459379"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>247650</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>41564</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>1462088</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>688930</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="12" name="Picture 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3340D06D-4953-96BB-2B2B-DF5AD0C4390B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="17964150" y="222539"/>
+          <a:ext cx="1214438" cy="647366"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{DF488C28-E294-4FC5-B88E-45C03C2670F4}" name="Table1" displayName="Table1" ref="A6:D15" totalsRowShown="0" headerRowDxfId="108" dataDxfId="107" headerRowCellStyle="Normal" dataCellStyle="Normal">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{DF488C28-E294-4FC5-B88E-45C03C2670F4}" name="Table1" displayName="Table1" ref="A6:D15" totalsRowShown="0" headerRowDxfId="150" dataDxfId="149" headerRowCellStyle="Normal" dataCellStyle="Normal">
   <autoFilter ref="A6:D15" xr:uid="{DF488C28-E294-4FC5-B88E-45C03C2670F4}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{33DAD9C3-616B-4530-8A09-EA2123236523}" name="Test Scenario ID" dataDxfId="112" dataCellStyle="Normal"/>
-    <tableColumn id="2" xr3:uid="{930616D5-B050-48B4-BC07-2F47085FC38F}" name="Test Scenario Description" dataDxfId="111" dataCellStyle="Normal"/>
-    <tableColumn id="3" xr3:uid="{81B53550-0158-483A-8072-7528B8991C66}" name="Priority" dataDxfId="110" dataCellStyle="Normal"/>
-    <tableColumn id="4" xr3:uid="{4E0C06DA-320E-4E35-ABDA-665C29E66893}" name="Number of Test Cases" dataDxfId="109" dataCellStyle="Normal"/>
+    <tableColumn id="1" xr3:uid="{33DAD9C3-616B-4530-8A09-EA2123236523}" name="Test Scenario ID" dataDxfId="148" dataCellStyle="Normal"/>
+    <tableColumn id="2" xr3:uid="{930616D5-B050-48B4-BC07-2F47085FC38F}" name="Test Scenario Description" dataDxfId="147" dataCellStyle="Normal"/>
+    <tableColumn id="3" xr3:uid="{81B53550-0158-483A-8072-7528B8991C66}" name="Priority" dataDxfId="146" dataCellStyle="Normal"/>
+    <tableColumn id="4" xr3:uid="{4E0C06DA-320E-4E35-ABDA-665C29E66893}" name="Number of Test Cases" dataDxfId="145" dataCellStyle="Normal"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{7325E5B5-E902-49F8-AEF5-E792747C2CB9}" name="Table10" displayName="Table10" ref="A1:K7" totalsRowShown="0" headerRowDxfId="140" dataDxfId="9">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{7325E5B5-E902-49F8-AEF5-E792747C2CB9}" name="Table10" displayName="Table10" ref="A1:K7" totalsRowShown="0" headerRowDxfId="53" dataDxfId="52">
   <autoFilter ref="A1:K7" xr:uid="{7325E5B5-E902-49F8-AEF5-E792747C2CB9}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{3E6BAD88-77A0-44B6-9F2B-5FBB3CE091F2}" name="Test Case ID" dataDxfId="20"/>
-    <tableColumn id="2" xr3:uid="{B6334C76-74C3-494E-9AD8-250558808943}" name="Test Scenario" dataDxfId="19"/>
-    <tableColumn id="3" xr3:uid="{C0ABB8E4-BF9C-4E33-B022-CF3A4DE60B64}" name="Test Case Title" dataDxfId="18"/>
-    <tableColumn id="4" xr3:uid="{9B154E74-7F46-4204-9D85-09FD7A515891}" name="Test Description" dataDxfId="17"/>
-    <tableColumn id="5" xr3:uid="{F1A47D99-EDEF-4DEF-9E20-A7FD7E80C2FF}" name="Precondition" dataDxfId="16"/>
-    <tableColumn id="6" xr3:uid="{B6883181-BD4B-46FB-AA46-5EAB92EFDD14}" name="Test Data" dataDxfId="15"/>
-    <tableColumn id="7" xr3:uid="{CDC1D1E1-7F31-4F2F-A9D6-B5BB49DB18D2}" name="Test Step" dataDxfId="14"/>
-    <tableColumn id="8" xr3:uid="{4EC38E01-73BC-4A40-A90C-FBC00297BCCB}" name="Post Condition" dataDxfId="13"/>
-    <tableColumn id="9" xr3:uid="{8B71CA62-1B8D-4F3C-8F1C-80F149DDCD86}" name="Expected Result" dataDxfId="12"/>
-    <tableColumn id="10" xr3:uid="{2758D08A-14A0-421E-93F0-A1D3EED326FD}" name="Actual Result" dataDxfId="11"/>
-    <tableColumn id="11" xr3:uid="{D4909B32-B834-474B-8873-CE83A7F95DED}" name="Status" dataDxfId="10"/>
+    <tableColumn id="1" xr3:uid="{3E6BAD88-77A0-44B6-9F2B-5FBB3CE091F2}" name="Test Case ID" dataDxfId="51"/>
+    <tableColumn id="2" xr3:uid="{B6334C76-74C3-494E-9AD8-250558808943}" name="Test Scenario" dataDxfId="50"/>
+    <tableColumn id="3" xr3:uid="{C0ABB8E4-BF9C-4E33-B022-CF3A4DE60B64}" name="Test Case Title" dataDxfId="49"/>
+    <tableColumn id="4" xr3:uid="{9B154E74-7F46-4204-9D85-09FD7A515891}" name="Test Description" dataDxfId="48"/>
+    <tableColumn id="5" xr3:uid="{F1A47D99-EDEF-4DEF-9E20-A7FD7E80C2FF}" name="Precondition" dataDxfId="47"/>
+    <tableColumn id="6" xr3:uid="{B6883181-BD4B-46FB-AA46-5EAB92EFDD14}" name="Test Data" dataDxfId="46"/>
+    <tableColumn id="7" xr3:uid="{CDC1D1E1-7F31-4F2F-A9D6-B5BB49DB18D2}" name="Test Step" dataDxfId="45"/>
+    <tableColumn id="8" xr3:uid="{4EC38E01-73BC-4A40-A90C-FBC00297BCCB}" name="Post Condition" dataDxfId="44"/>
+    <tableColumn id="9" xr3:uid="{8B71CA62-1B8D-4F3C-8F1C-80F149DDCD86}" name="Expected Result" dataDxfId="43"/>
+    <tableColumn id="10" xr3:uid="{2758D08A-14A0-421E-93F0-A1D3EED326FD}" name="Actual Result" dataDxfId="42"/>
+    <tableColumn id="11" xr3:uid="{D4909B32-B834-474B-8873-CE83A7F95DED}" name="Status" dataDxfId="41"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{074B61AA-834B-4987-8591-EFE949C0CD3E}" name="Table11" displayName="Table11" ref="A1:L9" totalsRowShown="0" headerRowDxfId="139" dataDxfId="126">
-  <autoFilter ref="A1:L9" xr:uid="{074B61AA-834B-4987-8591-EFE949C0CD3E}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{074B61AA-834B-4987-8591-EFE949C0CD3E}" name="Table11" displayName="Table11" ref="A1:L6" totalsRowShown="0" headerRowDxfId="40" dataDxfId="39">
+  <autoFilter ref="A1:L6" xr:uid="{074B61AA-834B-4987-8591-EFE949C0CD3E}"/>
   <tableColumns count="12">
-    <tableColumn id="1" xr3:uid="{2E0BA05E-6B29-48D5-8C89-726D7682792E}" name="Bug_ID" dataDxfId="138"/>
-    <tableColumn id="2" xr3:uid="{4D01CBE5-0889-4880-92D7-4B66BC182ECB}" name="TC_ID" dataDxfId="137"/>
-    <tableColumn id="3" xr3:uid="{982AC477-4942-498F-B937-BBBFAD3FE9B0}" name="Module" dataDxfId="136"/>
-    <tableColumn id="4" xr3:uid="{45C656C2-F54B-4624-BEE7-F4B8A9A3F7AA}" name="Bug Title" dataDxfId="135"/>
-    <tableColumn id="5" xr3:uid="{5A4A270F-8EE2-456D-8096-C57A552FA8BD}" name="Description" dataDxfId="134"/>
-    <tableColumn id="6" xr3:uid="{5211538C-C43F-4AE0-A40C-4517593D85B8}" name="Steps to Reproduce" dataDxfId="133"/>
-    <tableColumn id="7" xr3:uid="{0D61D290-BC8B-4DAB-B115-362A2EC84928}" name="Expected Result" dataDxfId="132"/>
-    <tableColumn id="8" xr3:uid="{7C9A10CE-DFC8-4284-B52F-67B1076DE1F2}" name="Actual Result" dataDxfId="131"/>
-    <tableColumn id="9" xr3:uid="{A2A09C9A-0EC4-4EEB-8207-4D4AD9E6C2FE}" name="Severity" dataDxfId="130"/>
-    <tableColumn id="10" xr3:uid="{812B3DBC-B5F8-4461-8B42-A270EC894AB1}" name="Priority" dataDxfId="129"/>
-    <tableColumn id="11" xr3:uid="{84506A51-F862-4873-B24D-6E470DF7E85E}" name="Status" dataDxfId="128"/>
-    <tableColumn id="12" xr3:uid="{98CA703C-ECC2-42FB-AB7E-B2461D8721F0}" name="Screenshot/Notes" dataDxfId="127"/>
+    <tableColumn id="1" xr3:uid="{2E0BA05E-6B29-48D5-8C89-726D7682792E}" name="Bug_ID" dataDxfId="38"/>
+    <tableColumn id="2" xr3:uid="{4D01CBE5-0889-4880-92D7-4B66BC182ECB}" name="TC_ID" dataDxfId="37"/>
+    <tableColumn id="3" xr3:uid="{982AC477-4942-498F-B937-BBBFAD3FE9B0}" name="Module" dataDxfId="36"/>
+    <tableColumn id="4" xr3:uid="{45C656C2-F54B-4624-BEE7-F4B8A9A3F7AA}" name="Bug Title" dataDxfId="35"/>
+    <tableColumn id="5" xr3:uid="{5A4A270F-8EE2-456D-8096-C57A552FA8BD}" name="Description" dataDxfId="34"/>
+    <tableColumn id="6" xr3:uid="{5211538C-C43F-4AE0-A40C-4517593D85B8}" name="Steps to Reproduce" dataDxfId="33"/>
+    <tableColumn id="7" xr3:uid="{0D61D290-BC8B-4DAB-B115-362A2EC84928}" name="Expected Result" dataDxfId="32"/>
+    <tableColumn id="8" xr3:uid="{7C9A10CE-DFC8-4284-B52F-67B1076DE1F2}" name="Actual Result" dataDxfId="31"/>
+    <tableColumn id="9" xr3:uid="{A2A09C9A-0EC4-4EEB-8207-4D4AD9E6C2FE}" name="Severity" dataDxfId="30"/>
+    <tableColumn id="10" xr3:uid="{812B3DBC-B5F8-4461-8B42-A270EC894AB1}" name="Priority" dataDxfId="29"/>
+    <tableColumn id="11" xr3:uid="{84506A51-F862-4873-B24D-6E470DF7E85E}" name="Status" dataDxfId="28"/>
+    <tableColumn id="12" xr3:uid="{98CA703C-ECC2-42FB-AB7E-B2461D8721F0}" name="Screenshot/Notes" dataDxfId="27"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{B5F3787F-2FE5-47F0-A53F-BE14C9EDF880}" name="Table12" displayName="Table12" ref="A22:G32" totalsRowShown="0" headerRowDxfId="1" dataDxfId="0" tableBorderDxfId="125">
-  <autoFilter ref="A22:G32" xr:uid="{B5F3787F-2FE5-47F0-A53F-BE14C9EDF880}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{B5F3787F-2FE5-47F0-A53F-BE14C9EDF880}" name="Table12" displayName="Table12" ref="A22:G31" totalsRowShown="0" headerRowDxfId="26" dataDxfId="25" tableBorderDxfId="24">
+  <autoFilter ref="A22:G31" xr:uid="{B5F3787F-2FE5-47F0-A53F-BE14C9EDF880}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{9F53F743-51DF-481F-9F33-6444B7379A49}" name="Module" dataDxfId="8"/>
-    <tableColumn id="2" xr3:uid="{8809AAEF-A8F9-436C-8EB8-D71DC356BE56}" name="Total TCs" dataDxfId="7"/>
-    <tableColumn id="3" xr3:uid="{938B6847-EE17-4CDD-B2A0-CF0886EE64B8}" name="Pass" dataDxfId="6"/>
-    <tableColumn id="4" xr3:uid="{4F4A2014-C80D-4909-AADC-157B9CB87F8F}" name="Fail" dataDxfId="5"/>
-    <tableColumn id="5" xr3:uid="{BE788EF4-5FDE-4EB6-B750-431A6DA3708D}" name="Blocked" dataDxfId="4"/>
-    <tableColumn id="6" xr3:uid="{56E5F7D1-FE02-40AD-8B69-C21E5C9D2099}" name="Not Executed" dataDxfId="3"/>
-    <tableColumn id="7" xr3:uid="{0EEA2BFA-1D98-4AB4-9C6E-502E972DD0F6}" name="Pass Rate" dataDxfId="2"/>
+    <tableColumn id="1" xr3:uid="{9F53F743-51DF-481F-9F33-6444B7379A49}" name="Module" dataDxfId="23"/>
+    <tableColumn id="2" xr3:uid="{8809AAEF-A8F9-436C-8EB8-D71DC356BE56}" name="Total TCs" dataDxfId="22"/>
+    <tableColumn id="3" xr3:uid="{938B6847-EE17-4CDD-B2A0-CF0886EE64B8}" name="Pass" dataDxfId="21"/>
+    <tableColumn id="4" xr3:uid="{4F4A2014-C80D-4909-AADC-157B9CB87F8F}" name="Fail" dataDxfId="20"/>
+    <tableColumn id="5" xr3:uid="{BE788EF4-5FDE-4EB6-B750-431A6DA3708D}" name="Blocked" dataDxfId="19"/>
+    <tableColumn id="6" xr3:uid="{56E5F7D1-FE02-40AD-8B69-C21E5C9D2099}" name="Not Executed" dataDxfId="18"/>
+    <tableColumn id="7" xr3:uid="{0EEA2BFA-1D98-4AB4-9C6E-502E972DD0F6}" name="Pass Rate" dataDxfId="17"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{4D72BE03-3C67-483F-A000-0CB99AE08007}" name="Table2" displayName="Table2" ref="A1:K7" totalsRowShown="0" headerRowDxfId="145" dataDxfId="95">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{4D72BE03-3C67-483F-A000-0CB99AE08007}" name="Table2" displayName="Table2" ref="A1:K7" totalsRowShown="0" headerRowDxfId="144" dataDxfId="143">
   <autoFilter ref="A1:K7" xr:uid="{4D72BE03-3C67-483F-A000-0CB99AE08007}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{DC300589-A232-46E8-8D34-43EA76119908}" name="Test Case ID" dataDxfId="106"/>
-    <tableColumn id="2" xr3:uid="{96321DA6-69B9-4285-96FB-F624E3C3A963}" name="Test Scenario" dataDxfId="105"/>
-    <tableColumn id="3" xr3:uid="{47B1BA56-1BCF-45B6-B32B-B5379B2C21C2}" name="Test Case Title" dataDxfId="104"/>
-    <tableColumn id="4" xr3:uid="{C36FE4A9-C732-4047-A84B-CBFDF06E1798}" name="Test Description" dataDxfId="103"/>
-    <tableColumn id="5" xr3:uid="{D1518DD6-352E-4530-B986-D864E93A5AC8}" name="Precondition" dataDxfId="102"/>
-    <tableColumn id="6" xr3:uid="{8B4D31E2-8543-4172-9800-778AC567D164}" name="Test Data" dataDxfId="101"/>
-    <tableColumn id="7" xr3:uid="{CDA134EC-16A7-4594-9E02-221402834F08}" name="Test Step" dataDxfId="100"/>
-    <tableColumn id="8" xr3:uid="{1B527B44-6496-4F0D-A56D-4413FF4DDDA2}" name="Post Condition" dataDxfId="99"/>
-    <tableColumn id="9" xr3:uid="{B9389CBA-79E5-4A58-9516-26D20F6CBA6E}" name="Expected Result" dataDxfId="98"/>
-    <tableColumn id="10" xr3:uid="{52125505-5EBF-4612-93D2-682D2A1590E0}" name="Actual Result" dataDxfId="97"/>
-    <tableColumn id="11" xr3:uid="{169FE3A8-8576-4034-B520-E3C132891BF5}" name="Status" dataDxfId="96"/>
+    <tableColumn id="1" xr3:uid="{DC300589-A232-46E8-8D34-43EA76119908}" name="Test Case ID" dataDxfId="142"/>
+    <tableColumn id="2" xr3:uid="{96321DA6-69B9-4285-96FB-F624E3C3A963}" name="Test Scenario" dataDxfId="141"/>
+    <tableColumn id="3" xr3:uid="{47B1BA56-1BCF-45B6-B32B-B5379B2C21C2}" name="Test Case Title" dataDxfId="140"/>
+    <tableColumn id="4" xr3:uid="{C36FE4A9-C732-4047-A84B-CBFDF06E1798}" name="Test Description" dataDxfId="139"/>
+    <tableColumn id="5" xr3:uid="{D1518DD6-352E-4530-B986-D864E93A5AC8}" name="Precondition" dataDxfId="138"/>
+    <tableColumn id="6" xr3:uid="{8B4D31E2-8543-4172-9800-778AC567D164}" name="Test Data" dataDxfId="137"/>
+    <tableColumn id="7" xr3:uid="{CDA134EC-16A7-4594-9E02-221402834F08}" name="Test Step" dataDxfId="136"/>
+    <tableColumn id="8" xr3:uid="{1B527B44-6496-4F0D-A56D-4413FF4DDDA2}" name="Post Condition" dataDxfId="135"/>
+    <tableColumn id="9" xr3:uid="{B9389CBA-79E5-4A58-9516-26D20F6CBA6E}" name="Expected Result" dataDxfId="134"/>
+    <tableColumn id="10" xr3:uid="{52125505-5EBF-4612-93D2-682D2A1590E0}" name="Actual Result" dataDxfId="133"/>
+    <tableColumn id="11" xr3:uid="{169FE3A8-8576-4034-B520-E3C132891BF5}" name="Status" dataDxfId="132"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{485A2C55-6434-4192-8808-9E3314484566}" name="Table3" displayName="Table3" ref="A1:K10" totalsRowShown="0" headerRowDxfId="144" dataDxfId="83">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{485A2C55-6434-4192-8808-9E3314484566}" name="Table3" displayName="Table3" ref="A1:K10" totalsRowShown="0" headerRowDxfId="131" dataDxfId="130">
   <autoFilter ref="A1:K10" xr:uid="{485A2C55-6434-4192-8808-9E3314484566}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{961A2C21-4B0E-4E55-850D-8F76158E605A}" name="Test Case ID" dataDxfId="94"/>
-    <tableColumn id="2" xr3:uid="{091711FE-D3C8-4930-B519-8CC8A3B55476}" name="Test Scenario" dataDxfId="93"/>
-    <tableColumn id="3" xr3:uid="{88BABBCB-4F52-4C8E-B0AF-A7B1FEA920E1}" name="Test Case Title" dataDxfId="92"/>
-    <tableColumn id="4" xr3:uid="{89C7C9C1-F533-4481-A1AA-3D2ACF79367C}" name="Test Description" dataDxfId="91"/>
-    <tableColumn id="5" xr3:uid="{7E9B2060-966D-4E6E-87D8-0A35654D3D31}" name="Precondition" dataDxfId="90"/>
-    <tableColumn id="6" xr3:uid="{8212B4F5-4682-42D4-98D2-666EB7851034}" name="Test Data" dataDxfId="89"/>
-    <tableColumn id="7" xr3:uid="{C27ADF5D-D13B-4776-B1DB-99BAC727A1EF}" name="Test Step" dataDxfId="88"/>
-    <tableColumn id="8" xr3:uid="{87D91BD6-44DB-42EC-A509-CF909B0841C6}" name="Post Condition" dataDxfId="87"/>
-    <tableColumn id="9" xr3:uid="{CF0F8DF7-50EC-4BF7-9A2B-B588E2C6AD3C}" name="Expected Result" dataDxfId="86"/>
-    <tableColumn id="10" xr3:uid="{28E800BE-C6F2-40A9-92FE-FB97DA376781}" name="Actual Result" dataDxfId="85"/>
-    <tableColumn id="11" xr3:uid="{A019A1D5-1AC2-4238-9C78-8D26EEBABBDD}" name="Status" dataDxfId="84"/>
+    <tableColumn id="1" xr3:uid="{961A2C21-4B0E-4E55-850D-8F76158E605A}" name="Test Case ID" dataDxfId="129"/>
+    <tableColumn id="2" xr3:uid="{091711FE-D3C8-4930-B519-8CC8A3B55476}" name="Test Scenario" dataDxfId="128"/>
+    <tableColumn id="3" xr3:uid="{88BABBCB-4F52-4C8E-B0AF-A7B1FEA920E1}" name="Test Case Title" dataDxfId="127"/>
+    <tableColumn id="4" xr3:uid="{89C7C9C1-F533-4481-A1AA-3D2ACF79367C}" name="Test Description" dataDxfId="126"/>
+    <tableColumn id="5" xr3:uid="{7E9B2060-966D-4E6E-87D8-0A35654D3D31}" name="Precondition" dataDxfId="125"/>
+    <tableColumn id="6" xr3:uid="{8212B4F5-4682-42D4-98D2-666EB7851034}" name="Test Data" dataDxfId="124"/>
+    <tableColumn id="7" xr3:uid="{C27ADF5D-D13B-4776-B1DB-99BAC727A1EF}" name="Test Step" dataDxfId="123"/>
+    <tableColumn id="8" xr3:uid="{87D91BD6-44DB-42EC-A509-CF909B0841C6}" name="Post Condition" dataDxfId="122"/>
+    <tableColumn id="9" xr3:uid="{CF0F8DF7-50EC-4BF7-9A2B-B588E2C6AD3C}" name="Expected Result" dataDxfId="121"/>
+    <tableColumn id="10" xr3:uid="{28E800BE-C6F2-40A9-92FE-FB97DA376781}" name="Actual Result" dataDxfId="120"/>
+    <tableColumn id="11" xr3:uid="{A019A1D5-1AC2-4238-9C78-8D26EEBABBDD}" name="Status" dataDxfId="119"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{CDD8D6C6-33F1-4988-A8DE-6D9CC0E8CF5A}" name="Table4" displayName="Table4" ref="A1:K4" totalsRowShown="0" dataDxfId="71">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{CDD8D6C6-33F1-4988-A8DE-6D9CC0E8CF5A}" name="Table4" displayName="Table4" ref="A1:K4" totalsRowShown="0" headerRowDxfId="118" dataDxfId="117">
   <autoFilter ref="A1:K4" xr:uid="{CDD8D6C6-33F1-4988-A8DE-6D9CC0E8CF5A}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{30F17F19-8468-4A66-86EF-0BD83413ACA1}" name="Test Case ID" dataDxfId="82"/>
-    <tableColumn id="2" xr3:uid="{4A6BE90C-FDB5-4937-A0BB-FD1D07A1E264}" name="Test Scenario" dataDxfId="81"/>
-    <tableColumn id="3" xr3:uid="{A81A0D12-E511-4B28-B531-BA483F89581B}" name="Test Case Title" dataDxfId="80"/>
-    <tableColumn id="4" xr3:uid="{53B96AA9-7E95-49E4-A854-6D23E07EB42E}" name="Test Description" dataDxfId="79"/>
-    <tableColumn id="5" xr3:uid="{43B4D6A6-A260-4A56-B9E0-614CAA640920}" name="Precondition" dataDxfId="78"/>
-    <tableColumn id="6" xr3:uid="{125F2F89-B04E-4C4D-B84C-C5971AA23E32}" name="Test Data" dataDxfId="77"/>
-    <tableColumn id="7" xr3:uid="{532C8225-844B-43DE-B1D4-C10DDE0F4A7C}" name="Test Step" dataDxfId="76"/>
-    <tableColumn id="8" xr3:uid="{B349F424-2BCB-47BB-8B8D-7325C04BE2E2}" name="Post Condition" dataDxfId="75"/>
-    <tableColumn id="9" xr3:uid="{74D85BD0-D32D-46A4-9A02-3587A682A2A5}" name="Expected Result" dataDxfId="74"/>
-    <tableColumn id="10" xr3:uid="{16D75875-4017-4E31-BEF6-C8B6145CA67A}" name="Actual Result" dataDxfId="73"/>
-    <tableColumn id="11" xr3:uid="{6B9A5924-AE80-4BC1-AC2A-514E412DBC11}" name="Status" dataDxfId="72"/>
+    <tableColumn id="1" xr3:uid="{30F17F19-8468-4A66-86EF-0BD83413ACA1}" name="Test Case ID" dataDxfId="116"/>
+    <tableColumn id="2" xr3:uid="{4A6BE90C-FDB5-4937-A0BB-FD1D07A1E264}" name="Test Scenario" dataDxfId="115"/>
+    <tableColumn id="3" xr3:uid="{A81A0D12-E511-4B28-B531-BA483F89581B}" name="Test Case Title" dataDxfId="114"/>
+    <tableColumn id="4" xr3:uid="{53B96AA9-7E95-49E4-A854-6D23E07EB42E}" name="Test Description" dataDxfId="113"/>
+    <tableColumn id="5" xr3:uid="{43B4D6A6-A260-4A56-B9E0-614CAA640920}" name="Precondition" dataDxfId="112"/>
+    <tableColumn id="6" xr3:uid="{125F2F89-B04E-4C4D-B84C-C5971AA23E32}" name="Test Data" dataDxfId="111"/>
+    <tableColumn id="7" xr3:uid="{532C8225-844B-43DE-B1D4-C10DDE0F4A7C}" name="Test Step" dataDxfId="110"/>
+    <tableColumn id="8" xr3:uid="{B349F424-2BCB-47BB-8B8D-7325C04BE2E2}" name="Post Condition" dataDxfId="109"/>
+    <tableColumn id="9" xr3:uid="{74D85BD0-D32D-46A4-9A02-3587A682A2A5}" name="Expected Result" dataDxfId="108"/>
+    <tableColumn id="10" xr3:uid="{16D75875-4017-4E31-BEF6-C8B6145CA67A}" name="Actual Result" dataDxfId="107"/>
+    <tableColumn id="11" xr3:uid="{6B9A5924-AE80-4BC1-AC2A-514E412DBC11}" name="Status" dataDxfId="106"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{2F2CD9A7-F28B-49A3-BA1A-8B9419497702}" name="Table5" displayName="Table5" ref="A1:K1048536" totalsRowShown="0" headerRowDxfId="143" dataDxfId="59">
-  <autoFilter ref="A1:K1048536" xr:uid="{2F2CD9A7-F28B-49A3-BA1A-8B9419497702}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{2E3F6B91-1F8B-4FE1-A0AC-D1A0FB7AA9CF}" name="Table5" displayName="Table5" ref="A1:K5" totalsRowShown="0" headerRowDxfId="105" dataDxfId="104" tableBorderDxfId="103">
+  <autoFilter ref="A1:K5" xr:uid="{2E3F6B91-1F8B-4FE1-A0AC-D1A0FB7AA9CF}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{0D226DCB-6C82-4EC9-B004-7987CA88E747}" name="Test Case ID" dataDxfId="70"/>
-    <tableColumn id="2" xr3:uid="{2B8C524D-F967-4CD2-99DB-17BB7C53B979}" name="Test Scenario" dataDxfId="69"/>
-    <tableColumn id="3" xr3:uid="{8F126CDB-54FF-4428-9D53-80F7CD33AE59}" name="Test Case Title" dataDxfId="68"/>
-    <tableColumn id="4" xr3:uid="{2F835388-3B79-45BC-B9D6-6D0B342331C2}" name="Test Description" dataDxfId="67"/>
-    <tableColumn id="5" xr3:uid="{96290188-9DCF-4A07-AED0-00B8C688CE2D}" name="Precondition" dataDxfId="66"/>
-    <tableColumn id="6" xr3:uid="{1654F620-E13C-417D-80C1-5E39317DDB39}" name="Test Data" dataDxfId="65"/>
-    <tableColumn id="7" xr3:uid="{68D864EC-D616-410E-AD3B-027AB6C374BA}" name="Test Step" dataDxfId="64"/>
-    <tableColumn id="8" xr3:uid="{3AD86295-3168-4771-8600-051142D0F686}" name="Post Condition" dataDxfId="63"/>
-    <tableColumn id="9" xr3:uid="{EC3E50E0-492E-4FCC-9623-21B63D026C38}" name="Expected Result" dataDxfId="62"/>
-    <tableColumn id="10" xr3:uid="{AA545278-7F12-4EEA-8BE8-01C01ABC7EBA}" name="Actual Result" dataDxfId="61"/>
-    <tableColumn id="11" xr3:uid="{8BA99794-01D4-49A8-AF75-A6D90B674686}" name="Status" dataDxfId="60"/>
+    <tableColumn id="1" xr3:uid="{6876B7D9-AED4-40A7-9B3F-EAAE7EC27F19}" name="Test Case ID" dataDxfId="102"/>
+    <tableColumn id="2" xr3:uid="{586F0A72-FB20-402D-B906-57CEC15B5844}" name="Test Scenario" dataDxfId="101"/>
+    <tableColumn id="3" xr3:uid="{FD20C9B8-3526-43CA-8EF7-13306F6F1E73}" name="Test Case Title" dataDxfId="100"/>
+    <tableColumn id="4" xr3:uid="{745A2EB8-ABE5-4979-B5E6-271B46F7EF61}" name="Test Description" dataDxfId="99"/>
+    <tableColumn id="5" xr3:uid="{32B27CD7-3A6A-4BC6-864D-23319902CC30}" name="Precondition" dataDxfId="98"/>
+    <tableColumn id="6" xr3:uid="{3B781098-E0A9-48D9-B5BC-2FB2A26565E5}" name="Test Data" dataDxfId="97"/>
+    <tableColumn id="7" xr3:uid="{45BBE8D4-63E2-416F-ACC2-7CD2C1C91220}" name="Test Step" dataDxfId="96"/>
+    <tableColumn id="8" xr3:uid="{CA3B1689-8E28-4BD5-9C34-18D7D98C1AAC}" name="Post Condition" dataDxfId="95"/>
+    <tableColumn id="9" xr3:uid="{B4CDF521-EE6D-4DF0-872E-9D72AC1E8555}" name="Expected Result" dataDxfId="94"/>
+    <tableColumn id="10" xr3:uid="{E6AAEB15-C80D-4145-B1B3-C95E2ACCF6EF}" name="Actual Result" dataDxfId="93"/>
+    <tableColumn id="11" xr3:uid="{73F576F5-8370-4E97-BEBB-223ABB9B606A}" name="Status" dataDxfId="92"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{C4579C64-BF71-4412-B0D5-57B184F01462}" name="Table6" displayName="Table6" ref="A1:K6" totalsRowShown="0" headerRowDxfId="142" dataDxfId="46">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{C4579C64-BF71-4412-B0D5-57B184F01462}" name="Table6" displayName="Table6" ref="A1:K6" totalsRowShown="0" headerRowDxfId="91" dataDxfId="90">
   <autoFilter ref="A1:K6" xr:uid="{C4579C64-BF71-4412-B0D5-57B184F01462}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{0CBAA722-80DA-4B08-85C0-C0643AD8A54D}" name="Test Case ID" dataDxfId="57"/>
-    <tableColumn id="2" xr3:uid="{1AE71C13-BF8A-46EB-8744-52C4492B1CA8}" name="Test Scenario" dataDxfId="56"/>
-    <tableColumn id="3" xr3:uid="{DEF6BFB4-FC3B-4290-BB73-914F5D0B138C}" name="Test Case Title" dataDxfId="55"/>
-    <tableColumn id="4" xr3:uid="{046A0014-010C-4B5D-BF73-3F6A7EA80901}" name="Test Description" dataDxfId="54"/>
-    <tableColumn id="5" xr3:uid="{B0659832-BE71-4176-9A59-0F58481951A5}" name="Precondition" dataDxfId="53"/>
-    <tableColumn id="6" xr3:uid="{86937CF6-785A-4BD5-9949-C42326EF2091}" name="Test Data" dataDxfId="52"/>
-    <tableColumn id="7" xr3:uid="{F4174DC9-407D-4FFC-8A52-D9003B91192F}" name="Test Step" dataDxfId="51"/>
-    <tableColumn id="8" xr3:uid="{8E2C6CB3-792C-458C-89B9-86623CAEAEFC}" name="Post Condition" dataDxfId="50"/>
-    <tableColumn id="9" xr3:uid="{15B93BDE-1870-4194-97A8-207E864C076F}" name="Expected Result" dataDxfId="49"/>
-    <tableColumn id="10" xr3:uid="{11F7E854-2EC6-4E5B-9967-97D2AF75D128}" name="Actual Result" dataDxfId="48"/>
-    <tableColumn id="11" xr3:uid="{8CF96C9E-249C-44E9-B980-052118023CDD}" name="Status" dataDxfId="47"/>
+    <tableColumn id="1" xr3:uid="{0CBAA722-80DA-4B08-85C0-C0643AD8A54D}" name="Test Case ID" dataDxfId="89"/>
+    <tableColumn id="2" xr3:uid="{1AE71C13-BF8A-46EB-8744-52C4492B1CA8}" name="Test Scenario" dataDxfId="88"/>
+    <tableColumn id="3" xr3:uid="{DEF6BFB4-FC3B-4290-BB73-914F5D0B138C}" name="Test Case Title" dataDxfId="87"/>
+    <tableColumn id="4" xr3:uid="{046A0014-010C-4B5D-BF73-3F6A7EA80901}" name="Test Description" dataDxfId="86"/>
+    <tableColumn id="5" xr3:uid="{B0659832-BE71-4176-9A59-0F58481951A5}" name="Precondition" dataDxfId="85"/>
+    <tableColumn id="6" xr3:uid="{86937CF6-785A-4BD5-9949-C42326EF2091}" name="Test Data" dataDxfId="84"/>
+    <tableColumn id="7" xr3:uid="{F4174DC9-407D-4FFC-8A52-D9003B91192F}" name="Test Step" dataDxfId="83"/>
+    <tableColumn id="8" xr3:uid="{8E2C6CB3-792C-458C-89B9-86623CAEAEFC}" name="Post Condition" dataDxfId="82"/>
+    <tableColumn id="9" xr3:uid="{15B93BDE-1870-4194-97A8-207E864C076F}" name="Expected Result" dataDxfId="81"/>
+    <tableColumn id="10" xr3:uid="{11F7E854-2EC6-4E5B-9967-97D2AF75D128}" name="Actual Result" dataDxfId="80"/>
+    <tableColumn id="11" xr3:uid="{8CF96C9E-249C-44E9-B980-052118023CDD}" name="Status" dataDxfId="79"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{C5E2AD33-062C-4FF3-97E2-14489F8737F1}" name="Table7" displayName="Table7" ref="A1:K6" totalsRowShown="0" headerRowDxfId="34" dataDxfId="33">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{C5E2AD33-062C-4FF3-97E2-14489F8737F1}" name="Table7" displayName="Table7" ref="A1:K6" totalsRowShown="0" headerRowDxfId="163" dataDxfId="162">
   <autoFilter ref="A1:K6" xr:uid="{C5E2AD33-062C-4FF3-97E2-14489F8737F1}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{CCBD9104-AFBA-47C3-8646-BBD44D55B38B}" name="Test Case ID" dataDxfId="45"/>
-    <tableColumn id="2" xr3:uid="{31C7960A-934A-41FB-B59F-E05141EDD80A}" name="Test Scenario" dataDxfId="44"/>
-    <tableColumn id="3" xr3:uid="{4AEC1D30-8657-40F5-832C-2953CD84B686}" name="Test Case Title" dataDxfId="43"/>
-    <tableColumn id="4" xr3:uid="{0FFF58E0-3C76-4C11-A76F-388626A5967B}" name="Test Description" dataDxfId="42"/>
-    <tableColumn id="5" xr3:uid="{9407EA85-7D2E-4347-B374-302A957DB7C6}" name="Precondition" dataDxfId="41"/>
-    <tableColumn id="6" xr3:uid="{21F6E5C5-88ED-423D-A4A8-0A4611713610}" name="Test Data" dataDxfId="40"/>
-    <tableColumn id="7" xr3:uid="{9F5F42E4-CFB2-4DA8-8C26-83A88E35D7BF}" name="Test Step" dataDxfId="39"/>
-    <tableColumn id="8" xr3:uid="{94D4F544-5CE4-4724-BB7C-0D5E7E5BA04A}" name="Post Condition" dataDxfId="38"/>
-    <tableColumn id="9" xr3:uid="{EC00A77A-F3B3-4584-88AE-EC522129EB55}" name="Expected Result" dataDxfId="37"/>
-    <tableColumn id="10" xr3:uid="{5B0A3255-9926-4CF2-BF04-AA0AB69B800C}" name="Actual Result" dataDxfId="36"/>
-    <tableColumn id="11" xr3:uid="{FAEC2F86-5C61-44B3-9E1A-0EE2E542A7B9}" name="Status" dataDxfId="35"/>
+    <tableColumn id="1" xr3:uid="{CCBD9104-AFBA-47C3-8646-BBD44D55B38B}" name="Test Case ID" dataDxfId="161"/>
+    <tableColumn id="2" xr3:uid="{31C7960A-934A-41FB-B59F-E05141EDD80A}" name="Test Scenario" dataDxfId="160"/>
+    <tableColumn id="3" xr3:uid="{4AEC1D30-8657-40F5-832C-2953CD84B686}" name="Test Case Title" dataDxfId="159"/>
+    <tableColumn id="4" xr3:uid="{0FFF58E0-3C76-4C11-A76F-388626A5967B}" name="Test Description" dataDxfId="158"/>
+    <tableColumn id="5" xr3:uid="{9407EA85-7D2E-4347-B374-302A957DB7C6}" name="Precondition" dataDxfId="157"/>
+    <tableColumn id="6" xr3:uid="{21F6E5C5-88ED-423D-A4A8-0A4611713610}" name="Test Data" dataDxfId="156"/>
+    <tableColumn id="7" xr3:uid="{9F5F42E4-CFB2-4DA8-8C26-83A88E35D7BF}" name="Test Step" dataDxfId="155"/>
+    <tableColumn id="8" xr3:uid="{94D4F544-5CE4-4724-BB7C-0D5E7E5BA04A}" name="Post Condition" dataDxfId="154"/>
+    <tableColumn id="9" xr3:uid="{EC00A77A-F3B3-4584-88AE-EC522129EB55}" name="Expected Result" dataDxfId="153"/>
+    <tableColumn id="10" xr3:uid="{5B0A3255-9926-4CF2-BF04-AA0AB69B800C}" name="Actual Result" dataDxfId="152"/>
+    <tableColumn id="11" xr3:uid="{FAEC2F86-5C61-44B3-9E1A-0EE2E542A7B9}" name="Status" dataDxfId="151"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{76C7F6F1-DEA0-45ED-9527-F69EBF725CC3}" name="Table8" displayName="Table8" ref="A1:K8" totalsRowShown="0" dataDxfId="21">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{76C7F6F1-DEA0-45ED-9527-F69EBF725CC3}" name="Table8" displayName="Table8" ref="A1:K8" totalsRowShown="0" dataDxfId="78">
   <autoFilter ref="A1:K8" xr:uid="{76C7F6F1-DEA0-45ED-9527-F69EBF725CC3}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{78F7358B-BBF5-4E44-95AB-658611EC578F}" name="Test Case ID" dataDxfId="32"/>
-    <tableColumn id="2" xr3:uid="{4C2135E9-2DC4-4097-B4BC-F2C75DD17DC5}" name="Test Scenario" dataDxfId="31"/>
-    <tableColumn id="3" xr3:uid="{6D5B481E-4B3E-4AB4-B904-FBB02F64973F}" name="Test Case Title" dataDxfId="30"/>
-    <tableColumn id="4" xr3:uid="{C798261B-A80F-41B4-B2FF-A03FB57028CA}" name="Test Description" dataDxfId="29"/>
-    <tableColumn id="5" xr3:uid="{B2C9C8E7-63BF-4BD3-AB7C-0B94F88557DC}" name="Precondition" dataDxfId="28"/>
-    <tableColumn id="6" xr3:uid="{3DCB78A0-24D7-4E9E-A397-A7ED87EDB0DC}" name="Test Data" dataDxfId="27"/>
-    <tableColumn id="7" xr3:uid="{7C1F9FC6-BFAA-4E1F-A192-B44375AC929B}" name="Test Step" dataDxfId="26"/>
-    <tableColumn id="8" xr3:uid="{EEE8B405-347E-49F5-B1D8-F91861C4FC16}" name="Post Condition" dataDxfId="25"/>
-    <tableColumn id="9" xr3:uid="{10C2E695-D46A-4680-BE17-45F9AE21F104}" name="Expected Result" dataDxfId="24"/>
-    <tableColumn id="10" xr3:uid="{C6D62D5E-0EAB-47C0-9C55-C96F9AF6647F}" name="Actual Result" dataDxfId="23"/>
-    <tableColumn id="11" xr3:uid="{789CA9A0-3FA3-467F-8F87-FC85389D8700}" name="Status" dataDxfId="22"/>
+    <tableColumn id="1" xr3:uid="{78F7358B-BBF5-4E44-95AB-658611EC578F}" name="Test Case ID" dataDxfId="77"/>
+    <tableColumn id="2" xr3:uid="{4C2135E9-2DC4-4097-B4BC-F2C75DD17DC5}" name="Test Scenario" dataDxfId="76"/>
+    <tableColumn id="3" xr3:uid="{6D5B481E-4B3E-4AB4-B904-FBB02F64973F}" name="Test Case Title" dataDxfId="75"/>
+    <tableColumn id="4" xr3:uid="{C798261B-A80F-41B4-B2FF-A03FB57028CA}" name="Test Description" dataDxfId="74"/>
+    <tableColumn id="5" xr3:uid="{B2C9C8E7-63BF-4BD3-AB7C-0B94F88557DC}" name="Precondition" dataDxfId="73"/>
+    <tableColumn id="6" xr3:uid="{3DCB78A0-24D7-4E9E-A397-A7ED87EDB0DC}" name="Test Data" dataDxfId="72"/>
+    <tableColumn id="7" xr3:uid="{7C1F9FC6-BFAA-4E1F-A192-B44375AC929B}" name="Test Step" dataDxfId="71"/>
+    <tableColumn id="8" xr3:uid="{EEE8B405-347E-49F5-B1D8-F91861C4FC16}" name="Post Condition" dataDxfId="70"/>
+    <tableColumn id="9" xr3:uid="{10C2E695-D46A-4680-BE17-45F9AE21F104}" name="Expected Result" dataDxfId="69"/>
+    <tableColumn id="10" xr3:uid="{C6D62D5E-0EAB-47C0-9C55-C96F9AF6647F}" name="Actual Result" dataDxfId="68"/>
+    <tableColumn id="11" xr3:uid="{789CA9A0-3FA3-467F-8F87-FC85389D8700}" name="Status" dataDxfId="67"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{977FBCCA-BB0D-471A-B840-B1BF610C9A7E}" name="Table9" displayName="Table9" ref="A1:K6" totalsRowShown="0" headerRowDxfId="141" dataDxfId="113">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{977FBCCA-BB0D-471A-B840-B1BF610C9A7E}" name="Table9" displayName="Table9" ref="A1:K6" totalsRowShown="0" headerRowDxfId="66" dataDxfId="65">
   <autoFilter ref="A1:K6" xr:uid="{977FBCCA-BB0D-471A-B840-B1BF610C9A7E}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{E14DB9FF-88A1-4EE7-B230-D8894A0E1AFB}" name="Test Case ID" dataDxfId="124"/>
-    <tableColumn id="2" xr3:uid="{D4FC117F-56A6-412F-984A-D6DBFC8F6B01}" name="Test Scenario" dataDxfId="123"/>
-    <tableColumn id="3" xr3:uid="{E5DE9E41-179E-45D8-A348-BD490AC75E5D}" name="Test Case Title" dataDxfId="122"/>
-    <tableColumn id="4" xr3:uid="{89C1E1C2-62E8-4407-A716-9188B6576B51}" name="Test Description" dataDxfId="121"/>
-    <tableColumn id="5" xr3:uid="{9FC31264-0A03-44DC-BB14-CE8594D16932}" name="Precondition" dataDxfId="120"/>
-    <tableColumn id="6" xr3:uid="{52040CDD-D184-449A-AA2D-20B3EB5BD5EF}" name="Test Data" dataDxfId="119"/>
-    <tableColumn id="7" xr3:uid="{057CB6AB-A65B-40E5-BF01-A6F370B4BCA2}" name="Test Step" dataDxfId="118"/>
-    <tableColumn id="8" xr3:uid="{0CADDAEE-24CB-4B0B-BD9A-A1895CB19AC7}" name="Post Condition" dataDxfId="117"/>
-    <tableColumn id="9" xr3:uid="{33917D9D-4F6F-4611-9B5E-C61943DC50AE}" name="Expected Result" dataDxfId="116"/>
-    <tableColumn id="10" xr3:uid="{FEFFF501-E422-47CC-ACA8-7793EF2B2B40}" name="Actual Result" dataDxfId="115"/>
-    <tableColumn id="11" xr3:uid="{BAD0A7C4-8AC6-4E11-87E7-837E3A37BD85}" name="Status" dataDxfId="114"/>
+    <tableColumn id="1" xr3:uid="{E14DB9FF-88A1-4EE7-B230-D8894A0E1AFB}" name="Test Case ID" dataDxfId="64"/>
+    <tableColumn id="2" xr3:uid="{D4FC117F-56A6-412F-984A-D6DBFC8F6B01}" name="Test Scenario" dataDxfId="63"/>
+    <tableColumn id="3" xr3:uid="{E5DE9E41-179E-45D8-A348-BD490AC75E5D}" name="Test Case Title" dataDxfId="62"/>
+    <tableColumn id="4" xr3:uid="{89C1E1C2-62E8-4407-A716-9188B6576B51}" name="Test Description" dataDxfId="61"/>
+    <tableColumn id="5" xr3:uid="{9FC31264-0A03-44DC-BB14-CE8594D16932}" name="Precondition" dataDxfId="60"/>
+    <tableColumn id="6" xr3:uid="{52040CDD-D184-449A-AA2D-20B3EB5BD5EF}" name="Test Data" dataDxfId="59"/>
+    <tableColumn id="7" xr3:uid="{057CB6AB-A65B-40E5-BF01-A6F370B4BCA2}" name="Test Step" dataDxfId="58"/>
+    <tableColumn id="8" xr3:uid="{0CADDAEE-24CB-4B0B-BD9A-A1895CB19AC7}" name="Post Condition" dataDxfId="57"/>
+    <tableColumn id="9" xr3:uid="{33917D9D-4F6F-4611-9B5E-C61943DC50AE}" name="Expected Result" dataDxfId="56"/>
+    <tableColumn id="10" xr3:uid="{FEFFF501-E422-47CC-ACA8-7793EF2B2B40}" name="Actual Result" dataDxfId="55"/>
+    <tableColumn id="11" xr3:uid="{BAD0A7C4-8AC6-4E11-87E7-837E3A37BD85}" name="Status" dataDxfId="54"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2685,200 +3653,200 @@
   <dimension ref="A1:D16"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="28" style="13" customWidth="1"/>
-    <col min="2" max="2" width="58" style="13" customWidth="1"/>
-    <col min="3" max="3" width="12" style="13" customWidth="1"/>
-    <col min="4" max="4" width="21.9296875" style="13" customWidth="1"/>
-    <col min="5" max="16384" width="8.6640625" style="13"/>
+    <col min="1" max="1" width="28" style="5" customWidth="1"/>
+    <col min="2" max="2" width="58" style="5" customWidth="1"/>
+    <col min="3" max="3" width="12" style="5" customWidth="1"/>
+    <col min="4" max="4" width="21.9296875" style="5" customWidth="1"/>
+    <col min="5" max="16384" width="8.6640625" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="13" customFormat="1" ht="18" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A1" s="10" t="s">
+    <row r="1" spans="1:4" ht="18" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="11" t="s">
-        <v>381</v>
-      </c>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-    </row>
-    <row r="2" spans="1:4" s="13" customFormat="1" ht="18" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A2" s="10" t="s">
+      <c r="B1" s="15" t="s">
+        <v>366</v>
+      </c>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+    </row>
+    <row r="2" spans="1:4" ht="18" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A2" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="11" t="s">
+      <c r="B2" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="11"/>
-      <c r="D2" s="11"/>
-    </row>
-    <row r="3" spans="1:4" s="13" customFormat="1" ht="18" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A3" s="10" t="s">
+      <c r="C2" s="15"/>
+      <c r="D2" s="15"/>
+    </row>
+    <row r="3" spans="1:4" ht="18" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A3" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="11" t="s">
-        <v>382</v>
-      </c>
-      <c r="C3" s="11"/>
-      <c r="D3" s="11"/>
-    </row>
-    <row r="4" spans="1:4" s="13" customFormat="1" ht="18" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A4" s="10" t="s">
+      <c r="B3" s="15" t="s">
+        <v>367</v>
+      </c>
+      <c r="C3" s="15"/>
+      <c r="D3" s="15"/>
+    </row>
+    <row r="4" spans="1:4" ht="18" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A4" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="12">
+      <c r="B4" s="16">
         <v>46163</v>
       </c>
-      <c r="C4" s="11"/>
-      <c r="D4" s="11"/>
-    </row>
-    <row r="5" spans="1:4" s="13" customFormat="1" ht="18" customHeight="1" thickTop="1" x14ac:dyDescent="0.45">
-      <c r="A5" s="8"/>
-      <c r="B5" s="9"/>
-      <c r="C5" s="9"/>
-      <c r="D5" s="9"/>
-    </row>
-    <row r="6" spans="1:4" s="13" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A6" s="13" t="s">
+      <c r="C4" s="15"/>
+      <c r="D4" s="15"/>
+    </row>
+    <row r="5" spans="1:4" ht="18" customHeight="1" thickTop="1" x14ac:dyDescent="0.45">
+      <c r="A5" s="2"/>
+      <c r="B5" s="3"/>
+      <c r="C5" s="3"/>
+      <c r="D5" s="3"/>
+    </row>
+    <row r="6" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A6" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="13" t="s">
+      <c r="B6" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="13" t="s">
+      <c r="C6" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="D6" s="13" t="s">
+      <c r="D6" s="5" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:4" s="13" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A7" s="13" t="s">
-        <v>383</v>
-      </c>
-      <c r="B7" s="13" t="s">
+    <row r="7" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A7" s="5" t="s">
+        <v>368</v>
+      </c>
+      <c r="B7" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="19" t="s">
+      <c r="C7" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D7" s="13">
+      <c r="D7" s="5">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:4" s="13" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A8" s="13" t="s">
-        <v>385</v>
-      </c>
-      <c r="B8" s="13" t="s">
+    <row r="8" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A8" s="5" t="s">
+        <v>370</v>
+      </c>
+      <c r="B8" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C8" s="19" t="s">
+      <c r="C8" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D8" s="13">
+      <c r="D8" s="5">
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:4" s="13" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A9" s="13" t="s">
-        <v>384</v>
-      </c>
-      <c r="B9" s="13" t="s">
+    <row r="9" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A9" s="5" t="s">
+        <v>369</v>
+      </c>
+      <c r="B9" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C9" s="19" t="s">
+      <c r="C9" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D9" s="13">
+      <c r="D9" s="5">
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:4" s="13" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A10" s="13" t="s">
-        <v>386</v>
-      </c>
-      <c r="B10" s="13" t="s">
+    <row r="10" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A10" s="5" t="s">
+        <v>371</v>
+      </c>
+      <c r="B10" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="C10" s="20" t="s">
+      <c r="C10" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="D10" s="13">
+      <c r="D10" s="5">
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:4" s="13" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A11" s="13" t="s">
-        <v>388</v>
-      </c>
-      <c r="B11" s="13" t="s">
+    <row r="11" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A11" s="5" t="s">
+        <v>373</v>
+      </c>
+      <c r="B11" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="C11" s="21" t="s">
+      <c r="C11" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="D11" s="13">
+      <c r="D11" s="5">
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:4" s="13" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A12" s="13" t="s">
-        <v>387</v>
-      </c>
-      <c r="B12" s="13" t="s">
+    <row r="12" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A12" s="5" t="s">
+        <v>372</v>
+      </c>
+      <c r="B12" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="C12" s="21" t="s">
+      <c r="C12" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="D12" s="13">
+      <c r="D12" s="5">
         <v>5</v>
       </c>
     </row>
-    <row r="13" spans="1:4" s="13" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A13" s="13" t="s">
-        <v>392</v>
-      </c>
-      <c r="B13" s="13" t="s">
+    <row r="13" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A13" s="5" t="s">
+        <v>377</v>
+      </c>
+      <c r="B13" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C13" s="21" t="s">
+      <c r="C13" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="D13" s="13">
+      <c r="D13" s="5">
         <v>7</v>
       </c>
     </row>
-    <row r="14" spans="1:4" s="13" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A14" s="13" t="s">
-        <v>393</v>
-      </c>
-      <c r="B14" s="13" t="s">
+    <row r="14" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A14" s="5" t="s">
+        <v>378</v>
+      </c>
+      <c r="B14" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="21" t="s">
+      <c r="C14" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="D14" s="13">
+      <c r="D14" s="5">
         <v>5</v>
       </c>
     </row>
-    <row r="15" spans="1:4" s="13" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A15" s="13" t="s">
-        <v>394</v>
-      </c>
-      <c r="B15" s="13" t="s">
+    <row r="15" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A15" s="5" t="s">
+        <v>379</v>
+      </c>
+      <c r="B15" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="C15" s="21" t="s">
+      <c r="C15" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="D15" s="13">
+      <c r="D15" s="5">
         <v>6</v>
       </c>
     </row>
-    <row r="16" spans="1:4" s="13" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="16" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.45"/>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="B1:D1"/>
@@ -2913,231 +3881,260 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="25.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="D1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="E1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="F1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="G1" s="7" t="s">
+      <c r="G1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="H1" s="7" t="s">
+      <c r="H1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="I1" s="7" t="s">
+      <c r="I1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="J1" s="7" t="s">
+      <c r="J1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="K1" s="7" t="s">
+      <c r="K1" s="1" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="47.65" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="13" t="s">
+      <c r="A2" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="B2" s="13" t="s">
-        <v>397</v>
-      </c>
-      <c r="C2" s="13" t="s">
+      <c r="B2" s="5" t="s">
+        <v>382</v>
+      </c>
+      <c r="C2" s="5" t="s">
         <v>284</v>
       </c>
-      <c r="D2" s="13" t="s">
+      <c r="D2" s="5" t="s">
         <v>285</v>
       </c>
-      <c r="E2" s="13" t="s">
+      <c r="E2" s="5" t="s">
         <v>286</v>
       </c>
-      <c r="F2" s="13" t="s">
+      <c r="F2" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="G2" s="13" t="s">
+      <c r="G2" s="5" t="s">
         <v>287</v>
       </c>
-      <c r="H2" s="13" t="s">
+      <c r="H2" s="5" t="s">
         <v>288</v>
       </c>
-      <c r="I2" s="13" t="s">
+      <c r="I2" s="5" t="s">
         <v>289</v>
       </c>
-      <c r="J2" s="13"/>
-      <c r="K2" s="13"/>
+      <c r="J2" s="5" t="s">
+        <v>419</v>
+      </c>
+      <c r="K2" s="5" t="s">
+        <v>348</v>
+      </c>
     </row>
     <row r="3" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A3" s="13" t="s">
+      <c r="A3" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B3" s="13" t="s">
-        <v>397</v>
-      </c>
-      <c r="C3" s="13" t="s">
+      <c r="B3" s="5" t="s">
+        <v>382</v>
+      </c>
+      <c r="C3" s="5" t="s">
         <v>290</v>
       </c>
-      <c r="D3" s="13" t="s">
+      <c r="D3" s="5" t="s">
         <v>291</v>
       </c>
-      <c r="E3" s="13" t="s">
+      <c r="E3" s="5" t="s">
         <v>292</v>
       </c>
-      <c r="F3" s="13" t="s">
+      <c r="F3" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="G3" s="13" t="s">
+      <c r="G3" s="5" t="s">
         <v>293</v>
       </c>
-      <c r="H3" s="13" t="s">
+      <c r="H3" s="5" t="s">
         <v>294</v>
       </c>
-      <c r="I3" s="13" t="s">
+      <c r="I3" s="5" t="s">
         <v>295</v>
       </c>
-      <c r="J3" s="13"/>
-      <c r="K3" s="13"/>
+      <c r="J3" s="5" t="s">
+        <v>420</v>
+      </c>
+      <c r="K3" s="5" t="s">
+        <v>348</v>
+      </c>
     </row>
     <row r="4" spans="1:11" ht="51.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A4" s="13" t="s">
+      <c r="A4" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="B4" s="13" t="s">
-        <v>397</v>
-      </c>
-      <c r="C4" s="13" t="s">
+      <c r="B4" s="5" t="s">
+        <v>382</v>
+      </c>
+      <c r="C4" s="5" t="s">
         <v>296</v>
       </c>
-      <c r="D4" s="13" t="s">
+      <c r="D4" s="5" t="s">
         <v>297</v>
       </c>
-      <c r="E4" s="13" t="s">
+      <c r="E4" s="5" t="s">
         <v>298</v>
       </c>
-      <c r="F4" s="13" t="s">
+      <c r="F4" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="G4" s="13" t="s">
+      <c r="G4" s="5" t="s">
         <v>299</v>
       </c>
-      <c r="H4" s="13" t="s">
+      <c r="H4" s="5" t="s">
         <v>300</v>
       </c>
-      <c r="I4" s="13" t="s">
+      <c r="I4" s="5" t="s">
         <v>301</v>
       </c>
-      <c r="J4" s="13"/>
-      <c r="K4" s="13"/>
+      <c r="J4" s="5" t="s">
+        <v>421</v>
+      </c>
+      <c r="K4" s="5" t="s">
+        <v>348</v>
+      </c>
     </row>
     <row r="5" spans="1:11" ht="51.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A5" s="13" t="s">
+      <c r="A5" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="B5" s="13" t="s">
-        <v>397</v>
-      </c>
-      <c r="C5" s="13" t="s">
+      <c r="B5" s="5" t="s">
+        <v>382</v>
+      </c>
+      <c r="C5" s="5" t="s">
         <v>302</v>
       </c>
-      <c r="D5" s="13" t="s">
+      <c r="D5" s="5" t="s">
         <v>303</v>
       </c>
-      <c r="E5" s="13" t="s">
+      <c r="E5" s="5" t="s">
         <v>304</v>
       </c>
-      <c r="F5" s="13" t="s">
+      <c r="F5" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="G5" s="13" t="s">
+      <c r="G5" s="5" t="s">
         <v>305</v>
       </c>
-      <c r="H5" s="13" t="s">
+      <c r="H5" s="5" t="s">
         <v>306</v>
       </c>
-      <c r="I5" s="22" t="s">
-        <v>398</v>
-      </c>
-      <c r="J5" s="13"/>
-      <c r="K5" s="13"/>
+      <c r="I5" s="10" t="s">
+        <v>383</v>
+      </c>
+      <c r="J5" s="5" t="s">
+        <v>422</v>
+      </c>
+      <c r="K5" s="5" t="s">
+        <v>348</v>
+      </c>
     </row>
     <row r="6" spans="1:11" ht="51.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A6" s="13" t="s">
+      <c r="A6" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="B6" s="13" t="s">
-        <v>397</v>
-      </c>
-      <c r="C6" s="13" t="s">
+      <c r="B6" s="5" t="s">
+        <v>382</v>
+      </c>
+      <c r="C6" s="5" t="s">
         <v>307</v>
       </c>
-      <c r="D6" s="13" t="s">
+      <c r="D6" s="5" t="s">
         <v>308</v>
       </c>
-      <c r="E6" s="13" t="s">
+      <c r="E6" s="5" t="s">
         <v>309</v>
       </c>
-      <c r="F6" s="13" t="s">
+      <c r="F6" s="5" t="s">
         <v>310</v>
       </c>
-      <c r="G6" s="13" t="s">
+      <c r="G6" s="5" t="s">
         <v>311</v>
       </c>
-      <c r="H6" s="13" t="s">
+      <c r="H6" s="5" t="s">
         <v>312</v>
       </c>
-      <c r="I6" s="13" t="s">
+      <c r="I6" s="5" t="s">
         <v>313</v>
       </c>
-      <c r="J6" s="13"/>
-      <c r="K6" s="13"/>
+      <c r="J6" s="5" t="s">
+        <v>423</v>
+      </c>
+      <c r="K6" s="5" t="s">
+        <v>348</v>
+      </c>
     </row>
     <row r="7" spans="1:11" ht="51.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A7" s="13" t="s">
+      <c r="A7" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="B7" s="13" t="s">
-        <v>397</v>
-      </c>
-      <c r="C7" s="13" t="s">
+      <c r="B7" s="5" t="s">
+        <v>382</v>
+      </c>
+      <c r="C7" s="5" t="s">
         <v>314</v>
       </c>
-      <c r="D7" s="13" t="s">
+      <c r="D7" s="5" t="s">
         <v>315</v>
       </c>
-      <c r="E7" s="13" t="s">
+      <c r="E7" s="5" t="s">
         <v>316</v>
       </c>
-      <c r="F7" s="13" t="s">
+      <c r="F7" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="G7" s="13" t="s">
+      <c r="G7" s="5" t="s">
         <v>317</v>
       </c>
-      <c r="H7" s="13" t="s">
+      <c r="H7" s="5" t="s">
         <v>318</v>
       </c>
-      <c r="I7" s="13" t="s">
+      <c r="I7" s="5" t="s">
         <v>319</v>
       </c>
-      <c r="J7" s="13"/>
-      <c r="K7" s="13"/>
+      <c r="J7" s="5" t="s">
+        <v>424</v>
+      </c>
+      <c r="K7" s="5" t="s">
+        <v>348</v>
+      </c>
     </row>
     <row r="8" spans="1:11" ht="51.75" customHeight="1" x14ac:dyDescent="0.45"/>
     <row r="9" spans="1:11" ht="51.75" customHeight="1" x14ac:dyDescent="0.45"/>
   </sheetData>
+  <conditionalFormatting sqref="K2:K7">
+    <cfRule type="containsText" dxfId="6" priority="1" operator="containsText" text="Pass">
+      <formula>NOT(ISERROR(SEARCH("Pass",K2)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" sqref="K2:K7" xr:uid="{00000000-0002-0000-0A00-000000000000}">
+    <dataValidation type="list" allowBlank="1" sqref="K2:K7" xr:uid="{1B914D53-1B5F-4245-89F9-0BE60197E5D6}">
       <formula1>"Pass,Fail,Blocked,Not Executed,In Progress"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -3152,232 +4149,285 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:L6"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="2" width="10" style="7" customWidth="1"/>
-    <col min="3" max="3" width="16" style="7" customWidth="1"/>
-    <col min="4" max="4" width="32" style="7" customWidth="1"/>
-    <col min="5" max="5" width="38" style="7" customWidth="1"/>
-    <col min="6" max="6" width="42" style="7" customWidth="1"/>
-    <col min="7" max="8" width="32" style="7" customWidth="1"/>
-    <col min="9" max="9" width="12" style="7" customWidth="1"/>
-    <col min="10" max="10" width="10" style="7" customWidth="1"/>
-    <col min="11" max="11" width="14" style="7" customWidth="1"/>
-    <col min="12" max="12" width="24" style="7" customWidth="1"/>
-    <col min="13" max="16384" width="8.6640625" style="7"/>
+    <col min="1" max="2" width="10" style="1" customWidth="1"/>
+    <col min="3" max="3" width="16" style="1" customWidth="1"/>
+    <col min="4" max="4" width="32" style="1" customWidth="1"/>
+    <col min="5" max="5" width="38" style="1" customWidth="1"/>
+    <col min="6" max="6" width="42" style="1" customWidth="1"/>
+    <col min="7" max="8" width="32" style="1" customWidth="1"/>
+    <col min="9" max="9" width="12" style="1" customWidth="1"/>
+    <col min="10" max="10" width="10" style="1" customWidth="1"/>
+    <col min="11" max="11" width="14" style="1" customWidth="1"/>
+    <col min="12" max="12" width="24.265625" style="1" customWidth="1"/>
+    <col min="13" max="16384" width="8.6640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="25.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="7" t="s">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1" s="1" t="s">
         <v>320</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="1" t="s">
         <v>321</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C1" s="1" t="s">
         <v>322</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="D1" s="1" t="s">
         <v>323</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="E1" s="1" t="s">
         <v>324</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="F1" s="1" t="s">
         <v>325</v>
       </c>
-      <c r="G1" s="7" t="s">
+      <c r="G1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="H1" s="7" t="s">
+      <c r="H1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="I1" s="7" t="s">
+      <c r="I1" s="1" t="s">
         <v>326</v>
       </c>
-      <c r="J1" s="7" t="s">
+      <c r="J1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="K1" s="7" t="s">
+      <c r="K1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="L1" s="7" t="s">
+      <c r="L1" s="1" t="s">
         <v>327</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="51" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="13" t="s">
+    <row r="2" spans="1:12" ht="57" x14ac:dyDescent="0.45">
+      <c r="A2" s="5" t="s">
         <v>328</v>
       </c>
-      <c r="B2" s="13" t="s">
-        <v>329</v>
-      </c>
-      <c r="C2" s="13" t="s">
+      <c r="B2" s="5" t="s">
+        <v>389</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>362</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>390</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>391</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>392</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>393</v>
+      </c>
+      <c r="H2" s="5" t="s">
+        <v>415</v>
+      </c>
+      <c r="I2" s="5" t="s">
+        <v>352</v>
+      </c>
+      <c r="J2" s="5" t="s">
+        <v>352</v>
+      </c>
+      <c r="K2" s="5" t="s">
+        <v>331</v>
+      </c>
+      <c r="L2" s="5"/>
+    </row>
+    <row r="3" spans="1:12" ht="57" x14ac:dyDescent="0.45">
+      <c r="A3" s="5" t="s">
+        <v>332</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>394</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>362</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>395</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>396</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>397</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>398</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>399</v>
+      </c>
+      <c r="I3" s="5" t="s">
+        <v>352</v>
+      </c>
+      <c r="J3" s="5" t="s">
+        <v>352</v>
+      </c>
+      <c r="K3" s="5" t="s">
+        <v>331</v>
+      </c>
+      <c r="L3" s="5"/>
+    </row>
+    <row r="4" spans="1:12" ht="57" x14ac:dyDescent="0.45">
+      <c r="A4" s="5" t="s">
+        <v>333</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>400</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>364</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>401</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>402</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>403</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>404</v>
+      </c>
+      <c r="H4" s="5" t="s">
+        <v>405</v>
+      </c>
+      <c r="I4" s="5" t="s">
+        <v>350</v>
+      </c>
+      <c r="J4" s="5" t="s">
+        <v>350</v>
+      </c>
+      <c r="K4" s="5" t="s">
+        <v>331</v>
+      </c>
+      <c r="L4" s="5"/>
+    </row>
+    <row r="5" spans="1:12" ht="57" x14ac:dyDescent="0.45">
+      <c r="A5" s="5" t="s">
+        <v>334</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>406</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>358</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>407</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>408</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>416</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>417</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>418</v>
+      </c>
+      <c r="I5" s="5" t="s">
         <v>330</v>
       </c>
-      <c r="D2" s="13" t="s">
+      <c r="J5" s="5" t="s">
+        <v>350</v>
+      </c>
+      <c r="K5" s="5" t="s">
         <v>331</v>
       </c>
-      <c r="E2" s="13" t="s">
-        <v>332</v>
-      </c>
-      <c r="F2" s="13" t="s">
-        <v>333</v>
-      </c>
-      <c r="G2" s="13" t="s">
-        <v>334</v>
-      </c>
-      <c r="H2" s="13" t="s">
+      <c r="L5" s="5"/>
+    </row>
+    <row r="6" spans="1:12" ht="57" x14ac:dyDescent="0.45">
+      <c r="A6" s="5" t="s">
         <v>335</v>
       </c>
-      <c r="I2" s="13" t="s">
-        <v>336</v>
-      </c>
-      <c r="J2" s="13" t="s">
-        <v>336</v>
-      </c>
-      <c r="K2" s="13" t="s">
-        <v>337</v>
-      </c>
-      <c r="L2" s="13" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A3" s="13" t="s">
-        <v>339</v>
-      </c>
-      <c r="B3" s="13"/>
-      <c r="C3" s="13"/>
-      <c r="D3" s="13"/>
-      <c r="E3" s="13"/>
-      <c r="F3" s="13"/>
-      <c r="G3" s="13"/>
-      <c r="H3" s="13"/>
-      <c r="I3" s="13"/>
-      <c r="J3" s="13"/>
-      <c r="K3" s="13"/>
-      <c r="L3" s="13"/>
-    </row>
-    <row r="4" spans="1:12" ht="51.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A4" s="13" t="s">
-        <v>340</v>
-      </c>
-      <c r="B4" s="13"/>
-      <c r="C4" s="13"/>
-      <c r="D4" s="13"/>
-      <c r="E4" s="13"/>
-      <c r="F4" s="13"/>
-      <c r="G4" s="13"/>
-      <c r="H4" s="13"/>
-      <c r="I4" s="13"/>
-      <c r="J4" s="13"/>
-      <c r="K4" s="13"/>
-      <c r="L4" s="13"/>
-    </row>
-    <row r="5" spans="1:12" ht="51.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A5" s="13" t="s">
-        <v>341</v>
-      </c>
-      <c r="B5" s="13"/>
-      <c r="C5" s="13"/>
-      <c r="D5" s="13"/>
-      <c r="E5" s="13"/>
-      <c r="F5" s="13"/>
-      <c r="G5" s="13"/>
-      <c r="H5" s="13"/>
-      <c r="I5" s="13"/>
-      <c r="J5" s="13"/>
-      <c r="K5" s="13"/>
-      <c r="L5" s="13"/>
-    </row>
-    <row r="6" spans="1:12" ht="51.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A6" s="13" t="s">
-        <v>342</v>
-      </c>
-      <c r="B6" s="13"/>
-      <c r="C6" s="13"/>
-      <c r="D6" s="13"/>
-      <c r="E6" s="13"/>
-      <c r="F6" s="13"/>
-      <c r="G6" s="13"/>
-      <c r="H6" s="13"/>
-      <c r="I6" s="13"/>
-      <c r="J6" s="13"/>
-      <c r="K6" s="13"/>
-      <c r="L6" s="13"/>
-    </row>
-    <row r="7" spans="1:12" ht="51.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A7" s="13" t="s">
-        <v>343</v>
-      </c>
-      <c r="B7" s="13"/>
-      <c r="C7" s="13"/>
-      <c r="D7" s="13"/>
-      <c r="E7" s="13"/>
-      <c r="F7" s="13"/>
-      <c r="G7" s="13"/>
-      <c r="H7" s="13"/>
-      <c r="I7" s="13"/>
-      <c r="J7" s="13"/>
-      <c r="K7" s="13"/>
-      <c r="L7" s="13"/>
-    </row>
-    <row r="8" spans="1:12" ht="51.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A8" s="13" t="s">
-        <v>344</v>
-      </c>
-      <c r="B8" s="13"/>
-      <c r="C8" s="13"/>
-      <c r="D8" s="13"/>
-      <c r="E8" s="13"/>
-      <c r="F8" s="13"/>
-      <c r="G8" s="13"/>
-      <c r="H8" s="13"/>
-      <c r="I8" s="13"/>
-      <c r="J8" s="13"/>
-      <c r="K8" s="13"/>
-      <c r="L8" s="13"/>
-    </row>
-    <row r="9" spans="1:12" ht="51.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A9" s="13" t="s">
-        <v>345</v>
-      </c>
-      <c r="B9" s="13"/>
-      <c r="C9" s="13"/>
-      <c r="D9" s="13"/>
-      <c r="E9" s="13"/>
-      <c r="F9" s="13"/>
-      <c r="G9" s="13"/>
-      <c r="H9" s="13"/>
-      <c r="I9" s="13"/>
-      <c r="J9" s="13"/>
-      <c r="K9" s="13"/>
-      <c r="L9" s="13"/>
-    </row>
-    <row r="10" spans="1:12" ht="51.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="11" spans="1:12" ht="51.75" customHeight="1" x14ac:dyDescent="0.45"/>
+      <c r="B6" s="5" t="s">
+        <v>409</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>359</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>410</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>411</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>412</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>413</v>
+      </c>
+      <c r="H6" s="5" t="s">
+        <v>414</v>
+      </c>
+      <c r="I6" s="5" t="s">
+        <v>350</v>
+      </c>
+      <c r="J6" s="5" t="s">
+        <v>330</v>
+      </c>
+      <c r="K6" s="5" t="s">
+        <v>331</v>
+      </c>
+      <c r="L6" s="5"/>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="I2">
-    <cfRule type="containsText" dxfId="58" priority="1" operator="containsText" text="High">
-      <formula>NOT(ISERROR(SEARCH("High",I2)))</formula>
+  <phoneticPr fontId="6" type="noConversion"/>
+  <conditionalFormatting sqref="I2:I3">
+    <cfRule type="containsText" dxfId="5" priority="2" operator="containsText" text="Low">
+      <formula>NOT(ISERROR(SEARCH("Low",I2)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I3">
+    <cfRule type="containsText" dxfId="4" priority="7" operator="containsText" text="Low">
+      <formula>NOT(ISERROR(SEARCH("Low",I3)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I4">
+    <cfRule type="containsText" dxfId="3" priority="6" operator="containsText" text="Medium">
+      <formula>NOT(ISERROR(SEARCH("Medium",I4)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I5">
+    <cfRule type="containsText" dxfId="2" priority="1" operator="containsText" text="High">
+      <formula>NOT(ISERROR(SEARCH("High",I5)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="1" priority="3" operator="containsText" text="Low">
+      <formula>NOT(ISERROR(SEARCH("Low",I5)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I6">
+    <cfRule type="containsText" dxfId="0" priority="5" operator="containsText" text="Medium">
+      <formula>NOT(ISERROR(SEARCH("Medium",I6)))</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" sqref="I2:I18" xr:uid="{00000000-0002-0000-0B00-000000000000}">
+    <dataValidation type="list" allowBlank="1" sqref="I2:I15" xr:uid="{00000000-0002-0000-0B00-000000000000}">
       <formula1>"Critical,High,Medium,Low"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="K2:K18" xr:uid="{00000000-0002-0000-0B00-000001000000}">
+    <dataValidation type="list" allowBlank="1" sqref="K2:K15" xr:uid="{00000000-0002-0000-0B00-000001000000}">
       <formula1>"Open,In Progress,Fixed,Retest,Closed,Won't Fix"</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+  <drawing r:id="rId2"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId3"/>
   </tableParts>
 </worksheet>
 </file>
@@ -3387,337 +4437,509 @@
   <dimension ref="A1:O33"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="28" style="13" customWidth="1"/>
-    <col min="2" max="2" width="12" style="13" customWidth="1"/>
-    <col min="3" max="5" width="10" style="13" customWidth="1"/>
-    <col min="6" max="6" width="14" style="13" customWidth="1"/>
-    <col min="7" max="7" width="12" style="13" customWidth="1"/>
-    <col min="8" max="16384" width="8.6640625" style="13"/>
+    <col min="1" max="1" width="28" style="5" customWidth="1"/>
+    <col min="2" max="2" width="12" style="5" customWidth="1"/>
+    <col min="3" max="4" width="10" style="5" customWidth="1"/>
+    <col min="5" max="5" width="24.265625" style="5" customWidth="1"/>
+    <col min="6" max="6" width="14" style="5" customWidth="1"/>
+    <col min="7" max="7" width="12" style="5" customWidth="1"/>
+    <col min="8" max="16384" width="8.6640625" style="5"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="25.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="16" t="s">
-        <v>346</v>
-      </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
-      <c r="H1" s="16"/>
-      <c r="I1" s="16"/>
-      <c r="J1" s="16"/>
-      <c r="K1" s="16"/>
-      <c r="L1" s="16"/>
-      <c r="M1" s="16"/>
-      <c r="N1" s="16"/>
-      <c r="O1" s="16"/>
+      <c r="A1" s="23" t="s">
+        <v>388</v>
+      </c>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="23"/>
+      <c r="H1" s="23"/>
+      <c r="I1" s="23"/>
+      <c r="J1" s="23"/>
+      <c r="K1" s="23"/>
+      <c r="L1" s="23"/>
+      <c r="M1" s="23"/>
+      <c r="N1" s="23"/>
+      <c r="O1" s="23"/>
     </row>
     <row r="2" spans="1:15" ht="14.65" thickBot="1" x14ac:dyDescent="0.5"/>
     <row r="3" spans="1:15" ht="21.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A3" s="15" t="s">
-        <v>399</v>
-      </c>
-      <c r="B3" s="15"/>
-      <c r="C3" s="15"/>
-      <c r="D3" s="15"/>
-      <c r="E3" s="15"/>
-      <c r="F3" s="15"/>
-      <c r="G3" s="15"/>
+      <c r="A3" s="26" t="s">
+        <v>384</v>
+      </c>
+      <c r="B3" s="26"/>
+      <c r="C3" s="26"/>
+      <c r="D3" s="26"/>
+      <c r="E3" s="26"/>
+      <c r="F3" s="26"/>
+      <c r="G3" s="26"/>
     </row>
     <row r="4" spans="1:15" ht="18" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A4" s="10" t="s">
+      <c r="A4" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="11" t="s">
-        <v>347</v>
-      </c>
-      <c r="C4" s="11"/>
-      <c r="D4" s="11"/>
-      <c r="E4" s="11"/>
-      <c r="F4" s="11"/>
-      <c r="G4" s="11"/>
+      <c r="B4" s="15" t="s">
+        <v>336</v>
+      </c>
+      <c r="C4" s="15"/>
+      <c r="D4" s="15"/>
+      <c r="E4" s="15"/>
+      <c r="F4" s="15"/>
+      <c r="G4" s="15"/>
     </row>
     <row r="5" spans="1:15" ht="18" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A5" s="10" t="s">
-        <v>348</v>
-      </c>
-      <c r="B5" s="11" t="s">
-        <v>349</v>
-      </c>
-      <c r="C5" s="11"/>
-      <c r="D5" s="11"/>
-      <c r="E5" s="11"/>
-      <c r="F5" s="11"/>
-      <c r="G5" s="11"/>
+      <c r="A5" s="4" t="s">
+        <v>337</v>
+      </c>
+      <c r="B5" s="15" t="s">
+        <v>338</v>
+      </c>
+      <c r="C5" s="15"/>
+      <c r="D5" s="15"/>
+      <c r="E5" s="15"/>
+      <c r="F5" s="15"/>
+      <c r="G5" s="15"/>
     </row>
     <row r="6" spans="1:15" ht="18" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A6" s="10" t="s">
-        <v>350</v>
-      </c>
-      <c r="B6" s="11" t="s">
-        <v>351</v>
-      </c>
-      <c r="C6" s="11"/>
-      <c r="D6" s="11"/>
-      <c r="E6" s="11"/>
-      <c r="F6" s="11"/>
-      <c r="G6" s="11"/>
+      <c r="A6" s="4" t="s">
+        <v>339</v>
+      </c>
+      <c r="B6" s="15" t="s">
+        <v>340</v>
+      </c>
+      <c r="C6" s="15"/>
+      <c r="D6" s="15"/>
+      <c r="E6" s="15"/>
+      <c r="F6" s="15"/>
+      <c r="G6" s="15"/>
     </row>
     <row r="7" spans="1:15" ht="18" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A7" s="10" t="s">
-        <v>352</v>
-      </c>
-      <c r="B7" s="11" t="s">
-        <v>353</v>
-      </c>
-      <c r="C7" s="11"/>
-      <c r="D7" s="11"/>
-      <c r="E7" s="11"/>
-      <c r="F7" s="11"/>
-      <c r="G7" s="11"/>
+      <c r="A7" s="4" t="s">
+        <v>466</v>
+      </c>
+      <c r="B7" s="15" t="s">
+        <v>465</v>
+      </c>
+      <c r="C7" s="15"/>
+      <c r="D7" s="15"/>
+      <c r="E7" s="15"/>
+      <c r="F7" s="15"/>
+      <c r="G7" s="15"/>
     </row>
     <row r="8" spans="1:15" ht="18" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A8" s="10" t="s">
-        <v>354</v>
-      </c>
-      <c r="B8" s="11" t="s">
-        <v>382</v>
-      </c>
-      <c r="C8" s="11"/>
-      <c r="D8" s="11"/>
-      <c r="E8" s="11"/>
-      <c r="F8" s="11"/>
-      <c r="G8" s="11"/>
+      <c r="A8" s="4" t="s">
+        <v>341</v>
+      </c>
+      <c r="B8" s="15" t="s">
+        <v>367</v>
+      </c>
+      <c r="C8" s="15"/>
+      <c r="D8" s="15"/>
+      <c r="E8" s="15"/>
+      <c r="F8" s="15"/>
+      <c r="G8" s="15"/>
     </row>
     <row r="9" spans="1:15" ht="18" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A9" s="10" t="s">
-        <v>355</v>
-      </c>
-      <c r="B9" s="12">
+      <c r="A9" s="4" t="s">
+        <v>342</v>
+      </c>
+      <c r="B9" s="16">
         <v>46163</v>
       </c>
-      <c r="C9" s="11"/>
-      <c r="D9" s="11"/>
-      <c r="E9" s="11"/>
-      <c r="F9" s="11"/>
-      <c r="G9" s="11"/>
+      <c r="C9" s="15"/>
+      <c r="D9" s="15"/>
+      <c r="E9" s="15"/>
+      <c r="F9" s="15"/>
+      <c r="G9" s="15"/>
     </row>
     <row r="10" spans="1:15" ht="18" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A10" s="10" t="s">
-        <v>356</v>
-      </c>
-      <c r="B10" s="11"/>
-      <c r="C10" s="11"/>
-      <c r="D10" s="11"/>
-      <c r="E10" s="11"/>
-      <c r="F10" s="11"/>
-      <c r="G10" s="11"/>
+      <c r="A10" s="4" t="s">
+        <v>343</v>
+      </c>
+      <c r="B10" s="16"/>
+      <c r="C10" s="15"/>
+      <c r="D10" s="15"/>
+      <c r="E10" s="15"/>
+      <c r="F10" s="15"/>
+      <c r="G10" s="15"/>
     </row>
     <row r="11" spans="1:15" ht="18" customHeight="1" thickTop="1" x14ac:dyDescent="0.45"/>
     <row r="12" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="A12" s="2" t="s">
-        <v>400</v>
-      </c>
-      <c r="B12" s="2"/>
-      <c r="C12" s="2"/>
-      <c r="E12" s="1" t="s">
-        <v>357</v>
-      </c>
-      <c r="F12" s="1"/>
-      <c r="G12" s="1"/>
+      <c r="A12" s="24" t="s">
+        <v>385</v>
+      </c>
+      <c r="B12" s="24"/>
+      <c r="C12" s="24"/>
+      <c r="E12" s="22" t="s">
+        <v>387</v>
+      </c>
+      <c r="F12" s="22"/>
+      <c r="G12" s="22"/>
     </row>
     <row r="13" spans="1:15" ht="21.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A13" s="18" t="s">
-        <v>358</v>
-      </c>
-      <c r="B13" s="3">
+      <c r="A13" s="11" t="s">
+        <v>344</v>
+      </c>
+      <c r="B13" s="17">
         <v>56</v>
       </c>
-      <c r="E13" s="18" t="s">
-        <v>359</v>
-      </c>
-      <c r="F13" s="3"/>
+      <c r="C13" s="17"/>
+      <c r="E13" s="11" t="s">
+        <v>345</v>
+      </c>
+      <c r="F13" s="17">
+        <v>5</v>
+      </c>
+      <c r="G13" s="17"/>
+      <c r="I13" s="5" t="s">
+        <v>467</v>
+      </c>
     </row>
     <row r="14" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A14" s="18" t="s">
-        <v>360</v>
-      </c>
-      <c r="B14" s="3"/>
-      <c r="E14" s="18" t="s">
-        <v>361</v>
-      </c>
-      <c r="F14" s="4"/>
+      <c r="A14" s="11" t="s">
+        <v>346</v>
+      </c>
+      <c r="B14" s="17">
+        <v>50</v>
+      </c>
+      <c r="C14" s="17"/>
+      <c r="E14" s="11" t="s">
+        <v>347</v>
+      </c>
+      <c r="F14" s="19">
+        <v>0</v>
+      </c>
+      <c r="G14" s="19"/>
     </row>
     <row r="15" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A15" s="18" t="s">
-        <v>362</v>
-      </c>
-      <c r="B15" s="5"/>
-      <c r="E15" s="18" t="s">
-        <v>336</v>
-      </c>
-      <c r="F15" s="4"/>
+      <c r="A15" s="11" t="s">
+        <v>348</v>
+      </c>
+      <c r="B15" s="21">
+        <v>49</v>
+      </c>
+      <c r="C15" s="21"/>
+      <c r="E15" s="11" t="s">
+        <v>330</v>
+      </c>
+      <c r="F15" s="19">
+        <v>1</v>
+      </c>
+      <c r="G15" s="19"/>
     </row>
     <row r="16" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A16" s="18" t="s">
-        <v>363</v>
-      </c>
-      <c r="B16" s="4"/>
-      <c r="E16" s="18" t="s">
-        <v>364</v>
-      </c>
-      <c r="F16" s="6"/>
+      <c r="A16" s="11" t="s">
+        <v>349</v>
+      </c>
+      <c r="B16" s="19">
+        <v>1</v>
+      </c>
+      <c r="C16" s="19"/>
+      <c r="E16" s="11" t="s">
+        <v>350</v>
+      </c>
+      <c r="F16" s="20">
+        <v>2</v>
+      </c>
+      <c r="G16" s="20"/>
     </row>
     <row r="17" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A17" s="18" t="s">
-        <v>365</v>
-      </c>
-      <c r="B17" s="3"/>
-      <c r="E17" s="18" t="s">
-        <v>366</v>
-      </c>
-      <c r="F17" s="5"/>
+      <c r="A17" s="11" t="s">
+        <v>351</v>
+      </c>
+      <c r="B17" s="17">
+        <v>0</v>
+      </c>
+      <c r="C17" s="17"/>
+      <c r="E17" s="11" t="s">
+        <v>352</v>
+      </c>
+      <c r="F17" s="21">
+        <v>2</v>
+      </c>
+      <c r="G17" s="21"/>
     </row>
     <row r="18" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A18" s="18" t="s">
-        <v>367</v>
-      </c>
-      <c r="B18" s="3"/>
-      <c r="E18" s="18" t="s">
-        <v>337</v>
-      </c>
-      <c r="F18" s="3"/>
+      <c r="A18" s="11" t="s">
+        <v>353</v>
+      </c>
+      <c r="B18" s="17">
+        <v>0</v>
+      </c>
+      <c r="C18" s="17"/>
+      <c r="E18" s="11" t="s">
+        <v>331</v>
+      </c>
+      <c r="F18" s="17">
+        <v>5</v>
+      </c>
+      <c r="G18" s="17"/>
     </row>
     <row r="19" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A19" s="18" t="s">
-        <v>368</v>
-      </c>
-      <c r="B19" s="3"/>
-      <c r="E19" s="18" t="s">
-        <v>369</v>
-      </c>
-      <c r="F19" s="3"/>
+      <c r="A19" s="11" t="s">
+        <v>354</v>
+      </c>
+      <c r="B19" s="18">
+        <v>0.98</v>
+      </c>
+      <c r="C19" s="18"/>
+      <c r="E19" s="11" t="s">
+        <v>355</v>
+      </c>
+      <c r="F19" s="17">
+        <v>0</v>
+      </c>
+      <c r="G19" s="17"/>
     </row>
     <row r="20" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.45"/>
     <row r="21" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A21" s="17" t="s">
-        <v>401</v>
-      </c>
-      <c r="B21" s="17"/>
-      <c r="C21" s="17"/>
-      <c r="D21" s="17"/>
-      <c r="E21" s="17"/>
-      <c r="F21" s="17"/>
-      <c r="G21" s="17"/>
+      <c r="A21" s="25" t="s">
+        <v>386</v>
+      </c>
+      <c r="B21" s="25"/>
+      <c r="C21" s="25"/>
+      <c r="D21" s="25"/>
+      <c r="E21" s="25"/>
+      <c r="F21" s="25"/>
+      <c r="G21" s="25"/>
     </row>
     <row r="22" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A22" s="13" t="s">
+      <c r="A22" s="5" t="s">
         <v>322</v>
       </c>
-      <c r="B22" s="13" t="s">
-        <v>370</v>
-      </c>
-      <c r="C22" s="13" t="s">
+      <c r="B22" s="5" t="s">
+        <v>356</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>348</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>349</v>
+      </c>
+      <c r="E22" s="5" t="s">
+        <v>351</v>
+      </c>
+      <c r="F22" s="5" t="s">
+        <v>353</v>
+      </c>
+      <c r="G22" s="5" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A23" s="5" t="s">
+        <v>358</v>
+      </c>
+      <c r="B23" s="5">
+        <v>6</v>
+      </c>
+      <c r="C23" s="5">
+        <v>6</v>
+      </c>
+      <c r="D23" s="5">
+        <v>0</v>
+      </c>
+      <c r="E23" s="5">
+        <v>0</v>
+      </c>
+      <c r="F23" s="5">
+        <v>0</v>
+      </c>
+      <c r="G23" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A24" s="5" t="s">
+        <v>329</v>
+      </c>
+      <c r="B24" s="5">
+        <v>9</v>
+      </c>
+      <c r="C24" s="5">
+        <v>9</v>
+      </c>
+      <c r="D24" s="5">
+        <v>0</v>
+      </c>
+      <c r="E24" s="5">
+        <v>0</v>
+      </c>
+      <c r="F24" s="5">
+        <v>0</v>
+      </c>
+      <c r="G24" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A25" s="5" t="s">
+        <v>359</v>
+      </c>
+      <c r="B25" s="5">
+        <v>3</v>
+      </c>
+      <c r="C25" s="5">
+        <v>3</v>
+      </c>
+      <c r="D25" s="5">
+        <v>0</v>
+      </c>
+      <c r="E25" s="5">
+        <v>0</v>
+      </c>
+      <c r="F25" s="5">
+        <v>0</v>
+      </c>
+      <c r="G25" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A26" s="5" t="s">
+        <v>360</v>
+      </c>
+      <c r="B26" s="5">
+        <v>4</v>
+      </c>
+      <c r="C26" s="5">
+        <v>4</v>
+      </c>
+      <c r="D26" s="5">
+        <v>0</v>
+      </c>
+      <c r="E26" s="5">
+        <v>0</v>
+      </c>
+      <c r="F26" s="5">
+        <v>0</v>
+      </c>
+      <c r="G26" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A27" s="5" t="s">
+        <v>361</v>
+      </c>
+      <c r="B27" s="5">
+        <v>5</v>
+      </c>
+      <c r="C27" s="5">
+        <v>5</v>
+      </c>
+      <c r="D27" s="5">
+        <v>0</v>
+      </c>
+      <c r="E27" s="5">
+        <v>0</v>
+      </c>
+      <c r="F27" s="5">
+        <v>0</v>
+      </c>
+      <c r="G27" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A28" s="5" t="s">
         <v>362</v>
       </c>
-      <c r="D22" s="13" t="s">
+      <c r="B28" s="5">
+        <v>5</v>
+      </c>
+      <c r="C28" s="5">
+        <v>4</v>
+      </c>
+      <c r="D28" s="5">
+        <v>1</v>
+      </c>
+      <c r="E28" s="5">
+        <v>0</v>
+      </c>
+      <c r="F28" s="5">
+        <v>0</v>
+      </c>
+      <c r="G28" s="12">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A29" s="5" t="s">
         <v>363</v>
       </c>
-      <c r="E22" s="13" t="s">
+      <c r="B29" s="5">
+        <v>7</v>
+      </c>
+      <c r="C29" s="5">
+        <v>7</v>
+      </c>
+      <c r="D29" s="5">
+        <v>0</v>
+      </c>
+      <c r="E29" s="5">
+        <v>0</v>
+      </c>
+      <c r="F29" s="5">
+        <v>0</v>
+      </c>
+      <c r="G29" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A30" s="5" t="s">
+        <v>364</v>
+      </c>
+      <c r="B30" s="5">
+        <v>5</v>
+      </c>
+      <c r="C30" s="5">
+        <v>5</v>
+      </c>
+      <c r="D30" s="5">
+        <v>0</v>
+      </c>
+      <c r="E30" s="5">
+        <v>0</v>
+      </c>
+      <c r="F30" s="5">
+        <v>0</v>
+      </c>
+      <c r="G30" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A31" s="5" t="s">
         <v>365</v>
       </c>
-      <c r="F22" s="13" t="s">
-        <v>367</v>
-      </c>
-      <c r="G22" s="13" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A23" s="13" t="s">
-        <v>372</v>
-      </c>
-      <c r="B23" s="13">
+      <c r="B31" s="5">
         <v>6</v>
       </c>
-    </row>
-    <row r="24" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A24" s="13" t="s">
-        <v>330</v>
-      </c>
-      <c r="B24" s="13">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A25" s="13" t="s">
-        <v>373</v>
-      </c>
-      <c r="B25" s="13">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A26" s="13" t="s">
-        <v>374</v>
-      </c>
-      <c r="B26" s="13">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A27" s="13" t="s">
-        <v>375</v>
-      </c>
-      <c r="B27" s="13">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A28" s="13" t="s">
-        <v>376</v>
-      </c>
-      <c r="B28" s="13">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A29" s="13" t="s">
-        <v>377</v>
-      </c>
-      <c r="B29" s="13">
+      <c r="C31" s="5">
         <v>6</v>
       </c>
-    </row>
-    <row r="30" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A30" s="13" t="s">
-        <v>378</v>
-      </c>
-      <c r="B30" s="13">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A31" s="13" t="s">
-        <v>379</v>
-      </c>
-      <c r="B31" s="13">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A32" s="13" t="s">
-        <v>380</v>
-      </c>
-      <c r="B32" s="13">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="33" s="13" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.45"/>
+      <c r="D31" s="5">
+        <v>0</v>
+      </c>
+      <c r="E31" s="5">
+        <v>0</v>
+      </c>
+      <c r="F31" s="5">
+        <v>0</v>
+      </c>
+      <c r="G31" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="33" ht="18" customHeight="1" x14ac:dyDescent="0.45"/>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="26">
     <mergeCell ref="E12:G12"/>
     <mergeCell ref="A1:O1"/>
     <mergeCell ref="A12:C12"/>
@@ -3730,6 +4952,20 @@
     <mergeCell ref="A3:G3"/>
     <mergeCell ref="B4:G4"/>
     <mergeCell ref="B5:G5"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="F14:G14"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="F16:G16"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F18:G18"/>
+    <mergeCell ref="F19:G19"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -3758,229 +4994,258 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="D1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="E1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="F1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="G1" s="7" t="s">
+      <c r="G1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="H1" s="7" t="s">
+      <c r="H1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="I1" s="7" t="s">
+      <c r="I1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="J1" s="7" t="s">
+      <c r="J1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="K1" s="7" t="s">
+      <c r="K1" s="1" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="51.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="13" t="s">
+      <c r="A2" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="B2" s="13" t="s">
+      <c r="B2" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="C2" s="13" t="s">
+      <c r="C2" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="D2" s="13" t="s">
+      <c r="D2" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="E2" s="13" t="s">
+      <c r="E2" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="F2" s="13" t="s">
+      <c r="F2" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="G2" s="13" t="s">
+      <c r="G2" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="H2" s="13" t="s">
+      <c r="H2" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="I2" s="13" t="s">
+      <c r="I2" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="J2" s="13"/>
-      <c r="K2" s="13"/>
+      <c r="J2" s="5" t="s">
+        <v>459</v>
+      </c>
+      <c r="K2" s="5" t="s">
+        <v>348</v>
+      </c>
     </row>
     <row r="3" spans="1:11" ht="51.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A3" s="13" t="s">
+      <c r="A3" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B3" s="13" t="s">
+      <c r="B3" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="C3" s="13" t="s">
+      <c r="C3" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="D3" s="13" t="s">
+      <c r="D3" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="E3" s="13" t="s">
+      <c r="E3" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="F3" s="13" t="s">
+      <c r="F3" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="G3" s="13" t="s">
+      <c r="G3" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="H3" s="13" t="s">
+      <c r="H3" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="I3" s="13" t="s">
+      <c r="I3" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="J3" s="13"/>
-      <c r="K3" s="13"/>
+      <c r="J3" s="5" t="s">
+        <v>460</v>
+      </c>
+      <c r="K3" s="5" t="s">
+        <v>348</v>
+      </c>
     </row>
     <row r="4" spans="1:11" ht="51.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A4" s="13" t="s">
+      <c r="A4" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="B4" s="13" t="s">
+      <c r="B4" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="C4" s="13" t="s">
+      <c r="C4" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="D4" s="13" t="s">
+      <c r="D4" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="E4" s="13" t="s">
+      <c r="E4" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="F4" s="13" t="s">
+      <c r="F4" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="G4" s="13" t="s">
+      <c r="G4" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="H4" s="13" t="s">
+      <c r="H4" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="I4" s="13" t="s">
+      <c r="I4" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="J4" s="13"/>
-      <c r="K4" s="13"/>
+      <c r="J4" s="5" t="s">
+        <v>461</v>
+      </c>
+      <c r="K4" s="5" t="s">
+        <v>348</v>
+      </c>
     </row>
     <row r="5" spans="1:11" ht="51.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A5" s="13" t="s">
+      <c r="A5" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="B5" s="13" t="s">
+      <c r="B5" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="C5" s="13" t="s">
+      <c r="C5" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="D5" s="13" t="s">
+      <c r="D5" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="E5" s="13" t="s">
+      <c r="E5" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="F5" s="13" t="s">
+      <c r="F5" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="G5" s="13" t="s">
+      <c r="G5" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="H5" s="13" t="s">
+      <c r="H5" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="I5" s="13" t="s">
+      <c r="I5" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="J5" s="13"/>
-      <c r="K5" s="13"/>
+      <c r="J5" s="5" t="s">
+        <v>462</v>
+      </c>
+      <c r="K5" s="5" t="s">
+        <v>348</v>
+      </c>
     </row>
     <row r="6" spans="1:11" ht="51.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A6" s="13" t="s">
+      <c r="A6" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="B6" s="13" t="s">
+      <c r="B6" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="C6" s="13" t="s">
+      <c r="C6" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="D6" s="13" t="s">
+      <c r="D6" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="E6" s="13" t="s">
+      <c r="E6" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="F6" s="13" t="s">
+      <c r="F6" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="G6" s="13" t="s">
+      <c r="G6" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="H6" s="13" t="s">
+      <c r="H6" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="I6" s="13" t="s">
+      <c r="I6" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="J6" s="13"/>
-      <c r="K6" s="13"/>
+      <c r="J6" s="5" t="s">
+        <v>463</v>
+      </c>
+      <c r="K6" s="5" t="s">
+        <v>348</v>
+      </c>
     </row>
     <row r="7" spans="1:11" ht="51.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A7" s="13" t="s">
+      <c r="A7" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="B7" s="13" t="s">
+      <c r="B7" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="C7" s="13" t="s">
+      <c r="C7" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="D7" s="13" t="s">
+      <c r="D7" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="E7" s="13" t="s">
+      <c r="E7" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="F7" s="13" t="s">
+      <c r="F7" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="G7" s="13" t="s">
+      <c r="G7" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="H7" s="13" t="s">
+      <c r="H7" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="I7" s="22" t="s">
-        <v>389</v>
-      </c>
-      <c r="J7" s="13"/>
-      <c r="K7" s="13"/>
+      <c r="I7" s="10" t="s">
+        <v>374</v>
+      </c>
+      <c r="J7" s="5" t="s">
+        <v>464</v>
+      </c>
+      <c r="K7" s="5" t="s">
+        <v>348</v>
+      </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="K2:K7">
+    <cfRule type="containsText" dxfId="16" priority="1" operator="containsText" text="Pass">
+      <formula>NOT(ISERROR(SEARCH("Pass",K2)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" sqref="K2:K7" xr:uid="{00000000-0002-0000-0100-000000000000}">
+    <dataValidation type="list" allowBlank="1" sqref="K2:K7" xr:uid="{281F972B-1C55-491C-99F6-3E97DE8D6C47}">
       <formula1>"Pass,Fail,Blocked,Not Executed,In Progress"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -4012,323 +5277,364 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="D1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="E1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="F1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="G1" s="7" t="s">
+      <c r="G1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="H1" s="7" t="s">
+      <c r="H1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="I1" s="7" t="s">
+      <c r="I1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="J1" s="7" t="s">
+      <c r="J1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="K1" s="7" t="s">
+      <c r="K1" s="1" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="13" t="s">
+      <c r="A2" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="B2" s="13" t="s">
-        <v>390</v>
-      </c>
-      <c r="C2" s="13" t="s">
+      <c r="B2" s="5" t="s">
+        <v>375</v>
+      </c>
+      <c r="C2" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="D2" s="13" t="s">
+      <c r="D2" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="E2" s="13" t="s">
+      <c r="E2" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="F2" s="13" t="s">
+      <c r="F2" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="G2" s="13" t="s">
+      <c r="G2" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="H2" s="13" t="s">
+      <c r="H2" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="I2" s="13" t="s">
+      <c r="I2" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="J2" s="13"/>
-      <c r="K2" s="13"/>
+      <c r="J2" s="5" t="s">
+        <v>454</v>
+      </c>
+      <c r="K2" s="5" t="s">
+        <v>348</v>
+      </c>
     </row>
     <row r="3" spans="1:11" ht="51.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A3" s="13" t="s">
+      <c r="A3" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B3" s="13" t="s">
-        <v>390</v>
-      </c>
-      <c r="C3" s="13" t="s">
+      <c r="B3" s="5" t="s">
+        <v>375</v>
+      </c>
+      <c r="C3" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="D3" s="13" t="s">
+      <c r="D3" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="E3" s="13" t="s">
+      <c r="E3" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="F3" s="13" t="s">
+      <c r="F3" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="G3" s="13" t="s">
+      <c r="G3" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="H3" s="13" t="s">
+      <c r="H3" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="I3" s="13" t="s">
+      <c r="I3" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="J3" s="13"/>
-      <c r="K3" s="13"/>
+      <c r="J3" s="5" t="s">
+        <v>455</v>
+      </c>
+      <c r="K3" s="5" t="s">
+        <v>348</v>
+      </c>
     </row>
     <row r="4" spans="1:11" ht="51.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A4" s="13" t="s">
+      <c r="A4" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="B4" s="13" t="s">
-        <v>390</v>
-      </c>
-      <c r="C4" s="13" t="s">
+      <c r="B4" s="5" t="s">
+        <v>375</v>
+      </c>
+      <c r="C4" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="D4" s="13" t="s">
+      <c r="D4" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="E4" s="13" t="s">
+      <c r="E4" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="F4" s="13" t="s">
+      <c r="F4" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="G4" s="13" t="s">
+      <c r="G4" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="H4" s="13" t="s">
+      <c r="H4" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="I4" s="13" t="s">
+      <c r="I4" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="J4" s="13"/>
-      <c r="K4" s="13"/>
+      <c r="J4" s="5" t="s">
+        <v>455</v>
+      </c>
+      <c r="K4" s="5" t="s">
+        <v>348</v>
+      </c>
     </row>
     <row r="5" spans="1:11" ht="51.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A5" s="13" t="s">
+      <c r="A5" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="B5" s="13" t="s">
-        <v>390</v>
-      </c>
-      <c r="C5" s="13" t="s">
+      <c r="B5" s="5" t="s">
+        <v>375</v>
+      </c>
+      <c r="C5" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="D5" s="13" t="s">
+      <c r="D5" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="E5" s="13" t="s">
+      <c r="E5" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="F5" s="13" t="s">
+      <c r="F5" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="G5" s="13" t="s">
+      <c r="G5" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="H5" s="13" t="s">
+      <c r="H5" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="I5" s="13" t="s">
+      <c r="I5" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="J5" s="13"/>
-      <c r="K5" s="13"/>
+      <c r="J5" s="5" t="s">
+        <v>455</v>
+      </c>
+      <c r="K5" s="5" t="s">
+        <v>348</v>
+      </c>
     </row>
     <row r="6" spans="1:11" ht="51.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A6" s="13" t="s">
+      <c r="A6" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="B6" s="13" t="s">
-        <v>390</v>
-      </c>
-      <c r="C6" s="13" t="s">
+      <c r="B6" s="5" t="s">
+        <v>375</v>
+      </c>
+      <c r="C6" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="D6" s="13" t="s">
+      <c r="D6" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="E6" s="13" t="s">
+      <c r="E6" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="F6" s="13" t="s">
+      <c r="F6" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="G6" s="13" t="s">
+      <c r="G6" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="H6" s="13" t="s">
+      <c r="H6" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="I6" s="13" t="s">
+      <c r="I6" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="J6" s="13"/>
-      <c r="K6" s="13"/>
+      <c r="J6" s="5" t="s">
+        <v>456</v>
+      </c>
+      <c r="K6" s="5" t="s">
+        <v>348</v>
+      </c>
     </row>
     <row r="7" spans="1:11" ht="51.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A7" s="13" t="s">
+      <c r="A7" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="B7" s="13" t="s">
-        <v>390</v>
-      </c>
-      <c r="C7" s="13" t="s">
+      <c r="B7" s="5" t="s">
+        <v>375</v>
+      </c>
+      <c r="C7" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="D7" s="13" t="s">
+      <c r="D7" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="E7" s="13" t="s">
+      <c r="E7" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="F7" s="13" t="s">
+      <c r="F7" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="G7" s="13" t="s">
+      <c r="G7" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="H7" s="13" t="s">
+      <c r="H7" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="I7" s="13" t="s">
+      <c r="I7" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="J7" s="13"/>
-      <c r="K7" s="13"/>
+      <c r="J7" s="5" t="s">
+        <v>456</v>
+      </c>
+      <c r="K7" s="5" t="s">
+        <v>348</v>
+      </c>
     </row>
     <row r="8" spans="1:11" ht="51.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A8" s="13" t="s">
+      <c r="A8" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="B8" s="13" t="s">
-        <v>390</v>
-      </c>
-      <c r="C8" s="13" t="s">
+      <c r="B8" s="5" t="s">
+        <v>375</v>
+      </c>
+      <c r="C8" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="D8" s="13" t="s">
+      <c r="D8" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="E8" s="13" t="s">
+      <c r="E8" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="F8" s="13" t="s">
+      <c r="F8" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="G8" s="13" t="s">
+      <c r="G8" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="H8" s="13" t="s">
+      <c r="H8" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="I8" s="13" t="s">
+      <c r="I8" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="J8" s="13"/>
-      <c r="K8" s="13"/>
+      <c r="J8" s="5" t="s">
+        <v>457</v>
+      </c>
+      <c r="K8" s="5" t="s">
+        <v>348</v>
+      </c>
     </row>
     <row r="9" spans="1:11" ht="51.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A9" s="13" t="s">
+      <c r="A9" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="B9" s="13" t="s">
-        <v>390</v>
-      </c>
-      <c r="C9" s="13" t="s">
+      <c r="B9" s="5" t="s">
+        <v>375</v>
+      </c>
+      <c r="C9" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="D9" s="13" t="s">
+      <c r="D9" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="E9" s="13" t="s">
+      <c r="E9" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="F9" s="13" t="s">
+      <c r="F9" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="G9" s="13" t="s">
+      <c r="G9" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="H9" s="13" t="s">
+      <c r="H9" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="I9" s="13" t="s">
+      <c r="I9" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="J9" s="13"/>
-      <c r="K9" s="13"/>
+      <c r="J9" s="5" t="s">
+        <v>456</v>
+      </c>
+      <c r="K9" s="5" t="s">
+        <v>348</v>
+      </c>
     </row>
     <row r="10" spans="1:11" ht="51.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A10" s="13" t="s">
+      <c r="A10" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="B10" s="13" t="s">
-        <v>390</v>
-      </c>
-      <c r="C10" s="13" t="s">
+      <c r="B10" s="5" t="s">
+        <v>375</v>
+      </c>
+      <c r="C10" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="D10" s="13" t="s">
+      <c r="D10" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="E10" s="13" t="s">
+      <c r="E10" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="F10" s="13" t="s">
+      <c r="F10" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="G10" s="13" t="s">
+      <c r="G10" s="5" t="s">
         <v>109</v>
       </c>
-      <c r="H10" s="13" t="s">
+      <c r="H10" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="I10" s="13" t="s">
+      <c r="I10" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="J10" s="13"/>
-      <c r="K10" s="13"/>
+      <c r="J10" s="5" t="s">
+        <v>458</v>
+      </c>
+      <c r="K10" s="5" t="s">
+        <v>348</v>
+      </c>
     </row>
     <row r="11" spans="1:11" ht="51.75" customHeight="1" x14ac:dyDescent="0.45"/>
   </sheetData>
+  <conditionalFormatting sqref="K5:K10">
+    <cfRule type="containsText" dxfId="15" priority="1" operator="containsText" text="Pass">
+      <formula>NOT(ISERROR(SEARCH("Pass",K5)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" sqref="K2:K10" xr:uid="{00000000-0002-0000-0200-000000000000}">
+    <dataValidation type="list" allowBlank="1" sqref="K2:K10" xr:uid="{7B1B7323-DEA2-4388-A571-4CBBEFC9550F}">
       <formula1>"Pass,Fail,Blocked,Not Executed,In Progress"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -4346,148 +5652,165 @@
   <dimension ref="A1:K4"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="12.06640625" customWidth="1"/>
-    <col min="2" max="2" width="23.265625" customWidth="1"/>
-    <col min="3" max="3" width="22" customWidth="1"/>
-    <col min="4" max="4" width="55.73046875" customWidth="1"/>
-    <col min="5" max="5" width="49.86328125" customWidth="1"/>
-    <col min="6" max="6" width="26" customWidth="1"/>
-    <col min="7" max="7" width="44" customWidth="1"/>
-    <col min="8" max="8" width="59.9296875" customWidth="1"/>
-    <col min="9" max="9" width="50.06640625" customWidth="1"/>
+    <col min="1" max="1" width="11.796875" customWidth="1"/>
+    <col min="2" max="2" width="18.1328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="44" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="26.59765625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.1328125" customWidth="1"/>
+    <col min="7" max="7" width="40.796875" customWidth="1"/>
+    <col min="8" max="8" width="34.73046875" customWidth="1"/>
+    <col min="9" max="9" width="39.06640625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="32" customWidth="1"/>
     <col min="11" max="11" width="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="51.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="13" t="s">
+    <row r="2" spans="1:11" ht="57" x14ac:dyDescent="0.45">
+      <c r="A2" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="B2" s="13" t="s">
-        <v>384</v>
-      </c>
-      <c r="C2" s="13" t="s">
+      <c r="B2" s="5" t="s">
+        <v>369</v>
+      </c>
+      <c r="C2" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="D2" s="13" t="s">
+      <c r="D2" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="E2" s="13" t="s">
+      <c r="E2" s="5" t="s">
         <v>112</v>
       </c>
-      <c r="F2" s="13" t="s">
+      <c r="F2" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="G2" s="13" t="s">
+      <c r="G2" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="H2" s="13" t="s">
+      <c r="H2" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="I2" s="13" t="s">
+      <c r="I2" s="5" t="s">
         <v>115</v>
       </c>
-      <c r="J2" s="13"/>
-      <c r="K2" s="13"/>
-    </row>
-    <row r="3" spans="1:11" ht="51.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A3" s="13" t="s">
+      <c r="J2" s="5" t="s">
+        <v>451</v>
+      </c>
+      <c r="K2" s="5" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="57" x14ac:dyDescent="0.45">
+      <c r="A3" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B3" s="13" t="s">
-        <v>384</v>
-      </c>
-      <c r="C3" s="13" t="s">
+      <c r="B3" s="5" t="s">
+        <v>369</v>
+      </c>
+      <c r="C3" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="D3" s="13" t="s">
+      <c r="D3" s="5" t="s">
         <v>117</v>
       </c>
-      <c r="E3" s="13" t="s">
+      <c r="E3" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="F3" s="13" t="s">
+      <c r="F3" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="G3" s="13" t="s">
+      <c r="G3" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="H3" s="13" t="s">
+      <c r="H3" s="5" t="s">
         <v>120</v>
       </c>
-      <c r="I3" s="13" t="s">
+      <c r="I3" s="5" t="s">
         <v>121</v>
       </c>
-      <c r="J3" s="13"/>
-      <c r="K3" s="13"/>
-    </row>
-    <row r="4" spans="1:11" ht="51.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A4" s="13" t="s">
+      <c r="J3" s="5" t="s">
+        <v>453</v>
+      </c>
+      <c r="K3" s="5" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="57" x14ac:dyDescent="0.45">
+      <c r="A4" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="B4" s="13" t="s">
-        <v>384</v>
-      </c>
-      <c r="C4" s="13" t="s">
+      <c r="B4" s="5" t="s">
+        <v>369</v>
+      </c>
+      <c r="C4" s="5" t="s">
         <v>122</v>
       </c>
-      <c r="D4" s="13" t="s">
+      <c r="D4" s="5" t="s">
         <v>123</v>
       </c>
-      <c r="E4" s="13" t="s">
+      <c r="E4" s="5" t="s">
         <v>124</v>
       </c>
-      <c r="F4" s="13" t="s">
+      <c r="F4" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="G4" s="13" t="s">
+      <c r="G4" s="5" t="s">
         <v>125</v>
       </c>
-      <c r="H4" s="13" t="s">
+      <c r="H4" s="5" t="s">
         <v>126</v>
       </c>
-      <c r="I4" s="13" t="s">
+      <c r="I4" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="J4" s="13"/>
-      <c r="K4" s="13"/>
+      <c r="J4" s="5" t="s">
+        <v>452</v>
+      </c>
+      <c r="K4" s="5" t="s">
+        <v>348</v>
+      </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="K2:K4">
+    <cfRule type="containsText" dxfId="14" priority="1" operator="containsText" text="Pass">
+      <formula>NOT(ISERROR(SEARCH("Pass",K2)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" sqref="K2:K4" xr:uid="{00000000-0002-0000-0300-000000000000}">
       <formula1>"Pass,Fail,Blocked,Not Executed,In Progress"</formula1>
@@ -4503,61 +5826,59 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39194ACA-1A28-40CD-9D66-086FDDEF2DA0}">
   <dimension ref="A1:K5"/>
-  <sheetFormatPr defaultColWidth="13.59765625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="12.06640625" style="13" customWidth="1"/>
-    <col min="2" max="2" width="18" style="13" customWidth="1"/>
-    <col min="3" max="3" width="31.1328125" style="13" customWidth="1"/>
-    <col min="4" max="4" width="49.59765625" style="13" customWidth="1"/>
-    <col min="5" max="5" width="43.3984375" style="13" customWidth="1"/>
-    <col min="6" max="6" width="30.9296875" style="13" customWidth="1"/>
-    <col min="7" max="7" width="49.19921875" style="13" customWidth="1"/>
-    <col min="8" max="8" width="52.46484375" style="13" customWidth="1"/>
-    <col min="9" max="9" width="57.86328125" style="13" customWidth="1"/>
-    <col min="10" max="10" width="32" style="13" customWidth="1"/>
-    <col min="11" max="11" width="12" style="13" customWidth="1"/>
-    <col min="12" max="539" width="13.59765625" style="13" customWidth="1"/>
-    <col min="540" max="16384" width="13.59765625" style="13"/>
+    <col min="1" max="1" width="14.9296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.9296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.73046875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="24.73046875" customWidth="1"/>
+    <col min="5" max="5" width="32.73046875" customWidth="1"/>
+    <col min="6" max="6" width="23.06640625" customWidth="1"/>
+    <col min="7" max="7" width="38.265625" customWidth="1"/>
+    <col min="8" max="8" width="26.19921875" customWidth="1"/>
+    <col min="9" max="9" width="30.9296875" customWidth="1"/>
+    <col min="10" max="10" width="46.73046875" customWidth="1"/>
+    <col min="11" max="11" width="10.19921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="7" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="7" t="s">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A1" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C1" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="D1" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="E1" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="F1" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="G1" s="7" t="s">
+      <c r="G1" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="H1" s="7" t="s">
+      <c r="H1" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="I1" s="7" t="s">
+      <c r="I1" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="J1" s="7" t="s">
+      <c r="J1" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="K1" s="7" t="s">
+      <c r="K1" s="14" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="2" spans="1:11" s="13" customFormat="1" ht="51.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:11" ht="71.25" x14ac:dyDescent="0.45">
       <c r="A2" s="13" t="s">
         <v>32</v>
       </c>
@@ -4585,8 +5906,14 @@
       <c r="I2" s="13" t="s">
         <v>135</v>
       </c>
-    </row>
-    <row r="3" spans="1:11" s="13" customFormat="1" ht="51.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="J2" s="13" t="s">
+        <v>447</v>
+      </c>
+      <c r="K2" s="13" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A3" s="13" t="s">
         <v>41</v>
       </c>
@@ -4614,8 +5941,14 @@
       <c r="I3" s="13" t="s">
         <v>142</v>
       </c>
-    </row>
-    <row r="4" spans="1:11" s="13" customFormat="1" ht="51.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="J3" s="13" t="s">
+        <v>448</v>
+      </c>
+      <c r="K3" s="13" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A4" s="13" t="s">
         <v>49</v>
       </c>
@@ -4643,8 +5976,14 @@
       <c r="I4" s="13" t="s">
         <v>146</v>
       </c>
-    </row>
-    <row r="5" spans="1:11" s="13" customFormat="1" ht="51.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="J4" s="13" t="s">
+        <v>449</v>
+      </c>
+      <c r="K4" s="13" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A5" s="13" t="s">
         <v>56</v>
       </c>
@@ -4672,16 +6011,26 @@
       <c r="I5" s="13" t="s">
         <v>153</v>
       </c>
+      <c r="J5" s="13" t="s">
+        <v>450</v>
+      </c>
+      <c r="K5" s="13" t="s">
+        <v>348</v>
+      </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="K2:K5">
+    <cfRule type="containsText" dxfId="13" priority="1" operator="containsText" text="Pass">
+      <formula>NOT(ISERROR(SEARCH("Pass",K2)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" sqref="K2:K5" xr:uid="{00000000-0002-0000-0400-000000000000}">
+    <dataValidation type="list" allowBlank="1" sqref="K2:K5" xr:uid="{3818BB88-780C-4B54-A645-F9478169F534}">
       <formula1>"Pass,Fail,Blocked,Not Executed,In Progress"</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>
   </tableParts>
@@ -4707,198 +6056,223 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="D1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="E1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="F1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="G1" s="7" t="s">
+      <c r="G1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="H1" s="7" t="s">
+      <c r="H1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="I1" s="7" t="s">
+      <c r="I1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="J1" s="7" t="s">
+      <c r="J1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="K1" s="7" t="s">
+      <c r="K1" s="1" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="51.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="13" t="s">
+      <c r="A2" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="B2" s="13" t="s">
+      <c r="B2" s="5" t="s">
         <v>154</v>
       </c>
-      <c r="C2" s="13" t="s">
+      <c r="C2" s="5" t="s">
         <v>155</v>
       </c>
-      <c r="D2" s="13" t="s">
+      <c r="D2" s="5" t="s">
         <v>156</v>
       </c>
-      <c r="E2" s="13" t="s">
+      <c r="E2" s="5" t="s">
         <v>157</v>
       </c>
-      <c r="F2" s="13" t="s">
+      <c r="F2" s="5" t="s">
         <v>158</v>
       </c>
-      <c r="G2" s="13" t="s">
+      <c r="G2" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="H2" s="13" t="s">
+      <c r="H2" s="5" t="s">
         <v>160</v>
       </c>
-      <c r="I2" s="13" t="s">
+      <c r="I2" s="5" t="s">
         <v>161</v>
       </c>
-      <c r="J2" s="13"/>
-      <c r="K2" s="13"/>
+      <c r="J2" s="5" t="s">
+        <v>442</v>
+      </c>
+      <c r="K2" s="5" t="s">
+        <v>348</v>
+      </c>
     </row>
     <row r="3" spans="1:11" ht="51.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A3" s="13" t="s">
+      <c r="A3" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B3" s="13" t="s">
+      <c r="B3" s="5" t="s">
         <v>154</v>
       </c>
-      <c r="C3" s="13" t="s">
+      <c r="C3" s="5" t="s">
         <v>162</v>
       </c>
-      <c r="D3" s="13" t="s">
+      <c r="D3" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="E3" s="13" t="s">
+      <c r="E3" s="5" t="s">
         <v>164</v>
       </c>
-      <c r="F3" s="13" t="s">
+      <c r="F3" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="G3" s="13" t="s">
+      <c r="G3" s="5" t="s">
         <v>165</v>
       </c>
-      <c r="H3" s="13" t="s">
+      <c r="H3" s="5" t="s">
         <v>166</v>
       </c>
-      <c r="I3" s="13" t="s">
+      <c r="I3" s="5" t="s">
         <v>167</v>
       </c>
-      <c r="J3" s="13"/>
-      <c r="K3" s="13"/>
+      <c r="J3" s="5" t="s">
+        <v>443</v>
+      </c>
+      <c r="K3" s="5" t="s">
+        <v>348</v>
+      </c>
     </row>
     <row r="4" spans="1:11" ht="51.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A4" s="13" t="s">
+      <c r="A4" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="B4" s="13" t="s">
+      <c r="B4" s="5" t="s">
         <v>154</v>
       </c>
-      <c r="C4" s="13" t="s">
+      <c r="C4" s="5" t="s">
         <v>168</v>
       </c>
-      <c r="D4" s="13" t="s">
+      <c r="D4" s="5" t="s">
         <v>169</v>
       </c>
-      <c r="E4" s="13" t="s">
+      <c r="E4" s="5" t="s">
         <v>164</v>
       </c>
-      <c r="F4" s="13" t="s">
+      <c r="F4" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="G4" s="13" t="s">
+      <c r="G4" s="5" t="s">
         <v>170</v>
       </c>
-      <c r="H4" s="13" t="s">
+      <c r="H4" s="5" t="s">
         <v>171</v>
       </c>
-      <c r="I4" s="13" t="s">
+      <c r="I4" s="5" t="s">
         <v>172</v>
       </c>
-      <c r="J4" s="13"/>
-      <c r="K4" s="13"/>
+      <c r="J4" s="5" t="s">
+        <v>444</v>
+      </c>
+      <c r="K4" s="5" t="s">
+        <v>348</v>
+      </c>
     </row>
     <row r="5" spans="1:11" ht="51.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A5" s="13" t="s">
+      <c r="A5" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="B5" s="13" t="s">
+      <c r="B5" s="5" t="s">
         <v>154</v>
       </c>
-      <c r="C5" s="13" t="s">
+      <c r="C5" s="5" t="s">
         <v>173</v>
       </c>
-      <c r="D5" s="13" t="s">
+      <c r="D5" s="5" t="s">
         <v>174</v>
       </c>
-      <c r="E5" s="13" t="s">
+      <c r="E5" s="5" t="s">
         <v>164</v>
       </c>
-      <c r="F5" s="13" t="s">
+      <c r="F5" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="G5" s="13" t="s">
+      <c r="G5" s="5" t="s">
         <v>175</v>
       </c>
-      <c r="H5" s="13" t="s">
+      <c r="H5" s="5" t="s">
         <v>176</v>
       </c>
-      <c r="I5" s="13" t="s">
+      <c r="I5" s="5" t="s">
         <v>177</v>
       </c>
-      <c r="J5" s="13"/>
-      <c r="K5" s="13"/>
+      <c r="J5" s="5" t="s">
+        <v>445</v>
+      </c>
+      <c r="K5" s="5" t="s">
+        <v>348</v>
+      </c>
     </row>
     <row r="6" spans="1:11" ht="51.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A6" s="13" t="s">
+      <c r="A6" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="B6" s="13" t="s">
+      <c r="B6" s="5" t="s">
         <v>154</v>
       </c>
-      <c r="C6" s="13" t="s">
+      <c r="C6" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="D6" s="13" t="s">
+      <c r="D6" s="5" t="s">
         <v>179</v>
       </c>
-      <c r="E6" s="13" t="s">
+      <c r="E6" s="5" t="s">
         <v>164</v>
       </c>
-      <c r="F6" s="13" t="s">
+      <c r="F6" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="G6" s="13" t="s">
+      <c r="G6" s="5" t="s">
         <v>180</v>
       </c>
-      <c r="H6" s="13" t="s">
+      <c r="H6" s="5" t="s">
         <v>181</v>
       </c>
-      <c r="I6" s="13" t="s">
+      <c r="I6" s="5" t="s">
         <v>182</v>
       </c>
-      <c r="J6" s="13"/>
-      <c r="K6" s="13"/>
+      <c r="J6" s="5" t="s">
+        <v>446</v>
+      </c>
+      <c r="K6" s="5" t="s">
+        <v>348</v>
+      </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="K2:K6">
+    <cfRule type="containsText" dxfId="12" priority="1" operator="containsText" text="Pass">
+      <formula>NOT(ISERROR(SEARCH("Pass",K2)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" sqref="K2:K6" xr:uid="{00000000-0002-0000-0500-000000000000}">
+    <dataValidation type="list" allowBlank="1" sqref="K2:K6" xr:uid="{3A3298BF-ED4B-47D9-A88B-3F023B45D19F}">
       <formula1>"Pass,Fail,Blocked,Not Executed,In Progress"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -4916,213 +6290,248 @@
   <dimension ref="A1:K6"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="12.06640625" style="14" customWidth="1"/>
-    <col min="2" max="2" width="27.33203125" style="14" customWidth="1"/>
-    <col min="3" max="3" width="22" style="14" customWidth="1"/>
-    <col min="4" max="4" width="60.3984375" style="14" customWidth="1"/>
-    <col min="5" max="5" width="44.3984375" style="14" customWidth="1"/>
-    <col min="6" max="6" width="26" style="14" customWidth="1"/>
-    <col min="7" max="7" width="44" style="14" customWidth="1"/>
-    <col min="8" max="8" width="47.59765625" style="14" customWidth="1"/>
-    <col min="9" max="9" width="59.1328125" style="14" customWidth="1"/>
-    <col min="10" max="10" width="32" style="14" customWidth="1"/>
-    <col min="11" max="11" width="12" style="14" customWidth="1"/>
-    <col min="12" max="16384" width="8.6640625" style="14"/>
+    <col min="1" max="1" width="12.06640625" style="6" customWidth="1"/>
+    <col min="2" max="2" width="27.33203125" style="6" customWidth="1"/>
+    <col min="3" max="3" width="22" style="6" customWidth="1"/>
+    <col min="4" max="4" width="60.3984375" style="6" customWidth="1"/>
+    <col min="5" max="5" width="44.3984375" style="6" customWidth="1"/>
+    <col min="6" max="6" width="26" style="6" customWidth="1"/>
+    <col min="7" max="7" width="44" style="6" customWidth="1"/>
+    <col min="8" max="8" width="47.59765625" style="6" customWidth="1"/>
+    <col min="9" max="9" width="59.1328125" style="6" customWidth="1"/>
+    <col min="10" max="10" width="32" style="6" customWidth="1"/>
+    <col min="11" max="11" width="12" style="6" customWidth="1"/>
+    <col min="12" max="16384" width="8.6640625" style="6"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="F1" s="13" t="s">
+      <c r="F1" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="G1" s="13" t="s">
+      <c r="G1" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="H1" s="13" t="s">
+      <c r="H1" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="I1" s="13" t="s">
+      <c r="I1" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="J1" s="13" t="s">
+      <c r="J1" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="K1" s="13" t="s">
+      <c r="K1" s="5" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="51.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="13" t="s">
+      <c r="A2" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="B2" s="13" t="s">
-        <v>391</v>
-      </c>
-      <c r="C2" s="13" t="s">
+      <c r="B2" s="5" t="s">
+        <v>376</v>
+      </c>
+      <c r="C2" s="5" t="s">
         <v>183</v>
       </c>
-      <c r="D2" s="13" t="s">
+      <c r="D2" s="5" t="s">
         <v>184</v>
       </c>
-      <c r="E2" s="13" t="s">
+      <c r="E2" s="5" t="s">
         <v>185</v>
       </c>
-      <c r="F2" s="13" t="s">
+      <c r="F2" s="5" t="s">
         <v>186</v>
       </c>
-      <c r="G2" s="13" t="s">
+      <c r="G2" s="5" t="s">
         <v>187</v>
       </c>
-      <c r="H2" s="13" t="s">
+      <c r="H2" s="5" t="s">
         <v>188</v>
       </c>
-      <c r="I2" s="13" t="s">
+      <c r="I2" s="5" t="s">
         <v>189</v>
       </c>
-      <c r="J2" s="13"/>
-      <c r="K2" s="13"/>
+      <c r="J2" s="5" t="s">
+        <v>437</v>
+      </c>
+      <c r="K2" s="5" t="s">
+        <v>348</v>
+      </c>
     </row>
     <row r="3" spans="1:11" ht="51.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A3" s="13" t="s">
+      <c r="A3" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B3" s="13" t="s">
-        <v>391</v>
-      </c>
-      <c r="C3" s="13" t="s">
+      <c r="B3" s="5" t="s">
+        <v>376</v>
+      </c>
+      <c r="C3" s="5" t="s">
         <v>190</v>
       </c>
-      <c r="D3" s="13" t="s">
+      <c r="D3" s="5" t="s">
         <v>191</v>
       </c>
-      <c r="E3" s="13" t="s">
+      <c r="E3" s="5" t="s">
         <v>185</v>
       </c>
-      <c r="F3" s="13" t="s">
+      <c r="F3" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="G3" s="13" t="s">
+      <c r="G3" s="5" t="s">
         <v>192</v>
       </c>
-      <c r="H3" s="13" t="s">
+      <c r="H3" s="5" t="s">
         <v>193</v>
       </c>
-      <c r="I3" s="13" t="s">
+      <c r="I3" s="5" t="s">
         <v>194</v>
       </c>
-      <c r="J3" s="13"/>
-      <c r="K3" s="13"/>
+      <c r="J3" s="5" t="s">
+        <v>438</v>
+      </c>
+      <c r="K3" s="5" t="s">
+        <v>349</v>
+      </c>
     </row>
     <row r="4" spans="1:11" ht="51.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A4" s="13" t="s">
+      <c r="A4" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="B4" s="13" t="s">
-        <v>391</v>
-      </c>
-      <c r="C4" s="13" t="s">
+      <c r="B4" s="5" t="s">
+        <v>376</v>
+      </c>
+      <c r="C4" s="5" t="s">
         <v>190</v>
       </c>
-      <c r="D4" s="13" t="s">
+      <c r="D4" s="5" t="s">
         <v>195</v>
       </c>
-      <c r="E4" s="13" t="s">
+      <c r="E4" s="5" t="s">
         <v>185</v>
       </c>
-      <c r="F4" s="13" t="s">
+      <c r="F4" s="5" t="s">
         <v>196</v>
       </c>
-      <c r="G4" s="13" t="s">
+      <c r="G4" s="5" t="s">
         <v>197</v>
       </c>
-      <c r="H4" s="13" t="s">
+      <c r="H4" s="5" t="s">
         <v>198</v>
       </c>
-      <c r="I4" s="13" t="s">
+      <c r="I4" s="5" t="s">
         <v>199</v>
       </c>
-      <c r="J4" s="13"/>
-      <c r="K4" s="13"/>
+      <c r="J4" s="5" t="s">
+        <v>439</v>
+      </c>
+      <c r="K4" s="5" t="s">
+        <v>348</v>
+      </c>
     </row>
     <row r="5" spans="1:11" ht="51.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A5" s="13" t="s">
+      <c r="A5" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="B5" s="13" t="s">
-        <v>391</v>
-      </c>
-      <c r="C5" s="13" t="s">
+      <c r="B5" s="5" t="s">
+        <v>376</v>
+      </c>
+      <c r="C5" s="5" t="s">
         <v>190</v>
       </c>
-      <c r="D5" s="13" t="s">
+      <c r="D5" s="5" t="s">
         <v>200</v>
       </c>
-      <c r="E5" s="13" t="s">
+      <c r="E5" s="5" t="s">
         <v>185</v>
       </c>
-      <c r="F5" s="13" t="s">
+      <c r="F5" s="5" t="s">
         <v>201</v>
       </c>
-      <c r="G5" s="13" t="s">
+      <c r="G5" s="5" t="s">
         <v>202</v>
       </c>
-      <c r="H5" s="13" t="s">
+      <c r="H5" s="5" t="s">
         <v>203</v>
       </c>
-      <c r="I5" s="13" t="s">
+      <c r="I5" s="5" t="s">
         <v>204</v>
       </c>
-      <c r="J5" s="13"/>
-      <c r="K5" s="13"/>
+      <c r="J5" s="5" t="s">
+        <v>440</v>
+      </c>
+      <c r="K5" s="5" t="s">
+        <v>348</v>
+      </c>
     </row>
     <row r="6" spans="1:11" ht="51.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A6" s="13" t="s">
+      <c r="A6" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="B6" s="13" t="s">
-        <v>391</v>
-      </c>
-      <c r="C6" s="13" t="s">
+      <c r="B6" s="5" t="s">
+        <v>376</v>
+      </c>
+      <c r="C6" s="5" t="s">
         <v>205</v>
       </c>
-      <c r="D6" s="13" t="s">
+      <c r="D6" s="5" t="s">
         <v>206</v>
       </c>
-      <c r="E6" s="13" t="s">
+      <c r="E6" s="5" t="s">
         <v>185</v>
       </c>
-      <c r="F6" s="13" t="s">
+      <c r="F6" s="5" t="s">
         <v>207</v>
       </c>
-      <c r="G6" s="13" t="s">
+      <c r="G6" s="5" t="s">
         <v>208</v>
       </c>
-      <c r="H6" s="13" t="s">
+      <c r="H6" s="5" t="s">
         <v>209</v>
       </c>
-      <c r="I6" s="13" t="s">
+      <c r="I6" s="5" t="s">
         <v>210</v>
       </c>
-      <c r="J6" s="13"/>
-      <c r="K6" s="13"/>
+      <c r="J6" s="5" t="s">
+        <v>441</v>
+      </c>
+      <c r="K6" s="5" t="s">
+        <v>348</v>
+      </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="K2">
+    <cfRule type="containsText" dxfId="11" priority="2" operator="containsText" text="Pass">
+      <formula>NOT(ISERROR(SEARCH("Pass",K2)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K3">
+    <cfRule type="containsText" dxfId="10" priority="3" operator="containsText" text="Fail">
+      <formula>NOT(ISERROR(SEARCH("Fail",K3)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K4:K6">
+    <cfRule type="containsText" dxfId="9" priority="1" operator="containsText" text="Pass">
+      <formula>NOT(ISERROR(SEARCH("Pass",K4)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" sqref="K2:K6" xr:uid="{00000000-0002-0000-0600-000000000000}">
+    <dataValidation type="list" allowBlank="1" sqref="K2:K6" xr:uid="{372DEBF2-427E-4538-BCF5-6D10E4E5AC37}">
       <formula1>"Pass,Fail,Blocked,Not Executed,In Progress"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -5154,262 +6563,295 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="25.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="D1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="E1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="F1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="G1" s="7" t="s">
+      <c r="G1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="H1" s="7" t="s">
+      <c r="H1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="I1" s="7" t="s">
+      <c r="I1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="J1" s="7" t="s">
+      <c r="J1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="K1" s="7" t="s">
+      <c r="K1" s="1" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="34.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="13" t="s">
+      <c r="A2" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="B2" s="13" t="s">
-        <v>395</v>
-      </c>
-      <c r="C2" s="13" t="s">
+      <c r="B2" s="5" t="s">
+        <v>380</v>
+      </c>
+      <c r="C2" s="5" t="s">
         <v>211</v>
       </c>
-      <c r="D2" s="13" t="s">
+      <c r="D2" s="5" t="s">
         <v>212</v>
       </c>
-      <c r="E2" s="13" t="s">
+      <c r="E2" s="5" t="s">
         <v>213</v>
       </c>
-      <c r="F2" s="13" t="s">
+      <c r="F2" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="G2" s="13" t="s">
+      <c r="G2" s="5" t="s">
         <v>214</v>
       </c>
-      <c r="H2" s="13" t="s">
+      <c r="H2" s="5" t="s">
         <v>215</v>
       </c>
-      <c r="I2" s="13" t="s">
+      <c r="I2" s="5" t="s">
         <v>216</v>
       </c>
-      <c r="J2" s="13"/>
-      <c r="K2" s="13"/>
+      <c r="J2" s="5" t="s">
+        <v>430</v>
+      </c>
+      <c r="K2" s="5" t="s">
+        <v>348</v>
+      </c>
     </row>
     <row r="3" spans="1:11" ht="51" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A3" s="13" t="s">
+      <c r="A3" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B3" s="13" t="s">
-        <v>395</v>
-      </c>
-      <c r="C3" s="13" t="s">
+      <c r="B3" s="5" t="s">
+        <v>380</v>
+      </c>
+      <c r="C3" s="5" t="s">
         <v>217</v>
       </c>
-      <c r="D3" s="13" t="s">
+      <c r="D3" s="5" t="s">
         <v>218</v>
       </c>
-      <c r="E3" s="13" t="s">
+      <c r="E3" s="5" t="s">
         <v>219</v>
       </c>
-      <c r="F3" s="13" t="s">
+      <c r="F3" s="5" t="s">
         <v>220</v>
       </c>
-      <c r="G3" s="13" t="s">
+      <c r="G3" s="5" t="s">
         <v>221</v>
       </c>
-      <c r="H3" s="13" t="s">
+      <c r="H3" s="5" t="s">
         <v>222</v>
       </c>
-      <c r="I3" s="13" t="s">
+      <c r="I3" s="5" t="s">
         <v>223</v>
       </c>
-      <c r="J3" s="13"/>
-      <c r="K3" s="13"/>
+      <c r="J3" s="5" t="s">
+        <v>431</v>
+      </c>
+      <c r="K3" s="5" t="s">
+        <v>348</v>
+      </c>
     </row>
     <row r="4" spans="1:11" ht="51.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A4" s="13" t="s">
+      <c r="A4" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="B4" s="13" t="s">
-        <v>395</v>
-      </c>
-      <c r="C4" s="13" t="s">
+      <c r="B4" s="5" t="s">
+        <v>380</v>
+      </c>
+      <c r="C4" s="5" t="s">
         <v>224</v>
       </c>
-      <c r="D4" s="13" t="s">
+      <c r="D4" s="5" t="s">
         <v>225</v>
       </c>
-      <c r="E4" s="13" t="s">
+      <c r="E4" s="5" t="s">
         <v>226</v>
       </c>
-      <c r="F4" s="13" t="s">
+      <c r="F4" s="5" t="s">
         <v>227</v>
       </c>
-      <c r="G4" s="13" t="s">
+      <c r="G4" s="5" t="s">
         <v>228</v>
       </c>
-      <c r="H4" s="13" t="s">
+      <c r="H4" s="5" t="s">
         <v>229</v>
       </c>
-      <c r="I4" s="13" t="s">
+      <c r="I4" s="5" t="s">
         <v>230</v>
       </c>
-      <c r="J4" s="13"/>
-      <c r="K4" s="13"/>
+      <c r="J4" s="5" t="s">
+        <v>432</v>
+      </c>
+      <c r="K4" s="5" t="s">
+        <v>348</v>
+      </c>
     </row>
     <row r="5" spans="1:11" ht="51.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A5" s="13" t="s">
+      <c r="A5" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="B5" s="13" t="s">
-        <v>395</v>
-      </c>
-      <c r="C5" s="13" t="s">
+      <c r="B5" s="5" t="s">
+        <v>380</v>
+      </c>
+      <c r="C5" s="5" t="s">
         <v>231</v>
       </c>
-      <c r="D5" s="13" t="s">
+      <c r="D5" s="5" t="s">
         <v>232</v>
       </c>
-      <c r="E5" s="13" t="s">
+      <c r="E5" s="5" t="s">
         <v>233</v>
       </c>
-      <c r="F5" s="13" t="s">
+      <c r="F5" s="5" t="s">
         <v>234</v>
       </c>
-      <c r="G5" s="13" t="s">
+      <c r="G5" s="5" t="s">
         <v>235</v>
       </c>
-      <c r="H5" s="13" t="s">
+      <c r="H5" s="5" t="s">
         <v>236</v>
       </c>
-      <c r="I5" s="13" t="s">
+      <c r="I5" s="5" t="s">
         <v>237</v>
       </c>
-      <c r="J5" s="13"/>
-      <c r="K5" s="13"/>
+      <c r="J5" s="5" t="s">
+        <v>433</v>
+      </c>
+      <c r="K5" s="5" t="s">
+        <v>348</v>
+      </c>
     </row>
     <row r="6" spans="1:11" ht="51.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A6" s="13" t="s">
+      <c r="A6" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="B6" s="13" t="s">
-        <v>395</v>
-      </c>
-      <c r="C6" s="13" t="s">
+      <c r="B6" s="5" t="s">
+        <v>380</v>
+      </c>
+      <c r="C6" s="5" t="s">
         <v>238</v>
       </c>
-      <c r="D6" s="13" t="s">
+      <c r="D6" s="5" t="s">
         <v>239</v>
       </c>
-      <c r="E6" s="13" t="s">
+      <c r="E6" s="5" t="s">
         <v>213</v>
       </c>
-      <c r="F6" s="13" t="s">
+      <c r="F6" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="G6" s="13" t="s">
+      <c r="G6" s="5" t="s">
         <v>240</v>
       </c>
-      <c r="H6" s="13" t="s">
+      <c r="H6" s="5" t="s">
         <v>241</v>
       </c>
-      <c r="I6" s="13" t="s">
+      <c r="I6" s="5" t="s">
         <v>242</v>
       </c>
-      <c r="J6" s="13"/>
-      <c r="K6" s="13"/>
+      <c r="J6" s="5" t="s">
+        <v>434</v>
+      </c>
+      <c r="K6" s="5" t="s">
+        <v>348</v>
+      </c>
     </row>
     <row r="7" spans="1:11" ht="51.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A7" s="13" t="s">
+      <c r="A7" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="B7" s="13" t="s">
-        <v>395</v>
-      </c>
-      <c r="C7" s="13" t="s">
+      <c r="B7" s="5" t="s">
+        <v>380</v>
+      </c>
+      <c r="C7" s="5" t="s">
         <v>243</v>
       </c>
-      <c r="D7" s="13" t="s">
+      <c r="D7" s="5" t="s">
         <v>244</v>
       </c>
-      <c r="E7" s="13" t="s">
+      <c r="E7" s="5" t="s">
         <v>213</v>
       </c>
-      <c r="F7" s="13" t="s">
+      <c r="F7" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="G7" s="13" t="s">
+      <c r="G7" s="5" t="s">
         <v>245</v>
       </c>
-      <c r="H7" s="13" t="s">
+      <c r="H7" s="5" t="s">
         <v>246</v>
       </c>
-      <c r="I7" s="13" t="s">
+      <c r="I7" s="5" t="s">
         <v>247</v>
       </c>
-      <c r="J7" s="13"/>
-      <c r="K7" s="13"/>
+      <c r="J7" s="5" t="s">
+        <v>435</v>
+      </c>
+      <c r="K7" s="5" t="s">
+        <v>348</v>
+      </c>
     </row>
     <row r="8" spans="1:11" ht="51.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A8" s="13" t="s">
+      <c r="A8" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="B8" s="13" t="s">
-        <v>395</v>
-      </c>
-      <c r="C8" s="13" t="s">
+      <c r="B8" s="5" t="s">
+        <v>380</v>
+      </c>
+      <c r="C8" s="5" t="s">
         <v>248</v>
       </c>
-      <c r="D8" s="13" t="s">
+      <c r="D8" s="5" t="s">
         <v>249</v>
       </c>
-      <c r="E8" s="13" t="s">
+      <c r="E8" s="5" t="s">
         <v>213</v>
       </c>
-      <c r="F8" s="13" t="s">
+      <c r="F8" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="G8" s="13" t="s">
+      <c r="G8" s="5" t="s">
         <v>250</v>
       </c>
-      <c r="H8" s="13" t="s">
+      <c r="H8" s="5" t="s">
         <v>251</v>
       </c>
-      <c r="I8" s="13" t="s">
+      <c r="I8" s="5" t="s">
         <v>252</v>
       </c>
-      <c r="J8" s="13"/>
-      <c r="K8" s="13"/>
+      <c r="J8" s="5" t="s">
+        <v>436</v>
+      </c>
+      <c r="K8" s="5" t="s">
+        <v>348</v>
+      </c>
     </row>
     <row r="9" spans="1:11" ht="51.75" customHeight="1" x14ac:dyDescent="0.45"/>
     <row r="10" spans="1:11" ht="51.75" customHeight="1" x14ac:dyDescent="0.45"/>
   </sheetData>
+  <conditionalFormatting sqref="K2:K8">
+    <cfRule type="containsText" dxfId="8" priority="1" operator="containsText" text="Pass">
+      <formula>NOT(ISERROR(SEARCH("Pass",K2)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" sqref="K2:K8" xr:uid="{00000000-0002-0000-0800-000000000000}">
+    <dataValidation type="list" allowBlank="1" sqref="K2:K8" xr:uid="{5D13BAD1-2AF9-4354-B64D-274BC3D02046}">
       <formula1>"Pass,Fail,Blocked,Not Executed,In Progress"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -5441,200 +6883,225 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="25.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="D1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="E1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="F1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="G1" s="7" t="s">
+      <c r="G1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="H1" s="7" t="s">
+      <c r="H1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="I1" s="7" t="s">
+      <c r="I1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="J1" s="7" t="s">
+      <c r="J1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="K1" s="7" t="s">
+      <c r="K1" s="1" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="48" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="13" t="s">
+      <c r="A2" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="B2" s="13" t="s">
-        <v>396</v>
-      </c>
-      <c r="C2" s="13" t="s">
+      <c r="B2" s="5" t="s">
+        <v>381</v>
+      </c>
+      <c r="C2" s="5" t="s">
         <v>253</v>
       </c>
-      <c r="D2" s="13" t="s">
+      <c r="D2" s="5" t="s">
         <v>254</v>
       </c>
-      <c r="E2" s="13" t="s">
+      <c r="E2" s="5" t="s">
         <v>255</v>
       </c>
-      <c r="F2" s="13" t="s">
+      <c r="F2" s="5" t="s">
         <v>227</v>
       </c>
-      <c r="G2" s="13" t="s">
+      <c r="G2" s="5" t="s">
         <v>256</v>
       </c>
-      <c r="H2" s="13" t="s">
+      <c r="H2" s="5" t="s">
         <v>257</v>
       </c>
-      <c r="I2" s="13" t="s">
+      <c r="I2" s="5" t="s">
         <v>258</v>
       </c>
-      <c r="J2" s="13"/>
-      <c r="K2" s="13"/>
+      <c r="J2" s="5" t="s">
+        <v>425</v>
+      </c>
+      <c r="K2" s="5" t="s">
+        <v>348</v>
+      </c>
     </row>
     <row r="3" spans="1:11" ht="42.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A3" s="13" t="s">
+      <c r="A3" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B3" s="13" t="s">
-        <v>396</v>
-      </c>
-      <c r="C3" s="13" t="s">
+      <c r="B3" s="5" t="s">
+        <v>381</v>
+      </c>
+      <c r="C3" s="5" t="s">
         <v>259</v>
       </c>
-      <c r="D3" s="13" t="s">
+      <c r="D3" s="5" t="s">
         <v>260</v>
       </c>
-      <c r="E3" s="13" t="s">
+      <c r="E3" s="5" t="s">
         <v>164</v>
       </c>
-      <c r="F3" s="13" t="s">
+      <c r="F3" s="5" t="s">
         <v>261</v>
       </c>
-      <c r="G3" s="13" t="s">
+      <c r="G3" s="5" t="s">
         <v>262</v>
       </c>
-      <c r="H3" s="13" t="s">
+      <c r="H3" s="5" t="s">
         <v>263</v>
       </c>
-      <c r="I3" s="13" t="s">
+      <c r="I3" s="5" t="s">
         <v>264</v>
       </c>
-      <c r="J3" s="13"/>
-      <c r="K3" s="13"/>
+      <c r="J3" s="5" t="s">
+        <v>426</v>
+      </c>
+      <c r="K3" s="5" t="s">
+        <v>348</v>
+      </c>
     </row>
     <row r="4" spans="1:11" ht="51.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A4" s="13" t="s">
+      <c r="A4" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="B4" s="13" t="s">
-        <v>396</v>
-      </c>
-      <c r="C4" s="13" t="s">
+      <c r="B4" s="5" t="s">
+        <v>381</v>
+      </c>
+      <c r="C4" s="5" t="s">
         <v>265</v>
       </c>
-      <c r="D4" s="13" t="s">
+      <c r="D4" s="5" t="s">
         <v>266</v>
       </c>
-      <c r="E4" s="13" t="s">
+      <c r="E4" s="5" t="s">
         <v>213</v>
       </c>
-      <c r="F4" s="13" t="s">
+      <c r="F4" s="5" t="s">
         <v>267</v>
       </c>
-      <c r="G4" s="13" t="s">
+      <c r="G4" s="5" t="s">
         <v>268</v>
       </c>
-      <c r="H4" s="13" t="s">
+      <c r="H4" s="5" t="s">
         <v>269</v>
       </c>
-      <c r="I4" s="13" t="s">
+      <c r="I4" s="5" t="s">
         <v>270</v>
       </c>
-      <c r="J4" s="13"/>
-      <c r="K4" s="13"/>
+      <c r="J4" s="5" t="s">
+        <v>427</v>
+      </c>
+      <c r="K4" s="5" t="s">
+        <v>348</v>
+      </c>
     </row>
     <row r="5" spans="1:11" ht="51.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A5" s="13" t="s">
+      <c r="A5" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="B5" s="13" t="s">
-        <v>396</v>
-      </c>
-      <c r="C5" s="13" t="s">
+      <c r="B5" s="5" t="s">
+        <v>381</v>
+      </c>
+      <c r="C5" s="5" t="s">
         <v>271</v>
       </c>
-      <c r="D5" s="13" t="s">
+      <c r="D5" s="5" t="s">
         <v>272</v>
       </c>
-      <c r="E5" s="13" t="s">
+      <c r="E5" s="5" t="s">
         <v>273</v>
       </c>
-      <c r="F5" s="13" t="s">
+      <c r="F5" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="G5" s="13" t="s">
+      <c r="G5" s="5" t="s">
         <v>274</v>
       </c>
-      <c r="H5" s="13" t="s">
+      <c r="H5" s="5" t="s">
         <v>275</v>
       </c>
-      <c r="I5" s="13" t="s">
+      <c r="I5" s="5" t="s">
         <v>276</v>
       </c>
-      <c r="J5" s="13"/>
-      <c r="K5" s="13"/>
+      <c r="J5" s="5" t="s">
+        <v>428</v>
+      </c>
+      <c r="K5" s="5" t="s">
+        <v>348</v>
+      </c>
     </row>
     <row r="6" spans="1:11" ht="51.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A6" s="13" t="s">
+      <c r="A6" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="B6" s="13" t="s">
-        <v>396</v>
-      </c>
-      <c r="C6" s="13" t="s">
+      <c r="B6" s="5" t="s">
+        <v>381</v>
+      </c>
+      <c r="C6" s="5" t="s">
         <v>277</v>
       </c>
-      <c r="D6" s="13" t="s">
+      <c r="D6" s="5" t="s">
         <v>278</v>
       </c>
-      <c r="E6" s="13" t="s">
+      <c r="E6" s="5" t="s">
         <v>279</v>
       </c>
-      <c r="F6" s="13" t="s">
+      <c r="F6" s="5" t="s">
         <v>280</v>
       </c>
-      <c r="G6" s="13" t="s">
+      <c r="G6" s="5" t="s">
         <v>281</v>
       </c>
-      <c r="H6" s="13" t="s">
+      <c r="H6" s="5" t="s">
         <v>282</v>
       </c>
-      <c r="I6" s="13" t="s">
+      <c r="I6" s="5" t="s">
         <v>283</v>
       </c>
-      <c r="J6" s="13"/>
-      <c r="K6" s="13"/>
+      <c r="J6" s="5" t="s">
+        <v>429</v>
+      </c>
+      <c r="K6" s="5" t="s">
+        <v>348</v>
+      </c>
     </row>
     <row r="7" spans="1:11" ht="51.75" customHeight="1" x14ac:dyDescent="0.45"/>
     <row r="8" spans="1:11" ht="51.75" customHeight="1" x14ac:dyDescent="0.45"/>
   </sheetData>
+  <conditionalFormatting sqref="K2:K6">
+    <cfRule type="containsText" dxfId="7" priority="1" operator="containsText" text="Pass">
+      <formula>NOT(ISERROR(SEARCH("Pass",K2)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" sqref="K2:K6" xr:uid="{00000000-0002-0000-0900-000000000000}">
+    <dataValidation type="list" allowBlank="1" sqref="K2:K6" xr:uid="{ACBF0B5C-0272-4CBB-8509-CEB13C0CBF39}">
       <formula1>"Pass,Fail,Blocked,Not Executed,In Progress"</formula1>
       <formula2>0</formula2>
     </dataValidation>

--- a/DarazNP - QA/Daraz_Nepal_QA_TestPlan.xlsx
+++ b/DarazNP - QA/Daraz_Nepal_QA_TestPlan.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\QA\DarazNP - QA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DDE6732A-62F1-43A2-A048-E5821CF26FEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43EB3697-1F48-4001-B821-12B2DE4E3B3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" tabRatio="500" firstSheet="4" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" tabRatio="500" firstSheet="7" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Test Scenario" sheetId="1" r:id="rId1"/>
@@ -27,12 +27,11 @@
     <sheet name="Summary" sheetId="13" r:id="rId12"/>
   </sheets>
   <calcPr calcId="0" iterateDelta="1E-4"/>
-  <fileRecoveryPr repairLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="802" uniqueCount="468">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="801" uniqueCount="467">
   <si>
     <t>Project Name</t>
   </si>
@@ -1277,12 +1276,6 @@
     <t>Tester Name</t>
   </si>
   <si>
-    <t>Test Start Date</t>
-  </si>
-  <si>
-    <t>Test End Date</t>
-  </si>
-  <si>
     <t>Total Test Cases</t>
   </si>
   <si>
@@ -1679,7 +1672,10 @@
     <t>Browser</t>
   </si>
   <si>
-    <t>S</t>
+    <t>Test Start Date(Manual)</t>
+  </si>
+  <si>
+    <t>Test End Date(Manual)</t>
   </si>
 </sst>
 </file>
@@ -1953,21 +1949,6 @@
     <xf numFmtId="14" fontId="3" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1981,6 +1962,21 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3665,7 +3661,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="15" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="C1" s="15"/>
       <c r="D1" s="15"/>
@@ -3685,7 +3681,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="C3" s="15"/>
       <c r="D3" s="15"/>
@@ -3722,7 +3718,7 @@
     </row>
     <row r="7" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A7" s="5" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="B7" s="5" t="s">
         <v>9</v>
@@ -3736,7 +3732,7 @@
     </row>
     <row r="8" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A8" s="5" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="B8" s="5" t="s">
         <v>11</v>
@@ -3750,7 +3746,7 @@
     </row>
     <row r="9" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A9" s="5" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="B9" s="5" t="s">
         <v>12</v>
@@ -3764,7 +3760,7 @@
     </row>
     <row r="10" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A10" s="5" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="B10" s="5" t="s">
         <v>13</v>
@@ -3778,7 +3774,7 @@
     </row>
     <row r="11" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A11" s="5" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>15</v>
@@ -3792,7 +3788,7 @@
     </row>
     <row r="12" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A12" s="5" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>17</v>
@@ -3806,7 +3802,7 @@
     </row>
     <row r="13" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A13" s="5" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="B13" s="5" t="s">
         <v>18</v>
@@ -3820,7 +3816,7 @@
     </row>
     <row r="14" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A14" s="5" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="B14" s="5" t="s">
         <v>19</v>
@@ -3834,7 +3830,7 @@
     </row>
     <row r="15" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A15" s="5" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="B15" s="5" t="s">
         <v>20</v>
@@ -3920,7 +3916,7 @@
         <v>32</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C2" s="5" t="s">
         <v>284</v>
@@ -3944,10 +3940,10 @@
         <v>289</v>
       </c>
       <c r="J2" s="5" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="K2" s="5" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.45">
@@ -3955,7 +3951,7 @@
         <v>41</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C3" s="5" t="s">
         <v>290</v>
@@ -3979,10 +3975,10 @@
         <v>295</v>
       </c>
       <c r="J3" s="5" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="K3" s="5" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="51.75" customHeight="1" x14ac:dyDescent="0.45">
@@ -3990,7 +3986,7 @@
         <v>49</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C4" s="5" t="s">
         <v>296</v>
@@ -4014,10 +4010,10 @@
         <v>301</v>
       </c>
       <c r="J4" s="5" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="K4" s="5" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="51.75" customHeight="1" x14ac:dyDescent="0.45">
@@ -4025,7 +4021,7 @@
         <v>56</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C5" s="5" t="s">
         <v>302</v>
@@ -4046,13 +4042,13 @@
         <v>306</v>
       </c>
       <c r="I5" s="10" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="J5" s="5" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="K5" s="5" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="51.75" customHeight="1" x14ac:dyDescent="0.45">
@@ -4060,7 +4056,7 @@
         <v>62</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C6" s="5" t="s">
         <v>307</v>
@@ -4084,10 +4080,10 @@
         <v>313</v>
       </c>
       <c r="J6" s="5" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="K6" s="5" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="51.75" customHeight="1" x14ac:dyDescent="0.45">
@@ -4095,7 +4091,7 @@
         <v>68</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>314</v>
@@ -4119,10 +4115,10 @@
         <v>319</v>
       </c>
       <c r="J7" s="5" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="K7" s="5" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="51.75" customHeight="1" x14ac:dyDescent="0.45"/>
@@ -4208,31 +4204,31 @@
         <v>328</v>
       </c>
       <c r="B2" s="5" t="s">
+        <v>387</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>360</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>388</v>
+      </c>
+      <c r="E2" s="5" t="s">
         <v>389</v>
       </c>
-      <c r="C2" s="5" t="s">
-        <v>362</v>
-      </c>
-      <c r="D2" s="5" t="s">
+      <c r="F2" s="5" t="s">
         <v>390</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="G2" s="5" t="s">
         <v>391</v>
       </c>
-      <c r="F2" s="5" t="s">
-        <v>392</v>
-      </c>
-      <c r="G2" s="5" t="s">
-        <v>393</v>
-      </c>
       <c r="H2" s="5" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="J2" s="5" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="K2" s="5" t="s">
         <v>331</v>
@@ -4244,31 +4240,31 @@
         <v>332</v>
       </c>
       <c r="B3" s="5" t="s">
+        <v>392</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>360</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>393</v>
+      </c>
+      <c r="E3" s="5" t="s">
         <v>394</v>
       </c>
-      <c r="C3" s="5" t="s">
-        <v>362</v>
-      </c>
-      <c r="D3" s="5" t="s">
+      <c r="F3" s="5" t="s">
         <v>395</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="G3" s="5" t="s">
         <v>396</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="H3" s="5" t="s">
         <v>397</v>
       </c>
-      <c r="G3" s="5" t="s">
-        <v>398</v>
-      </c>
-      <c r="H3" s="5" t="s">
-        <v>399</v>
-      </c>
       <c r="I3" s="5" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="J3" s="5" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="K3" s="5" t="s">
         <v>331</v>
@@ -4280,31 +4276,31 @@
         <v>333</v>
       </c>
       <c r="B4" s="5" t="s">
+        <v>398</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>362</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>399</v>
+      </c>
+      <c r="E4" s="5" t="s">
         <v>400</v>
       </c>
-      <c r="C4" s="5" t="s">
-        <v>364</v>
-      </c>
-      <c r="D4" s="5" t="s">
+      <c r="F4" s="5" t="s">
         <v>401</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="G4" s="5" t="s">
         <v>402</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="H4" s="5" t="s">
         <v>403</v>
       </c>
-      <c r="G4" s="5" t="s">
-        <v>404</v>
-      </c>
-      <c r="H4" s="5" t="s">
-        <v>405</v>
-      </c>
       <c r="I4" s="5" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="J4" s="5" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="K4" s="5" t="s">
         <v>331</v>
@@ -4316,31 +4312,31 @@
         <v>334</v>
       </c>
       <c r="B5" s="5" t="s">
+        <v>404</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>356</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>405</v>
+      </c>
+      <c r="E5" s="5" t="s">
         <v>406</v>
       </c>
-      <c r="C5" s="5" t="s">
-        <v>358</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>407</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>408</v>
-      </c>
       <c r="F5" s="5" t="s">
+        <v>414</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>415</v>
+      </c>
+      <c r="H5" s="5" t="s">
         <v>416</v>
-      </c>
-      <c r="G5" s="5" t="s">
-        <v>417</v>
-      </c>
-      <c r="H5" s="5" t="s">
-        <v>418</v>
       </c>
       <c r="I5" s="5" t="s">
         <v>330</v>
       </c>
       <c r="J5" s="5" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="K5" s="5" t="s">
         <v>331</v>
@@ -4352,28 +4348,28 @@
         <v>335</v>
       </c>
       <c r="B6" s="5" t="s">
+        <v>407</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>357</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>408</v>
+      </c>
+      <c r="E6" s="5" t="s">
         <v>409</v>
       </c>
-      <c r="C6" s="5" t="s">
-        <v>359</v>
-      </c>
-      <c r="D6" s="5" t="s">
+      <c r="F6" s="5" t="s">
         <v>410</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="G6" s="5" t="s">
         <v>411</v>
       </c>
-      <c r="F6" s="5" t="s">
+      <c r="H6" s="5" t="s">
         <v>412</v>
       </c>
-      <c r="G6" s="5" t="s">
-        <v>413</v>
-      </c>
-      <c r="H6" s="5" t="s">
-        <v>414</v>
-      </c>
       <c r="I6" s="5" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="J6" s="5" t="s">
         <v>330</v>
@@ -4447,35 +4443,35 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="25.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="23" t="s">
-        <v>388</v>
-      </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="23"/>
-      <c r="D1" s="23"/>
-      <c r="E1" s="23"/>
-      <c r="F1" s="23"/>
-      <c r="G1" s="23"/>
-      <c r="H1" s="23"/>
-      <c r="I1" s="23"/>
-      <c r="J1" s="23"/>
-      <c r="K1" s="23"/>
-      <c r="L1" s="23"/>
-      <c r="M1" s="23"/>
-      <c r="N1" s="23"/>
-      <c r="O1" s="23"/>
+      <c r="A1" s="18" t="s">
+        <v>386</v>
+      </c>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
+      <c r="I1" s="18"/>
+      <c r="J1" s="18"/>
+      <c r="K1" s="18"/>
+      <c r="L1" s="18"/>
+      <c r="M1" s="18"/>
+      <c r="N1" s="18"/>
+      <c r="O1" s="18"/>
     </row>
     <row r="2" spans="1:15" ht="14.65" thickBot="1" x14ac:dyDescent="0.5"/>
     <row r="3" spans="1:15" ht="21.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A3" s="26" t="s">
-        <v>384</v>
-      </c>
-      <c r="B3" s="26"/>
-      <c r="C3" s="26"/>
-      <c r="D3" s="26"/>
-      <c r="E3" s="26"/>
-      <c r="F3" s="26"/>
-      <c r="G3" s="26"/>
+      <c r="A3" s="21" t="s">
+        <v>382</v>
+      </c>
+      <c r="B3" s="21"/>
+      <c r="C3" s="21"/>
+      <c r="D3" s="21"/>
+      <c r="E3" s="21"/>
+      <c r="F3" s="21"/>
+      <c r="G3" s="21"/>
     </row>
     <row r="4" spans="1:15" ht="18" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A4" s="4" t="s">
@@ -4518,10 +4514,10 @@
     </row>
     <row r="7" spans="1:15" ht="18" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A7" s="4" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="B7" s="15" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="C7" s="15"/>
       <c r="D7" s="15"/>
@@ -4534,7 +4530,7 @@
         <v>341</v>
       </c>
       <c r="B8" s="15" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="C8" s="15"/>
       <c r="D8" s="15"/>
@@ -4544,7 +4540,7 @@
     </row>
     <row r="9" spans="1:15" ht="18" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A9" s="4" t="s">
-        <v>342</v>
+        <v>465</v>
       </c>
       <c r="B9" s="16">
         <v>46163</v>
@@ -4557,9 +4553,11 @@
     </row>
     <row r="10" spans="1:15" ht="18" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A10" s="4" t="s">
-        <v>343</v>
-      </c>
-      <c r="B10" s="16"/>
+        <v>466</v>
+      </c>
+      <c r="B10" s="16">
+        <v>46166</v>
+      </c>
       <c r="C10" s="15"/>
       <c r="D10" s="15"/>
       <c r="E10" s="15"/>
@@ -4568,170 +4566,167 @@
     </row>
     <row r="11" spans="1:15" ht="18" customHeight="1" thickTop="1" x14ac:dyDescent="0.45"/>
     <row r="12" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="A12" s="24" t="s">
+      <c r="A12" s="19" t="s">
+        <v>383</v>
+      </c>
+      <c r="B12" s="19"/>
+      <c r="C12" s="19"/>
+      <c r="E12" s="17" t="s">
         <v>385</v>
       </c>
-      <c r="B12" s="24"/>
-      <c r="C12" s="24"/>
-      <c r="E12" s="22" t="s">
-        <v>387</v>
-      </c>
-      <c r="F12" s="22"/>
-      <c r="G12" s="22"/>
+      <c r="F12" s="17"/>
+      <c r="G12" s="17"/>
     </row>
     <row r="13" spans="1:15" ht="21.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A13" s="11" t="s">
-        <v>344</v>
-      </c>
-      <c r="B13" s="17">
+        <v>342</v>
+      </c>
+      <c r="B13" s="22">
         <v>56</v>
       </c>
-      <c r="C13" s="17"/>
+      <c r="C13" s="22"/>
       <c r="E13" s="11" t="s">
-        <v>345</v>
-      </c>
-      <c r="F13" s="17">
+        <v>343</v>
+      </c>
+      <c r="F13" s="22">
         <v>5</v>
       </c>
-      <c r="G13" s="17"/>
-      <c r="I13" s="5" t="s">
-        <v>467</v>
-      </c>
+      <c r="G13" s="22"/>
     </row>
     <row r="14" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A14" s="11" t="s">
-        <v>346</v>
-      </c>
-      <c r="B14" s="17">
+        <v>344</v>
+      </c>
+      <c r="B14" s="22">
         <v>50</v>
       </c>
-      <c r="C14" s="17"/>
+      <c r="C14" s="22"/>
       <c r="E14" s="11" t="s">
-        <v>347</v>
-      </c>
-      <c r="F14" s="19">
+        <v>345</v>
+      </c>
+      <c r="F14" s="24">
         <v>0</v>
       </c>
-      <c r="G14" s="19"/>
+      <c r="G14" s="24"/>
     </row>
     <row r="15" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A15" s="11" t="s">
-        <v>348</v>
-      </c>
-      <c r="B15" s="21">
+        <v>346</v>
+      </c>
+      <c r="B15" s="23">
         <v>49</v>
       </c>
-      <c r="C15" s="21"/>
+      <c r="C15" s="23"/>
       <c r="E15" s="11" t="s">
         <v>330</v>
       </c>
-      <c r="F15" s="19">
+      <c r="F15" s="24">
         <v>1</v>
       </c>
-      <c r="G15" s="19"/>
+      <c r="G15" s="24"/>
     </row>
     <row r="16" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A16" s="11" t="s">
-        <v>349</v>
-      </c>
-      <c r="B16" s="19">
+        <v>347</v>
+      </c>
+      <c r="B16" s="24">
         <v>1</v>
       </c>
-      <c r="C16" s="19"/>
+      <c r="C16" s="24"/>
       <c r="E16" s="11" t="s">
-        <v>350</v>
-      </c>
-      <c r="F16" s="20">
+        <v>348</v>
+      </c>
+      <c r="F16" s="26">
         <v>2</v>
       </c>
-      <c r="G16" s="20"/>
+      <c r="G16" s="26"/>
     </row>
     <row r="17" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A17" s="11" t="s">
-        <v>351</v>
-      </c>
-      <c r="B17" s="17">
+        <v>349</v>
+      </c>
+      <c r="B17" s="22">
         <v>0</v>
       </c>
-      <c r="C17" s="17"/>
+      <c r="C17" s="22"/>
       <c r="E17" s="11" t="s">
-        <v>352</v>
-      </c>
-      <c r="F17" s="21">
+        <v>350</v>
+      </c>
+      <c r="F17" s="23">
         <v>2</v>
       </c>
-      <c r="G17" s="21"/>
+      <c r="G17" s="23"/>
     </row>
     <row r="18" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A18" s="11" t="s">
-        <v>353</v>
-      </c>
-      <c r="B18" s="17">
+        <v>351</v>
+      </c>
+      <c r="B18" s="22">
         <v>0</v>
       </c>
-      <c r="C18" s="17"/>
+      <c r="C18" s="22"/>
       <c r="E18" s="11" t="s">
         <v>331</v>
       </c>
-      <c r="F18" s="17">
+      <c r="F18" s="22">
         <v>5</v>
       </c>
-      <c r="G18" s="17"/>
+      <c r="G18" s="22"/>
     </row>
     <row r="19" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A19" s="11" t="s">
-        <v>354</v>
-      </c>
-      <c r="B19" s="18">
+        <v>352</v>
+      </c>
+      <c r="B19" s="25">
         <v>0.98</v>
       </c>
-      <c r="C19" s="18"/>
+      <c r="C19" s="25"/>
       <c r="E19" s="11" t="s">
-        <v>355</v>
-      </c>
-      <c r="F19" s="17">
+        <v>353</v>
+      </c>
+      <c r="F19" s="22">
         <v>0</v>
       </c>
-      <c r="G19" s="17"/>
+      <c r="G19" s="22"/>
     </row>
     <row r="20" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.45"/>
     <row r="21" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A21" s="25" t="s">
-        <v>386</v>
-      </c>
-      <c r="B21" s="25"/>
-      <c r="C21" s="25"/>
-      <c r="D21" s="25"/>
-      <c r="E21" s="25"/>
-      <c r="F21" s="25"/>
-      <c r="G21" s="25"/>
+      <c r="A21" s="20" t="s">
+        <v>384</v>
+      </c>
+      <c r="B21" s="20"/>
+      <c r="C21" s="20"/>
+      <c r="D21" s="20"/>
+      <c r="E21" s="20"/>
+      <c r="F21" s="20"/>
+      <c r="G21" s="20"/>
     </row>
     <row r="22" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A22" s="5" t="s">
         <v>322</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="D22" s="5" t="s">
+        <v>347</v>
+      </c>
+      <c r="E22" s="5" t="s">
         <v>349</v>
       </c>
-      <c r="E22" s="5" t="s">
+      <c r="F22" s="5" t="s">
         <v>351</v>
       </c>
-      <c r="F22" s="5" t="s">
-        <v>353</v>
-      </c>
       <c r="G22" s="5" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A23" s="5" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="B23" s="5">
         <v>6</v>
@@ -4777,7 +4772,7 @@
     </row>
     <row r="25" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A25" s="5" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="B25" s="5">
         <v>3</v>
@@ -4800,7 +4795,7 @@
     </row>
     <row r="26" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A26" s="5" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="B26" s="5">
         <v>4</v>
@@ -4823,7 +4818,7 @@
     </row>
     <row r="27" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A27" s="5" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="B27" s="5">
         <v>5</v>
@@ -4846,7 +4841,7 @@
     </row>
     <row r="28" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A28" s="5" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="B28" s="5">
         <v>5</v>
@@ -4869,7 +4864,7 @@
     </row>
     <row r="29" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A29" s="5" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="B29" s="5">
         <v>7</v>
@@ -4892,7 +4887,7 @@
     </row>
     <row r="30" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A30" s="5" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B30" s="5">
         <v>5</v>
@@ -4915,7 +4910,7 @@
     </row>
     <row r="31" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A31" s="5" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="B31" s="5">
         <v>6</v>
@@ -4940,6 +4935,16 @@
     <row r="33" ht="18" customHeight="1" x14ac:dyDescent="0.45"/>
   </sheetData>
   <mergeCells count="26">
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="F14:G14"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="F16:G16"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F18:G18"/>
+    <mergeCell ref="F19:G19"/>
     <mergeCell ref="E12:G12"/>
     <mergeCell ref="A1:O1"/>
     <mergeCell ref="A12:C12"/>
@@ -4956,16 +4961,6 @@
     <mergeCell ref="B14:C14"/>
     <mergeCell ref="B15:C15"/>
     <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="F14:G14"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="F16:G16"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="F18:G18"/>
-    <mergeCell ref="F19:G19"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -5057,10 +5052,10 @@
         <v>40</v>
       </c>
       <c r="J2" s="5" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="K2" s="5" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="51.75" customHeight="1" x14ac:dyDescent="0.45">
@@ -5092,10 +5087,10 @@
         <v>48</v>
       </c>
       <c r="J3" s="5" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="K3" s="5" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="51.75" customHeight="1" x14ac:dyDescent="0.45">
@@ -5127,10 +5122,10 @@
         <v>55</v>
       </c>
       <c r="J4" s="5" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="K4" s="5" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="51.75" customHeight="1" x14ac:dyDescent="0.45">
@@ -5162,10 +5157,10 @@
         <v>61</v>
       </c>
       <c r="J5" s="5" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="K5" s="5" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="51.75" customHeight="1" x14ac:dyDescent="0.45">
@@ -5197,10 +5192,10 @@
         <v>67</v>
       </c>
       <c r="J6" s="5" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="K6" s="5" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="51.75" customHeight="1" x14ac:dyDescent="0.45">
@@ -5229,13 +5224,13 @@
         <v>72</v>
       </c>
       <c r="I7" s="10" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="J7" s="5" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="K7" s="5" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
     </row>
   </sheetData>
@@ -5316,7 +5311,7 @@
         <v>32</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="C2" s="5" t="s">
         <v>73</v>
@@ -5340,10 +5335,10 @@
         <v>79</v>
       </c>
       <c r="J2" s="5" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="K2" s="5" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="51.75" customHeight="1" x14ac:dyDescent="0.45">
@@ -5351,7 +5346,7 @@
         <v>41</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="C3" s="5" t="s">
         <v>80</v>
@@ -5375,10 +5370,10 @@
         <v>85</v>
       </c>
       <c r="J3" s="5" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="K3" s="5" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="51.75" customHeight="1" x14ac:dyDescent="0.45">
@@ -5386,7 +5381,7 @@
         <v>49</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="C4" s="5" t="s">
         <v>80</v>
@@ -5410,10 +5405,10 @@
         <v>85</v>
       </c>
       <c r="J4" s="5" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="K4" s="5" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="51.75" customHeight="1" x14ac:dyDescent="0.45">
@@ -5421,7 +5416,7 @@
         <v>56</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="C5" s="5" t="s">
         <v>80</v>
@@ -5445,10 +5440,10 @@
         <v>85</v>
       </c>
       <c r="J5" s="5" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="K5" s="5" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="51.75" customHeight="1" x14ac:dyDescent="0.45">
@@ -5456,7 +5451,7 @@
         <v>62</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="C6" s="5" t="s">
         <v>80</v>
@@ -5480,10 +5475,10 @@
         <v>95</v>
       </c>
       <c r="J6" s="5" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="K6" s="5" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="51.75" customHeight="1" x14ac:dyDescent="0.45">
@@ -5491,7 +5486,7 @@
         <v>68</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>80</v>
@@ -5515,10 +5510,10 @@
         <v>95</v>
       </c>
       <c r="J7" s="5" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="K7" s="5" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="51.75" customHeight="1" x14ac:dyDescent="0.45">
@@ -5526,7 +5521,7 @@
         <v>99</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="C8" s="5" t="s">
         <v>80</v>
@@ -5550,10 +5545,10 @@
         <v>95</v>
       </c>
       <c r="J8" s="5" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="K8" s="5" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="51.75" customHeight="1" x14ac:dyDescent="0.45">
@@ -5561,7 +5556,7 @@
         <v>103</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="C9" s="5" t="s">
         <v>80</v>
@@ -5585,10 +5580,10 @@
         <v>95</v>
       </c>
       <c r="J9" s="5" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="K9" s="5" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="51.75" customHeight="1" x14ac:dyDescent="0.45">
@@ -5596,7 +5591,7 @@
         <v>107</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="C10" s="5" t="s">
         <v>80</v>
@@ -5620,10 +5615,10 @@
         <v>95</v>
       </c>
       <c r="J10" s="5" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="K10" s="5" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
     </row>
     <row r="11" spans="1:11" ht="51.75" customHeight="1" x14ac:dyDescent="0.45"/>
@@ -5705,7 +5700,7 @@
         <v>32</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C2" s="5" t="s">
         <v>110</v>
@@ -5729,10 +5724,10 @@
         <v>115</v>
       </c>
       <c r="J2" s="5" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="K2" s="5" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="57" x14ac:dyDescent="0.45">
@@ -5740,7 +5735,7 @@
         <v>41</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C3" s="5" t="s">
         <v>116</v>
@@ -5764,10 +5759,10 @@
         <v>121</v>
       </c>
       <c r="J3" s="5" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="K3" s="5" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="57" x14ac:dyDescent="0.45">
@@ -5775,7 +5770,7 @@
         <v>49</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C4" s="5" t="s">
         <v>122</v>
@@ -5799,10 +5794,10 @@
         <v>127</v>
       </c>
       <c r="J4" s="5" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="K4" s="5" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
     </row>
   </sheetData>
@@ -5907,10 +5902,10 @@
         <v>135</v>
       </c>
       <c r="J2" s="13" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="K2" s="13" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="42.75" x14ac:dyDescent="0.45">
@@ -5942,10 +5937,10 @@
         <v>142</v>
       </c>
       <c r="J3" s="13" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="K3" s="13" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="42.75" x14ac:dyDescent="0.45">
@@ -5977,10 +5972,10 @@
         <v>146</v>
       </c>
       <c r="J4" s="13" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="K4" s="13" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.45">
@@ -6012,10 +6007,10 @@
         <v>153</v>
       </c>
       <c r="J5" s="13" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="K5" s="13" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
     </row>
   </sheetData>
@@ -6119,10 +6114,10 @@
         <v>161</v>
       </c>
       <c r="J2" s="5" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="K2" s="5" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="51.75" customHeight="1" x14ac:dyDescent="0.45">
@@ -6154,10 +6149,10 @@
         <v>167</v>
       </c>
       <c r="J3" s="5" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="K3" s="5" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="51.75" customHeight="1" x14ac:dyDescent="0.45">
@@ -6189,10 +6184,10 @@
         <v>172</v>
       </c>
       <c r="J4" s="5" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="K4" s="5" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="51.75" customHeight="1" x14ac:dyDescent="0.45">
@@ -6224,10 +6219,10 @@
         <v>177</v>
       </c>
       <c r="J5" s="5" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="K5" s="5" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="51.75" customHeight="1" x14ac:dyDescent="0.45">
@@ -6259,10 +6254,10 @@
         <v>182</v>
       </c>
       <c r="J6" s="5" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="K6" s="5" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
     </row>
   </sheetData>
@@ -6344,7 +6339,7 @@
         <v>32</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="C2" s="5" t="s">
         <v>183</v>
@@ -6368,10 +6363,10 @@
         <v>189</v>
       </c>
       <c r="J2" s="5" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="K2" s="5" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="51.75" customHeight="1" x14ac:dyDescent="0.45">
@@ -6379,7 +6374,7 @@
         <v>41</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="C3" s="5" t="s">
         <v>190</v>
@@ -6403,10 +6398,10 @@
         <v>194</v>
       </c>
       <c r="J3" s="5" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="K3" s="5" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="51.75" customHeight="1" x14ac:dyDescent="0.45">
@@ -6414,7 +6409,7 @@
         <v>49</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="C4" s="5" t="s">
         <v>190</v>
@@ -6438,10 +6433,10 @@
         <v>199</v>
       </c>
       <c r="J4" s="5" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="K4" s="5" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="51.75" customHeight="1" x14ac:dyDescent="0.45">
@@ -6449,7 +6444,7 @@
         <v>56</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="C5" s="5" t="s">
         <v>190</v>
@@ -6473,10 +6468,10 @@
         <v>204</v>
       </c>
       <c r="J5" s="5" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="K5" s="5" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="51.75" customHeight="1" x14ac:dyDescent="0.45">
@@ -6484,7 +6479,7 @@
         <v>62</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="C6" s="5" t="s">
         <v>205</v>
@@ -6508,10 +6503,10 @@
         <v>210</v>
       </c>
       <c r="J6" s="5" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="K6" s="5" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
     </row>
   </sheetData>
@@ -6602,7 +6597,7 @@
         <v>32</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="C2" s="5" t="s">
         <v>211</v>
@@ -6626,10 +6621,10 @@
         <v>216</v>
       </c>
       <c r="J2" s="5" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="K2" s="5" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="51" customHeight="1" x14ac:dyDescent="0.45">
@@ -6637,7 +6632,7 @@
         <v>41</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="C3" s="5" t="s">
         <v>217</v>
@@ -6661,10 +6656,10 @@
         <v>223</v>
       </c>
       <c r="J3" s="5" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="K3" s="5" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="51.75" customHeight="1" x14ac:dyDescent="0.45">
@@ -6672,7 +6667,7 @@
         <v>49</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="C4" s="5" t="s">
         <v>224</v>
@@ -6696,10 +6691,10 @@
         <v>230</v>
       </c>
       <c r="J4" s="5" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="K4" s="5" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="51.75" customHeight="1" x14ac:dyDescent="0.45">
@@ -6707,7 +6702,7 @@
         <v>56</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="C5" s="5" t="s">
         <v>231</v>
@@ -6731,10 +6726,10 @@
         <v>237</v>
       </c>
       <c r="J5" s="5" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="K5" s="5" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="51.75" customHeight="1" x14ac:dyDescent="0.45">
@@ -6742,7 +6737,7 @@
         <v>62</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="C6" s="5" t="s">
         <v>238</v>
@@ -6766,10 +6761,10 @@
         <v>242</v>
       </c>
       <c r="J6" s="5" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="K6" s="5" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="51.75" customHeight="1" x14ac:dyDescent="0.45">
@@ -6777,7 +6772,7 @@
         <v>68</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>243</v>
@@ -6801,10 +6796,10 @@
         <v>247</v>
       </c>
       <c r="J7" s="5" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="K7" s="5" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="51.75" customHeight="1" x14ac:dyDescent="0.45">
@@ -6812,7 +6807,7 @@
         <v>99</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="C8" s="5" t="s">
         <v>248</v>
@@ -6836,10 +6831,10 @@
         <v>252</v>
       </c>
       <c r="J8" s="5" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="K8" s="5" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="51.75" customHeight="1" x14ac:dyDescent="0.45"/>
@@ -6922,7 +6917,7 @@
         <v>32</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="C2" s="5" t="s">
         <v>253</v>
@@ -6946,10 +6941,10 @@
         <v>258</v>
       </c>
       <c r="J2" s="5" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="K2" s="5" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="42.75" customHeight="1" x14ac:dyDescent="0.45">
@@ -6957,7 +6952,7 @@
         <v>41</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="C3" s="5" t="s">
         <v>259</v>
@@ -6981,10 +6976,10 @@
         <v>264</v>
       </c>
       <c r="J3" s="5" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="K3" s="5" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="51.75" customHeight="1" x14ac:dyDescent="0.45">
@@ -6992,7 +6987,7 @@
         <v>49</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="C4" s="5" t="s">
         <v>265</v>
@@ -7016,10 +7011,10 @@
         <v>270</v>
       </c>
       <c r="J4" s="5" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="K4" s="5" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="51.75" customHeight="1" x14ac:dyDescent="0.45">
@@ -7027,7 +7022,7 @@
         <v>56</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="C5" s="5" t="s">
         <v>271</v>
@@ -7051,10 +7046,10 @@
         <v>276</v>
       </c>
       <c r="J5" s="5" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="K5" s="5" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="51.75" customHeight="1" x14ac:dyDescent="0.45">
@@ -7062,7 +7057,7 @@
         <v>62</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="C6" s="5" t="s">
         <v>277</v>
@@ -7086,10 +7081,10 @@
         <v>283</v>
       </c>
       <c r="J6" s="5" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="K6" s="5" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="51.75" customHeight="1" x14ac:dyDescent="0.45"/>

--- a/DarazNP - QA/Daraz_Nepal_QA_TestPlan.xlsx
+++ b/DarazNP - QA/Daraz_Nepal_QA_TestPlan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\QA\DarazNP - QA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43EB3697-1F48-4001-B821-12B2DE4E3B3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B74C9749-543E-4CDF-8E23-6F02B3C549C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" tabRatio="500" firstSheet="7" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1675,7 +1675,7 @@
     <t>Test Start Date(Manual)</t>
   </si>
   <si>
-    <t>Test End Date(Manual)</t>
+    <t>Test End Date</t>
   </si>
 </sst>
 </file>
@@ -1943,10 +1943,19 @@
     <xf numFmtId="0" fontId="5" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="3" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="2" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1961,22 +1970,13 @@
     <xf numFmtId="0" fontId="4" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="3" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2176,40 +2176,6 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color rgb="FFBFBFBF"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -2307,6 +2273,45 @@
     </dxf>
     <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -2907,16 +2912,11 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border outline="0">
+        <top style="thin">
+          <color rgb="FFBFBFBF"/>
+        </top>
+      </border>
     </dxf>
     <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -3238,230 +3238,230 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{DF488C28-E294-4FC5-B88E-45C03C2670F4}" name="Table1" displayName="Table1" ref="A6:D15" totalsRowShown="0" headerRowDxfId="150" dataDxfId="149" headerRowCellStyle="Normal" dataCellStyle="Normal">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{DF488C28-E294-4FC5-B88E-45C03C2670F4}" name="Table1" displayName="Table1" ref="A6:D15" totalsRowShown="0" headerRowDxfId="153" dataDxfId="152" headerRowCellStyle="Normal" dataCellStyle="Normal">
   <autoFilter ref="A6:D15" xr:uid="{DF488C28-E294-4FC5-B88E-45C03C2670F4}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{33DAD9C3-616B-4530-8A09-EA2123236523}" name="Test Scenario ID" dataDxfId="148" dataCellStyle="Normal"/>
-    <tableColumn id="2" xr3:uid="{930616D5-B050-48B4-BC07-2F47085FC38F}" name="Test Scenario Description" dataDxfId="147" dataCellStyle="Normal"/>
-    <tableColumn id="3" xr3:uid="{81B53550-0158-483A-8072-7528B8991C66}" name="Priority" dataDxfId="146" dataCellStyle="Normal"/>
-    <tableColumn id="4" xr3:uid="{4E0C06DA-320E-4E35-ABDA-665C29E66893}" name="Number of Test Cases" dataDxfId="145" dataCellStyle="Normal"/>
+    <tableColumn id="1" xr3:uid="{33DAD9C3-616B-4530-8A09-EA2123236523}" name="Test Scenario ID" dataDxfId="151" dataCellStyle="Normal"/>
+    <tableColumn id="2" xr3:uid="{930616D5-B050-48B4-BC07-2F47085FC38F}" name="Test Scenario Description" dataDxfId="150" dataCellStyle="Normal"/>
+    <tableColumn id="3" xr3:uid="{81B53550-0158-483A-8072-7528B8991C66}" name="Priority" dataDxfId="149" dataCellStyle="Normal"/>
+    <tableColumn id="4" xr3:uid="{4E0C06DA-320E-4E35-ABDA-665C29E66893}" name="Number of Test Cases" dataDxfId="148" dataCellStyle="Normal"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{7325E5B5-E902-49F8-AEF5-E792747C2CB9}" name="Table10" displayName="Table10" ref="A1:K7" totalsRowShown="0" headerRowDxfId="53" dataDxfId="52">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{7325E5B5-E902-49F8-AEF5-E792747C2CB9}" name="Table10" displayName="Table10" ref="A1:K7" totalsRowShown="0" headerRowDxfId="43" dataDxfId="42">
   <autoFilter ref="A1:K7" xr:uid="{7325E5B5-E902-49F8-AEF5-E792747C2CB9}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{3E6BAD88-77A0-44B6-9F2B-5FBB3CE091F2}" name="Test Case ID" dataDxfId="51"/>
-    <tableColumn id="2" xr3:uid="{B6334C76-74C3-494E-9AD8-250558808943}" name="Test Scenario" dataDxfId="50"/>
-    <tableColumn id="3" xr3:uid="{C0ABB8E4-BF9C-4E33-B022-CF3A4DE60B64}" name="Test Case Title" dataDxfId="49"/>
-    <tableColumn id="4" xr3:uid="{9B154E74-7F46-4204-9D85-09FD7A515891}" name="Test Description" dataDxfId="48"/>
-    <tableColumn id="5" xr3:uid="{F1A47D99-EDEF-4DEF-9E20-A7FD7E80C2FF}" name="Precondition" dataDxfId="47"/>
-    <tableColumn id="6" xr3:uid="{B6883181-BD4B-46FB-AA46-5EAB92EFDD14}" name="Test Data" dataDxfId="46"/>
-    <tableColumn id="7" xr3:uid="{CDC1D1E1-7F31-4F2F-A9D6-B5BB49DB18D2}" name="Test Step" dataDxfId="45"/>
-    <tableColumn id="8" xr3:uid="{4EC38E01-73BC-4A40-A90C-FBC00297BCCB}" name="Post Condition" dataDxfId="44"/>
-    <tableColumn id="9" xr3:uid="{8B71CA62-1B8D-4F3C-8F1C-80F149DDCD86}" name="Expected Result" dataDxfId="43"/>
-    <tableColumn id="10" xr3:uid="{2758D08A-14A0-421E-93F0-A1D3EED326FD}" name="Actual Result" dataDxfId="42"/>
-    <tableColumn id="11" xr3:uid="{D4909B32-B834-474B-8873-CE83A7F95DED}" name="Status" dataDxfId="41"/>
+    <tableColumn id="1" xr3:uid="{3E6BAD88-77A0-44B6-9F2B-5FBB3CE091F2}" name="Test Case ID" dataDxfId="41"/>
+    <tableColumn id="2" xr3:uid="{B6334C76-74C3-494E-9AD8-250558808943}" name="Test Scenario" dataDxfId="40"/>
+    <tableColumn id="3" xr3:uid="{C0ABB8E4-BF9C-4E33-B022-CF3A4DE60B64}" name="Test Case Title" dataDxfId="39"/>
+    <tableColumn id="4" xr3:uid="{9B154E74-7F46-4204-9D85-09FD7A515891}" name="Test Description" dataDxfId="38"/>
+    <tableColumn id="5" xr3:uid="{F1A47D99-EDEF-4DEF-9E20-A7FD7E80C2FF}" name="Precondition" dataDxfId="37"/>
+    <tableColumn id="6" xr3:uid="{B6883181-BD4B-46FB-AA46-5EAB92EFDD14}" name="Test Data" dataDxfId="36"/>
+    <tableColumn id="7" xr3:uid="{CDC1D1E1-7F31-4F2F-A9D6-B5BB49DB18D2}" name="Test Step" dataDxfId="35"/>
+    <tableColumn id="8" xr3:uid="{4EC38E01-73BC-4A40-A90C-FBC00297BCCB}" name="Post Condition" dataDxfId="34"/>
+    <tableColumn id="9" xr3:uid="{8B71CA62-1B8D-4F3C-8F1C-80F149DDCD86}" name="Expected Result" dataDxfId="33"/>
+    <tableColumn id="10" xr3:uid="{2758D08A-14A0-421E-93F0-A1D3EED326FD}" name="Actual Result" dataDxfId="32"/>
+    <tableColumn id="11" xr3:uid="{D4909B32-B834-474B-8873-CE83A7F95DED}" name="Status" dataDxfId="31"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{074B61AA-834B-4987-8591-EFE949C0CD3E}" name="Table11" displayName="Table11" ref="A1:L6" totalsRowShown="0" headerRowDxfId="40" dataDxfId="39">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{074B61AA-834B-4987-8591-EFE949C0CD3E}" name="Table11" displayName="Table11" ref="A1:L6" totalsRowShown="0" headerRowDxfId="30" dataDxfId="29">
   <autoFilter ref="A1:L6" xr:uid="{074B61AA-834B-4987-8591-EFE949C0CD3E}"/>
   <tableColumns count="12">
-    <tableColumn id="1" xr3:uid="{2E0BA05E-6B29-48D5-8C89-726D7682792E}" name="Bug_ID" dataDxfId="38"/>
-    <tableColumn id="2" xr3:uid="{4D01CBE5-0889-4880-92D7-4B66BC182ECB}" name="TC_ID" dataDxfId="37"/>
-    <tableColumn id="3" xr3:uid="{982AC477-4942-498F-B937-BBBFAD3FE9B0}" name="Module" dataDxfId="36"/>
-    <tableColumn id="4" xr3:uid="{45C656C2-F54B-4624-BEE7-F4B8A9A3F7AA}" name="Bug Title" dataDxfId="35"/>
-    <tableColumn id="5" xr3:uid="{5A4A270F-8EE2-456D-8096-C57A552FA8BD}" name="Description" dataDxfId="34"/>
-    <tableColumn id="6" xr3:uid="{5211538C-C43F-4AE0-A40C-4517593D85B8}" name="Steps to Reproduce" dataDxfId="33"/>
-    <tableColumn id="7" xr3:uid="{0D61D290-BC8B-4DAB-B115-362A2EC84928}" name="Expected Result" dataDxfId="32"/>
-    <tableColumn id="8" xr3:uid="{7C9A10CE-DFC8-4284-B52F-67B1076DE1F2}" name="Actual Result" dataDxfId="31"/>
-    <tableColumn id="9" xr3:uid="{A2A09C9A-0EC4-4EEB-8207-4D4AD9E6C2FE}" name="Severity" dataDxfId="30"/>
-    <tableColumn id="10" xr3:uid="{812B3DBC-B5F8-4461-8B42-A270EC894AB1}" name="Priority" dataDxfId="29"/>
-    <tableColumn id="11" xr3:uid="{84506A51-F862-4873-B24D-6E470DF7E85E}" name="Status" dataDxfId="28"/>
-    <tableColumn id="12" xr3:uid="{98CA703C-ECC2-42FB-AB7E-B2461D8721F0}" name="Screenshot/Notes" dataDxfId="27"/>
+    <tableColumn id="1" xr3:uid="{2E0BA05E-6B29-48D5-8C89-726D7682792E}" name="Bug_ID" dataDxfId="28"/>
+    <tableColumn id="2" xr3:uid="{4D01CBE5-0889-4880-92D7-4B66BC182ECB}" name="TC_ID" dataDxfId="27"/>
+    <tableColumn id="3" xr3:uid="{982AC477-4942-498F-B937-BBBFAD3FE9B0}" name="Module" dataDxfId="26"/>
+    <tableColumn id="4" xr3:uid="{45C656C2-F54B-4624-BEE7-F4B8A9A3F7AA}" name="Bug Title" dataDxfId="25"/>
+    <tableColumn id="5" xr3:uid="{5A4A270F-8EE2-456D-8096-C57A552FA8BD}" name="Description" dataDxfId="24"/>
+    <tableColumn id="6" xr3:uid="{5211538C-C43F-4AE0-A40C-4517593D85B8}" name="Steps to Reproduce" dataDxfId="23"/>
+    <tableColumn id="7" xr3:uid="{0D61D290-BC8B-4DAB-B115-362A2EC84928}" name="Expected Result" dataDxfId="22"/>
+    <tableColumn id="8" xr3:uid="{7C9A10CE-DFC8-4284-B52F-67B1076DE1F2}" name="Actual Result" dataDxfId="21"/>
+    <tableColumn id="9" xr3:uid="{A2A09C9A-0EC4-4EEB-8207-4D4AD9E6C2FE}" name="Severity" dataDxfId="20"/>
+    <tableColumn id="10" xr3:uid="{812B3DBC-B5F8-4461-8B42-A270EC894AB1}" name="Priority" dataDxfId="19"/>
+    <tableColumn id="11" xr3:uid="{84506A51-F862-4873-B24D-6E470DF7E85E}" name="Status" dataDxfId="18"/>
+    <tableColumn id="12" xr3:uid="{98CA703C-ECC2-42FB-AB7E-B2461D8721F0}" name="Screenshot/Notes" dataDxfId="17"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{B5F3787F-2FE5-47F0-A53F-BE14C9EDF880}" name="Table12" displayName="Table12" ref="A22:G31" totalsRowShown="0" headerRowDxfId="26" dataDxfId="25" tableBorderDxfId="24">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{B5F3787F-2FE5-47F0-A53F-BE14C9EDF880}" name="Table12" displayName="Table12" ref="A22:G31" totalsRowShown="0" headerRowDxfId="163" dataDxfId="162" tableBorderDxfId="161">
   <autoFilter ref="A22:G31" xr:uid="{B5F3787F-2FE5-47F0-A53F-BE14C9EDF880}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{9F53F743-51DF-481F-9F33-6444B7379A49}" name="Module" dataDxfId="23"/>
-    <tableColumn id="2" xr3:uid="{8809AAEF-A8F9-436C-8EB8-D71DC356BE56}" name="Total TCs" dataDxfId="22"/>
-    <tableColumn id="3" xr3:uid="{938B6847-EE17-4CDD-B2A0-CF0886EE64B8}" name="Pass" dataDxfId="21"/>
-    <tableColumn id="4" xr3:uid="{4F4A2014-C80D-4909-AADC-157B9CB87F8F}" name="Fail" dataDxfId="20"/>
-    <tableColumn id="5" xr3:uid="{BE788EF4-5FDE-4EB6-B750-431A6DA3708D}" name="Blocked" dataDxfId="19"/>
-    <tableColumn id="6" xr3:uid="{56E5F7D1-FE02-40AD-8B69-C21E5C9D2099}" name="Not Executed" dataDxfId="18"/>
-    <tableColumn id="7" xr3:uid="{0EEA2BFA-1D98-4AB4-9C6E-502E972DD0F6}" name="Pass Rate" dataDxfId="17"/>
+    <tableColumn id="1" xr3:uid="{9F53F743-51DF-481F-9F33-6444B7379A49}" name="Module" dataDxfId="160"/>
+    <tableColumn id="2" xr3:uid="{8809AAEF-A8F9-436C-8EB8-D71DC356BE56}" name="Total TCs" dataDxfId="159"/>
+    <tableColumn id="3" xr3:uid="{938B6847-EE17-4CDD-B2A0-CF0886EE64B8}" name="Pass" dataDxfId="158"/>
+    <tableColumn id="4" xr3:uid="{4F4A2014-C80D-4909-AADC-157B9CB87F8F}" name="Fail" dataDxfId="157"/>
+    <tableColumn id="5" xr3:uid="{BE788EF4-5FDE-4EB6-B750-431A6DA3708D}" name="Blocked" dataDxfId="156"/>
+    <tableColumn id="6" xr3:uid="{56E5F7D1-FE02-40AD-8B69-C21E5C9D2099}" name="Not Executed" dataDxfId="155"/>
+    <tableColumn id="7" xr3:uid="{0EEA2BFA-1D98-4AB4-9C6E-502E972DD0F6}" name="Pass Rate" dataDxfId="154"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{4D72BE03-3C67-483F-A000-0CB99AE08007}" name="Table2" displayName="Table2" ref="A1:K7" totalsRowShown="0" headerRowDxfId="144" dataDxfId="143">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{4D72BE03-3C67-483F-A000-0CB99AE08007}" name="Table2" displayName="Table2" ref="A1:K7" totalsRowShown="0" headerRowDxfId="147" dataDxfId="146">
   <autoFilter ref="A1:K7" xr:uid="{4D72BE03-3C67-483F-A000-0CB99AE08007}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{DC300589-A232-46E8-8D34-43EA76119908}" name="Test Case ID" dataDxfId="142"/>
-    <tableColumn id="2" xr3:uid="{96321DA6-69B9-4285-96FB-F624E3C3A963}" name="Test Scenario" dataDxfId="141"/>
-    <tableColumn id="3" xr3:uid="{47B1BA56-1BCF-45B6-B32B-B5379B2C21C2}" name="Test Case Title" dataDxfId="140"/>
-    <tableColumn id="4" xr3:uid="{C36FE4A9-C732-4047-A84B-CBFDF06E1798}" name="Test Description" dataDxfId="139"/>
-    <tableColumn id="5" xr3:uid="{D1518DD6-352E-4530-B986-D864E93A5AC8}" name="Precondition" dataDxfId="138"/>
-    <tableColumn id="6" xr3:uid="{8B4D31E2-8543-4172-9800-778AC567D164}" name="Test Data" dataDxfId="137"/>
-    <tableColumn id="7" xr3:uid="{CDA134EC-16A7-4594-9E02-221402834F08}" name="Test Step" dataDxfId="136"/>
-    <tableColumn id="8" xr3:uid="{1B527B44-6496-4F0D-A56D-4413FF4DDDA2}" name="Post Condition" dataDxfId="135"/>
-    <tableColumn id="9" xr3:uid="{B9389CBA-79E5-4A58-9516-26D20F6CBA6E}" name="Expected Result" dataDxfId="134"/>
-    <tableColumn id="10" xr3:uid="{52125505-5EBF-4612-93D2-682D2A1590E0}" name="Actual Result" dataDxfId="133"/>
-    <tableColumn id="11" xr3:uid="{169FE3A8-8576-4034-B520-E3C132891BF5}" name="Status" dataDxfId="132"/>
+    <tableColumn id="1" xr3:uid="{DC300589-A232-46E8-8D34-43EA76119908}" name="Test Case ID" dataDxfId="145"/>
+    <tableColumn id="2" xr3:uid="{96321DA6-69B9-4285-96FB-F624E3C3A963}" name="Test Scenario" dataDxfId="144"/>
+    <tableColumn id="3" xr3:uid="{47B1BA56-1BCF-45B6-B32B-B5379B2C21C2}" name="Test Case Title" dataDxfId="143"/>
+    <tableColumn id="4" xr3:uid="{C36FE4A9-C732-4047-A84B-CBFDF06E1798}" name="Test Description" dataDxfId="142"/>
+    <tableColumn id="5" xr3:uid="{D1518DD6-352E-4530-B986-D864E93A5AC8}" name="Precondition" dataDxfId="141"/>
+    <tableColumn id="6" xr3:uid="{8B4D31E2-8543-4172-9800-778AC567D164}" name="Test Data" dataDxfId="140"/>
+    <tableColumn id="7" xr3:uid="{CDA134EC-16A7-4594-9E02-221402834F08}" name="Test Step" dataDxfId="139"/>
+    <tableColumn id="8" xr3:uid="{1B527B44-6496-4F0D-A56D-4413FF4DDDA2}" name="Post Condition" dataDxfId="138"/>
+    <tableColumn id="9" xr3:uid="{B9389CBA-79E5-4A58-9516-26D20F6CBA6E}" name="Expected Result" dataDxfId="137"/>
+    <tableColumn id="10" xr3:uid="{52125505-5EBF-4612-93D2-682D2A1590E0}" name="Actual Result" dataDxfId="136"/>
+    <tableColumn id="11" xr3:uid="{169FE3A8-8576-4034-B520-E3C132891BF5}" name="Status" dataDxfId="135"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{485A2C55-6434-4192-8808-9E3314484566}" name="Table3" displayName="Table3" ref="A1:K10" totalsRowShown="0" headerRowDxfId="131" dataDxfId="130">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{485A2C55-6434-4192-8808-9E3314484566}" name="Table3" displayName="Table3" ref="A1:K10" totalsRowShown="0" headerRowDxfId="134" dataDxfId="133">
   <autoFilter ref="A1:K10" xr:uid="{485A2C55-6434-4192-8808-9E3314484566}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{961A2C21-4B0E-4E55-850D-8F76158E605A}" name="Test Case ID" dataDxfId="129"/>
-    <tableColumn id="2" xr3:uid="{091711FE-D3C8-4930-B519-8CC8A3B55476}" name="Test Scenario" dataDxfId="128"/>
-    <tableColumn id="3" xr3:uid="{88BABBCB-4F52-4C8E-B0AF-A7B1FEA920E1}" name="Test Case Title" dataDxfId="127"/>
-    <tableColumn id="4" xr3:uid="{89C7C9C1-F533-4481-A1AA-3D2ACF79367C}" name="Test Description" dataDxfId="126"/>
-    <tableColumn id="5" xr3:uid="{7E9B2060-966D-4E6E-87D8-0A35654D3D31}" name="Precondition" dataDxfId="125"/>
-    <tableColumn id="6" xr3:uid="{8212B4F5-4682-42D4-98D2-666EB7851034}" name="Test Data" dataDxfId="124"/>
-    <tableColumn id="7" xr3:uid="{C27ADF5D-D13B-4776-B1DB-99BAC727A1EF}" name="Test Step" dataDxfId="123"/>
-    <tableColumn id="8" xr3:uid="{87D91BD6-44DB-42EC-A509-CF909B0841C6}" name="Post Condition" dataDxfId="122"/>
-    <tableColumn id="9" xr3:uid="{CF0F8DF7-50EC-4BF7-9A2B-B588E2C6AD3C}" name="Expected Result" dataDxfId="121"/>
-    <tableColumn id="10" xr3:uid="{28E800BE-C6F2-40A9-92FE-FB97DA376781}" name="Actual Result" dataDxfId="120"/>
-    <tableColumn id="11" xr3:uid="{A019A1D5-1AC2-4238-9C78-8D26EEBABBDD}" name="Status" dataDxfId="119"/>
+    <tableColumn id="1" xr3:uid="{961A2C21-4B0E-4E55-850D-8F76158E605A}" name="Test Case ID" dataDxfId="132"/>
+    <tableColumn id="2" xr3:uid="{091711FE-D3C8-4930-B519-8CC8A3B55476}" name="Test Scenario" dataDxfId="131"/>
+    <tableColumn id="3" xr3:uid="{88BABBCB-4F52-4C8E-B0AF-A7B1FEA920E1}" name="Test Case Title" dataDxfId="130"/>
+    <tableColumn id="4" xr3:uid="{89C7C9C1-F533-4481-A1AA-3D2ACF79367C}" name="Test Description" dataDxfId="129"/>
+    <tableColumn id="5" xr3:uid="{7E9B2060-966D-4E6E-87D8-0A35654D3D31}" name="Precondition" dataDxfId="128"/>
+    <tableColumn id="6" xr3:uid="{8212B4F5-4682-42D4-98D2-666EB7851034}" name="Test Data" dataDxfId="127"/>
+    <tableColumn id="7" xr3:uid="{C27ADF5D-D13B-4776-B1DB-99BAC727A1EF}" name="Test Step" dataDxfId="126"/>
+    <tableColumn id="8" xr3:uid="{87D91BD6-44DB-42EC-A509-CF909B0841C6}" name="Post Condition" dataDxfId="125"/>
+    <tableColumn id="9" xr3:uid="{CF0F8DF7-50EC-4BF7-9A2B-B588E2C6AD3C}" name="Expected Result" dataDxfId="124"/>
+    <tableColumn id="10" xr3:uid="{28E800BE-C6F2-40A9-92FE-FB97DA376781}" name="Actual Result" dataDxfId="123"/>
+    <tableColumn id="11" xr3:uid="{A019A1D5-1AC2-4238-9C78-8D26EEBABBDD}" name="Status" dataDxfId="122"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{CDD8D6C6-33F1-4988-A8DE-6D9CC0E8CF5A}" name="Table4" displayName="Table4" ref="A1:K4" totalsRowShown="0" headerRowDxfId="118" dataDxfId="117">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{CDD8D6C6-33F1-4988-A8DE-6D9CC0E8CF5A}" name="Table4" displayName="Table4" ref="A1:K4" totalsRowShown="0" headerRowDxfId="121" dataDxfId="120">
   <autoFilter ref="A1:K4" xr:uid="{CDD8D6C6-33F1-4988-A8DE-6D9CC0E8CF5A}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{30F17F19-8468-4A66-86EF-0BD83413ACA1}" name="Test Case ID" dataDxfId="116"/>
-    <tableColumn id="2" xr3:uid="{4A6BE90C-FDB5-4937-A0BB-FD1D07A1E264}" name="Test Scenario" dataDxfId="115"/>
-    <tableColumn id="3" xr3:uid="{A81A0D12-E511-4B28-B531-BA483F89581B}" name="Test Case Title" dataDxfId="114"/>
-    <tableColumn id="4" xr3:uid="{53B96AA9-7E95-49E4-A854-6D23E07EB42E}" name="Test Description" dataDxfId="113"/>
-    <tableColumn id="5" xr3:uid="{43B4D6A6-A260-4A56-B9E0-614CAA640920}" name="Precondition" dataDxfId="112"/>
-    <tableColumn id="6" xr3:uid="{125F2F89-B04E-4C4D-B84C-C5971AA23E32}" name="Test Data" dataDxfId="111"/>
-    <tableColumn id="7" xr3:uid="{532C8225-844B-43DE-B1D4-C10DDE0F4A7C}" name="Test Step" dataDxfId="110"/>
-    <tableColumn id="8" xr3:uid="{B349F424-2BCB-47BB-8B8D-7325C04BE2E2}" name="Post Condition" dataDxfId="109"/>
-    <tableColumn id="9" xr3:uid="{74D85BD0-D32D-46A4-9A02-3587A682A2A5}" name="Expected Result" dataDxfId="108"/>
-    <tableColumn id="10" xr3:uid="{16D75875-4017-4E31-BEF6-C8B6145CA67A}" name="Actual Result" dataDxfId="107"/>
-    <tableColumn id="11" xr3:uid="{6B9A5924-AE80-4BC1-AC2A-514E412DBC11}" name="Status" dataDxfId="106"/>
+    <tableColumn id="1" xr3:uid="{30F17F19-8468-4A66-86EF-0BD83413ACA1}" name="Test Case ID" dataDxfId="119"/>
+    <tableColumn id="2" xr3:uid="{4A6BE90C-FDB5-4937-A0BB-FD1D07A1E264}" name="Test Scenario" dataDxfId="118"/>
+    <tableColumn id="3" xr3:uid="{A81A0D12-E511-4B28-B531-BA483F89581B}" name="Test Case Title" dataDxfId="117"/>
+    <tableColumn id="4" xr3:uid="{53B96AA9-7E95-49E4-A854-6D23E07EB42E}" name="Test Description" dataDxfId="116"/>
+    <tableColumn id="5" xr3:uid="{43B4D6A6-A260-4A56-B9E0-614CAA640920}" name="Precondition" dataDxfId="115"/>
+    <tableColumn id="6" xr3:uid="{125F2F89-B04E-4C4D-B84C-C5971AA23E32}" name="Test Data" dataDxfId="114"/>
+    <tableColumn id="7" xr3:uid="{532C8225-844B-43DE-B1D4-C10DDE0F4A7C}" name="Test Step" dataDxfId="113"/>
+    <tableColumn id="8" xr3:uid="{B349F424-2BCB-47BB-8B8D-7325C04BE2E2}" name="Post Condition" dataDxfId="112"/>
+    <tableColumn id="9" xr3:uid="{74D85BD0-D32D-46A4-9A02-3587A682A2A5}" name="Expected Result" dataDxfId="111"/>
+    <tableColumn id="10" xr3:uid="{16D75875-4017-4E31-BEF6-C8B6145CA67A}" name="Actual Result" dataDxfId="110"/>
+    <tableColumn id="11" xr3:uid="{6B9A5924-AE80-4BC1-AC2A-514E412DBC11}" name="Status" dataDxfId="109"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{2E3F6B91-1F8B-4FE1-A0AC-D1A0FB7AA9CF}" name="Table5" displayName="Table5" ref="A1:K5" totalsRowShown="0" headerRowDxfId="105" dataDxfId="104" tableBorderDxfId="103">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{2E3F6B91-1F8B-4FE1-A0AC-D1A0FB7AA9CF}" name="Table5" displayName="Table5" ref="A1:K5" totalsRowShown="0" headerRowDxfId="108" dataDxfId="107" tableBorderDxfId="106">
   <autoFilter ref="A1:K5" xr:uid="{2E3F6B91-1F8B-4FE1-A0AC-D1A0FB7AA9CF}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{6876B7D9-AED4-40A7-9B3F-EAAE7EC27F19}" name="Test Case ID" dataDxfId="102"/>
-    <tableColumn id="2" xr3:uid="{586F0A72-FB20-402D-B906-57CEC15B5844}" name="Test Scenario" dataDxfId="101"/>
-    <tableColumn id="3" xr3:uid="{FD20C9B8-3526-43CA-8EF7-13306F6F1E73}" name="Test Case Title" dataDxfId="100"/>
-    <tableColumn id="4" xr3:uid="{745A2EB8-ABE5-4979-B5E6-271B46F7EF61}" name="Test Description" dataDxfId="99"/>
-    <tableColumn id="5" xr3:uid="{32B27CD7-3A6A-4BC6-864D-23319902CC30}" name="Precondition" dataDxfId="98"/>
-    <tableColumn id="6" xr3:uid="{3B781098-E0A9-48D9-B5BC-2FB2A26565E5}" name="Test Data" dataDxfId="97"/>
-    <tableColumn id="7" xr3:uid="{45BBE8D4-63E2-416F-ACC2-7CD2C1C91220}" name="Test Step" dataDxfId="96"/>
-    <tableColumn id="8" xr3:uid="{CA3B1689-8E28-4BD5-9C34-18D7D98C1AAC}" name="Post Condition" dataDxfId="95"/>
-    <tableColumn id="9" xr3:uid="{B4CDF521-EE6D-4DF0-872E-9D72AC1E8555}" name="Expected Result" dataDxfId="94"/>
-    <tableColumn id="10" xr3:uid="{E6AAEB15-C80D-4145-B1B3-C95E2ACCF6EF}" name="Actual Result" dataDxfId="93"/>
-    <tableColumn id="11" xr3:uid="{73F576F5-8370-4E97-BEBB-223ABB9B606A}" name="Status" dataDxfId="92"/>
+    <tableColumn id="1" xr3:uid="{6876B7D9-AED4-40A7-9B3F-EAAE7EC27F19}" name="Test Case ID" dataDxfId="105"/>
+    <tableColumn id="2" xr3:uid="{586F0A72-FB20-402D-B906-57CEC15B5844}" name="Test Scenario" dataDxfId="104"/>
+    <tableColumn id="3" xr3:uid="{FD20C9B8-3526-43CA-8EF7-13306F6F1E73}" name="Test Case Title" dataDxfId="103"/>
+    <tableColumn id="4" xr3:uid="{745A2EB8-ABE5-4979-B5E6-271B46F7EF61}" name="Test Description" dataDxfId="102"/>
+    <tableColumn id="5" xr3:uid="{32B27CD7-3A6A-4BC6-864D-23319902CC30}" name="Precondition" dataDxfId="101"/>
+    <tableColumn id="6" xr3:uid="{3B781098-E0A9-48D9-B5BC-2FB2A26565E5}" name="Test Data" dataDxfId="100"/>
+    <tableColumn id="7" xr3:uid="{45BBE8D4-63E2-416F-ACC2-7CD2C1C91220}" name="Test Step" dataDxfId="99"/>
+    <tableColumn id="8" xr3:uid="{CA3B1689-8E28-4BD5-9C34-18D7D98C1AAC}" name="Post Condition" dataDxfId="98"/>
+    <tableColumn id="9" xr3:uid="{B4CDF521-EE6D-4DF0-872E-9D72AC1E8555}" name="Expected Result" dataDxfId="97"/>
+    <tableColumn id="10" xr3:uid="{E6AAEB15-C80D-4145-B1B3-C95E2ACCF6EF}" name="Actual Result" dataDxfId="96"/>
+    <tableColumn id="11" xr3:uid="{73F576F5-8370-4E97-BEBB-223ABB9B606A}" name="Status" dataDxfId="95"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{C4579C64-BF71-4412-B0D5-57B184F01462}" name="Table6" displayName="Table6" ref="A1:K6" totalsRowShown="0" headerRowDxfId="91" dataDxfId="90">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{C4579C64-BF71-4412-B0D5-57B184F01462}" name="Table6" displayName="Table6" ref="A1:K6" totalsRowShown="0" headerRowDxfId="94" dataDxfId="93">
   <autoFilter ref="A1:K6" xr:uid="{C4579C64-BF71-4412-B0D5-57B184F01462}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{0CBAA722-80DA-4B08-85C0-C0643AD8A54D}" name="Test Case ID" dataDxfId="89"/>
-    <tableColumn id="2" xr3:uid="{1AE71C13-BF8A-46EB-8744-52C4492B1CA8}" name="Test Scenario" dataDxfId="88"/>
-    <tableColumn id="3" xr3:uid="{DEF6BFB4-FC3B-4290-BB73-914F5D0B138C}" name="Test Case Title" dataDxfId="87"/>
-    <tableColumn id="4" xr3:uid="{046A0014-010C-4B5D-BF73-3F6A7EA80901}" name="Test Description" dataDxfId="86"/>
-    <tableColumn id="5" xr3:uid="{B0659832-BE71-4176-9A59-0F58481951A5}" name="Precondition" dataDxfId="85"/>
-    <tableColumn id="6" xr3:uid="{86937CF6-785A-4BD5-9949-C42326EF2091}" name="Test Data" dataDxfId="84"/>
-    <tableColumn id="7" xr3:uid="{F4174DC9-407D-4FFC-8A52-D9003B91192F}" name="Test Step" dataDxfId="83"/>
-    <tableColumn id="8" xr3:uid="{8E2C6CB3-792C-458C-89B9-86623CAEAEFC}" name="Post Condition" dataDxfId="82"/>
-    <tableColumn id="9" xr3:uid="{15B93BDE-1870-4194-97A8-207E864C076F}" name="Expected Result" dataDxfId="81"/>
-    <tableColumn id="10" xr3:uid="{11F7E854-2EC6-4E5B-9967-97D2AF75D128}" name="Actual Result" dataDxfId="80"/>
-    <tableColumn id="11" xr3:uid="{8CF96C9E-249C-44E9-B980-052118023CDD}" name="Status" dataDxfId="79"/>
+    <tableColumn id="1" xr3:uid="{0CBAA722-80DA-4B08-85C0-C0643AD8A54D}" name="Test Case ID" dataDxfId="92"/>
+    <tableColumn id="2" xr3:uid="{1AE71C13-BF8A-46EB-8744-52C4492B1CA8}" name="Test Scenario" dataDxfId="91"/>
+    <tableColumn id="3" xr3:uid="{DEF6BFB4-FC3B-4290-BB73-914F5D0B138C}" name="Test Case Title" dataDxfId="90"/>
+    <tableColumn id="4" xr3:uid="{046A0014-010C-4B5D-BF73-3F6A7EA80901}" name="Test Description" dataDxfId="89"/>
+    <tableColumn id="5" xr3:uid="{B0659832-BE71-4176-9A59-0F58481951A5}" name="Precondition" dataDxfId="88"/>
+    <tableColumn id="6" xr3:uid="{86937CF6-785A-4BD5-9949-C42326EF2091}" name="Test Data" dataDxfId="87"/>
+    <tableColumn id="7" xr3:uid="{F4174DC9-407D-4FFC-8A52-D9003B91192F}" name="Test Step" dataDxfId="86"/>
+    <tableColumn id="8" xr3:uid="{8E2C6CB3-792C-458C-89B9-86623CAEAEFC}" name="Post Condition" dataDxfId="85"/>
+    <tableColumn id="9" xr3:uid="{15B93BDE-1870-4194-97A8-207E864C076F}" name="Expected Result" dataDxfId="84"/>
+    <tableColumn id="10" xr3:uid="{11F7E854-2EC6-4E5B-9967-97D2AF75D128}" name="Actual Result" dataDxfId="83"/>
+    <tableColumn id="11" xr3:uid="{8CF96C9E-249C-44E9-B980-052118023CDD}" name="Status" dataDxfId="82"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{C5E2AD33-062C-4FF3-97E2-14489F8737F1}" name="Table7" displayName="Table7" ref="A1:K6" totalsRowShown="0" headerRowDxfId="163" dataDxfId="162">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{C5E2AD33-062C-4FF3-97E2-14489F8737F1}" name="Table7" displayName="Table7" ref="A1:K6" totalsRowShown="0" headerRowDxfId="81" dataDxfId="80">
   <autoFilter ref="A1:K6" xr:uid="{C5E2AD33-062C-4FF3-97E2-14489F8737F1}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{CCBD9104-AFBA-47C3-8646-BBD44D55B38B}" name="Test Case ID" dataDxfId="161"/>
-    <tableColumn id="2" xr3:uid="{31C7960A-934A-41FB-B59F-E05141EDD80A}" name="Test Scenario" dataDxfId="160"/>
-    <tableColumn id="3" xr3:uid="{4AEC1D30-8657-40F5-832C-2953CD84B686}" name="Test Case Title" dataDxfId="159"/>
-    <tableColumn id="4" xr3:uid="{0FFF58E0-3C76-4C11-A76F-388626A5967B}" name="Test Description" dataDxfId="158"/>
-    <tableColumn id="5" xr3:uid="{9407EA85-7D2E-4347-B374-302A957DB7C6}" name="Precondition" dataDxfId="157"/>
-    <tableColumn id="6" xr3:uid="{21F6E5C5-88ED-423D-A4A8-0A4611713610}" name="Test Data" dataDxfId="156"/>
-    <tableColumn id="7" xr3:uid="{9F5F42E4-CFB2-4DA8-8C26-83A88E35D7BF}" name="Test Step" dataDxfId="155"/>
-    <tableColumn id="8" xr3:uid="{94D4F544-5CE4-4724-BB7C-0D5E7E5BA04A}" name="Post Condition" dataDxfId="154"/>
-    <tableColumn id="9" xr3:uid="{EC00A77A-F3B3-4584-88AE-EC522129EB55}" name="Expected Result" dataDxfId="153"/>
-    <tableColumn id="10" xr3:uid="{5B0A3255-9926-4CF2-BF04-AA0AB69B800C}" name="Actual Result" dataDxfId="152"/>
-    <tableColumn id="11" xr3:uid="{FAEC2F86-5C61-44B3-9E1A-0EE2E542A7B9}" name="Status" dataDxfId="151"/>
+    <tableColumn id="1" xr3:uid="{CCBD9104-AFBA-47C3-8646-BBD44D55B38B}" name="Test Case ID" dataDxfId="79"/>
+    <tableColumn id="2" xr3:uid="{31C7960A-934A-41FB-B59F-E05141EDD80A}" name="Test Scenario" dataDxfId="78"/>
+    <tableColumn id="3" xr3:uid="{4AEC1D30-8657-40F5-832C-2953CD84B686}" name="Test Case Title" dataDxfId="77"/>
+    <tableColumn id="4" xr3:uid="{0FFF58E0-3C76-4C11-A76F-388626A5967B}" name="Test Description" dataDxfId="76"/>
+    <tableColumn id="5" xr3:uid="{9407EA85-7D2E-4347-B374-302A957DB7C6}" name="Precondition" dataDxfId="75"/>
+    <tableColumn id="6" xr3:uid="{21F6E5C5-88ED-423D-A4A8-0A4611713610}" name="Test Data" dataDxfId="74"/>
+    <tableColumn id="7" xr3:uid="{9F5F42E4-CFB2-4DA8-8C26-83A88E35D7BF}" name="Test Step" dataDxfId="73"/>
+    <tableColumn id="8" xr3:uid="{94D4F544-5CE4-4724-BB7C-0D5E7E5BA04A}" name="Post Condition" dataDxfId="72"/>
+    <tableColumn id="9" xr3:uid="{EC00A77A-F3B3-4584-88AE-EC522129EB55}" name="Expected Result" dataDxfId="71"/>
+    <tableColumn id="10" xr3:uid="{5B0A3255-9926-4CF2-BF04-AA0AB69B800C}" name="Actual Result" dataDxfId="70"/>
+    <tableColumn id="11" xr3:uid="{FAEC2F86-5C61-44B3-9E1A-0EE2E542A7B9}" name="Status" dataDxfId="69"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{76C7F6F1-DEA0-45ED-9527-F69EBF725CC3}" name="Table8" displayName="Table8" ref="A1:K8" totalsRowShown="0" dataDxfId="78">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{76C7F6F1-DEA0-45ED-9527-F69EBF725CC3}" name="Table8" displayName="Table8" ref="A1:K8" totalsRowShown="0" dataDxfId="68">
   <autoFilter ref="A1:K8" xr:uid="{76C7F6F1-DEA0-45ED-9527-F69EBF725CC3}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{78F7358B-BBF5-4E44-95AB-658611EC578F}" name="Test Case ID" dataDxfId="77"/>
-    <tableColumn id="2" xr3:uid="{4C2135E9-2DC4-4097-B4BC-F2C75DD17DC5}" name="Test Scenario" dataDxfId="76"/>
-    <tableColumn id="3" xr3:uid="{6D5B481E-4B3E-4AB4-B904-FBB02F64973F}" name="Test Case Title" dataDxfId="75"/>
-    <tableColumn id="4" xr3:uid="{C798261B-A80F-41B4-B2FF-A03FB57028CA}" name="Test Description" dataDxfId="74"/>
-    <tableColumn id="5" xr3:uid="{B2C9C8E7-63BF-4BD3-AB7C-0B94F88557DC}" name="Precondition" dataDxfId="73"/>
-    <tableColumn id="6" xr3:uid="{3DCB78A0-24D7-4E9E-A397-A7ED87EDB0DC}" name="Test Data" dataDxfId="72"/>
-    <tableColumn id="7" xr3:uid="{7C1F9FC6-BFAA-4E1F-A192-B44375AC929B}" name="Test Step" dataDxfId="71"/>
-    <tableColumn id="8" xr3:uid="{EEE8B405-347E-49F5-B1D8-F91861C4FC16}" name="Post Condition" dataDxfId="70"/>
-    <tableColumn id="9" xr3:uid="{10C2E695-D46A-4680-BE17-45F9AE21F104}" name="Expected Result" dataDxfId="69"/>
-    <tableColumn id="10" xr3:uid="{C6D62D5E-0EAB-47C0-9C55-C96F9AF6647F}" name="Actual Result" dataDxfId="68"/>
-    <tableColumn id="11" xr3:uid="{789CA9A0-3FA3-467F-8F87-FC85389D8700}" name="Status" dataDxfId="67"/>
+    <tableColumn id="1" xr3:uid="{78F7358B-BBF5-4E44-95AB-658611EC578F}" name="Test Case ID" dataDxfId="67"/>
+    <tableColumn id="2" xr3:uid="{4C2135E9-2DC4-4097-B4BC-F2C75DD17DC5}" name="Test Scenario" dataDxfId="66"/>
+    <tableColumn id="3" xr3:uid="{6D5B481E-4B3E-4AB4-B904-FBB02F64973F}" name="Test Case Title" dataDxfId="65"/>
+    <tableColumn id="4" xr3:uid="{C798261B-A80F-41B4-B2FF-A03FB57028CA}" name="Test Description" dataDxfId="64"/>
+    <tableColumn id="5" xr3:uid="{B2C9C8E7-63BF-4BD3-AB7C-0B94F88557DC}" name="Precondition" dataDxfId="63"/>
+    <tableColumn id="6" xr3:uid="{3DCB78A0-24D7-4E9E-A397-A7ED87EDB0DC}" name="Test Data" dataDxfId="62"/>
+    <tableColumn id="7" xr3:uid="{7C1F9FC6-BFAA-4E1F-A192-B44375AC929B}" name="Test Step" dataDxfId="61"/>
+    <tableColumn id="8" xr3:uid="{EEE8B405-347E-49F5-B1D8-F91861C4FC16}" name="Post Condition" dataDxfId="60"/>
+    <tableColumn id="9" xr3:uid="{10C2E695-D46A-4680-BE17-45F9AE21F104}" name="Expected Result" dataDxfId="59"/>
+    <tableColumn id="10" xr3:uid="{C6D62D5E-0EAB-47C0-9C55-C96F9AF6647F}" name="Actual Result" dataDxfId="58"/>
+    <tableColumn id="11" xr3:uid="{789CA9A0-3FA3-467F-8F87-FC85389D8700}" name="Status" dataDxfId="57"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{977FBCCA-BB0D-471A-B840-B1BF610C9A7E}" name="Table9" displayName="Table9" ref="A1:K6" totalsRowShown="0" headerRowDxfId="66" dataDxfId="65">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{977FBCCA-BB0D-471A-B840-B1BF610C9A7E}" name="Table9" displayName="Table9" ref="A1:K6" totalsRowShown="0" headerRowDxfId="56" dataDxfId="55">
   <autoFilter ref="A1:K6" xr:uid="{977FBCCA-BB0D-471A-B840-B1BF610C9A7E}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{E14DB9FF-88A1-4EE7-B230-D8894A0E1AFB}" name="Test Case ID" dataDxfId="64"/>
-    <tableColumn id="2" xr3:uid="{D4FC117F-56A6-412F-984A-D6DBFC8F6B01}" name="Test Scenario" dataDxfId="63"/>
-    <tableColumn id="3" xr3:uid="{E5DE9E41-179E-45D8-A348-BD490AC75E5D}" name="Test Case Title" dataDxfId="62"/>
-    <tableColumn id="4" xr3:uid="{89C1E1C2-62E8-4407-A716-9188B6576B51}" name="Test Description" dataDxfId="61"/>
-    <tableColumn id="5" xr3:uid="{9FC31264-0A03-44DC-BB14-CE8594D16932}" name="Precondition" dataDxfId="60"/>
-    <tableColumn id="6" xr3:uid="{52040CDD-D184-449A-AA2D-20B3EB5BD5EF}" name="Test Data" dataDxfId="59"/>
-    <tableColumn id="7" xr3:uid="{057CB6AB-A65B-40E5-BF01-A6F370B4BCA2}" name="Test Step" dataDxfId="58"/>
-    <tableColumn id="8" xr3:uid="{0CADDAEE-24CB-4B0B-BD9A-A1895CB19AC7}" name="Post Condition" dataDxfId="57"/>
-    <tableColumn id="9" xr3:uid="{33917D9D-4F6F-4611-9B5E-C61943DC50AE}" name="Expected Result" dataDxfId="56"/>
-    <tableColumn id="10" xr3:uid="{FEFFF501-E422-47CC-ACA8-7793EF2B2B40}" name="Actual Result" dataDxfId="55"/>
-    <tableColumn id="11" xr3:uid="{BAD0A7C4-8AC6-4E11-87E7-837E3A37BD85}" name="Status" dataDxfId="54"/>
+    <tableColumn id="1" xr3:uid="{E14DB9FF-88A1-4EE7-B230-D8894A0E1AFB}" name="Test Case ID" dataDxfId="54"/>
+    <tableColumn id="2" xr3:uid="{D4FC117F-56A6-412F-984A-D6DBFC8F6B01}" name="Test Scenario" dataDxfId="53"/>
+    <tableColumn id="3" xr3:uid="{E5DE9E41-179E-45D8-A348-BD490AC75E5D}" name="Test Case Title" dataDxfId="52"/>
+    <tableColumn id="4" xr3:uid="{89C1E1C2-62E8-4407-A716-9188B6576B51}" name="Test Description" dataDxfId="51"/>
+    <tableColumn id="5" xr3:uid="{9FC31264-0A03-44DC-BB14-CE8594D16932}" name="Precondition" dataDxfId="50"/>
+    <tableColumn id="6" xr3:uid="{52040CDD-D184-449A-AA2D-20B3EB5BD5EF}" name="Test Data" dataDxfId="49"/>
+    <tableColumn id="7" xr3:uid="{057CB6AB-A65B-40E5-BF01-A6F370B4BCA2}" name="Test Step" dataDxfId="48"/>
+    <tableColumn id="8" xr3:uid="{0CADDAEE-24CB-4B0B-BD9A-A1895CB19AC7}" name="Post Condition" dataDxfId="47"/>
+    <tableColumn id="9" xr3:uid="{33917D9D-4F6F-4611-9B5E-C61943DC50AE}" name="Expected Result" dataDxfId="46"/>
+    <tableColumn id="10" xr3:uid="{FEFFF501-E422-47CC-ACA8-7793EF2B2B40}" name="Actual Result" dataDxfId="45"/>
+    <tableColumn id="11" xr3:uid="{BAD0A7C4-8AC6-4E11-87E7-837E3A37BD85}" name="Status" dataDxfId="44"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3660,41 +3660,41 @@
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="15" t="s">
+      <c r="B1" s="24" t="s">
         <v>364</v>
       </c>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
+      <c r="C1" s="24"/>
+      <c r="D1" s="24"/>
     </row>
     <row r="2" spans="1:4" ht="18" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A2" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="15" t="s">
+      <c r="B2" s="24" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="15"/>
-      <c r="D2" s="15"/>
+      <c r="C2" s="24"/>
+      <c r="D2" s="24"/>
     </row>
     <row r="3" spans="1:4" ht="18" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A3" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="15" t="s">
+      <c r="B3" s="24" t="s">
         <v>365</v>
       </c>
-      <c r="C3" s="15"/>
-      <c r="D3" s="15"/>
+      <c r="C3" s="24"/>
+      <c r="D3" s="24"/>
     </row>
     <row r="4" spans="1:4" ht="18" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A4" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="16">
+      <c r="B4" s="25">
         <v>46163</v>
       </c>
-      <c r="C4" s="15"/>
-      <c r="D4" s="15"/>
+      <c r="C4" s="24"/>
+      <c r="D4" s="24"/>
     </row>
     <row r="5" spans="1:4" ht="18" customHeight="1" thickTop="1" x14ac:dyDescent="0.45">
       <c r="A5" s="2"/>
@@ -4443,263 +4443,263 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="25.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="21" t="s">
         <v>386</v>
       </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-      <c r="F1" s="18"/>
-      <c r="G1" s="18"/>
-      <c r="H1" s="18"/>
-      <c r="I1" s="18"/>
-      <c r="J1" s="18"/>
-      <c r="K1" s="18"/>
-      <c r="L1" s="18"/>
-      <c r="M1" s="18"/>
-      <c r="N1" s="18"/>
-      <c r="O1" s="18"/>
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="21"/>
+      <c r="F1" s="21"/>
+      <c r="G1" s="21"/>
+      <c r="H1" s="21"/>
+      <c r="I1" s="21"/>
+      <c r="J1" s="21"/>
+      <c r="K1" s="21"/>
+      <c r="L1" s="21"/>
+      <c r="M1" s="21"/>
+      <c r="N1" s="21"/>
+      <c r="O1" s="21"/>
     </row>
     <row r="2" spans="1:15" ht="14.65" thickBot="1" x14ac:dyDescent="0.5"/>
     <row r="3" spans="1:15" ht="21.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A3" s="21" t="s">
+      <c r="A3" s="26" t="s">
         <v>382</v>
       </c>
-      <c r="B3" s="21"/>
-      <c r="C3" s="21"/>
-      <c r="D3" s="21"/>
-      <c r="E3" s="21"/>
-      <c r="F3" s="21"/>
-      <c r="G3" s="21"/>
+      <c r="B3" s="26"/>
+      <c r="C3" s="26"/>
+      <c r="D3" s="26"/>
+      <c r="E3" s="26"/>
+      <c r="F3" s="26"/>
+      <c r="G3" s="26"/>
     </row>
     <row r="4" spans="1:15" ht="18" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A4" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="15" t="s">
+      <c r="B4" s="24" t="s">
         <v>336</v>
       </c>
-      <c r="C4" s="15"/>
-      <c r="D4" s="15"/>
-      <c r="E4" s="15"/>
-      <c r="F4" s="15"/>
-      <c r="G4" s="15"/>
+      <c r="C4" s="24"/>
+      <c r="D4" s="24"/>
+      <c r="E4" s="24"/>
+      <c r="F4" s="24"/>
+      <c r="G4" s="24"/>
     </row>
     <row r="5" spans="1:15" ht="18" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A5" s="4" t="s">
         <v>337</v>
       </c>
-      <c r="B5" s="15" t="s">
+      <c r="B5" s="24" t="s">
         <v>338</v>
       </c>
-      <c r="C5" s="15"/>
-      <c r="D5" s="15"/>
-      <c r="E5" s="15"/>
-      <c r="F5" s="15"/>
-      <c r="G5" s="15"/>
+      <c r="C5" s="24"/>
+      <c r="D5" s="24"/>
+      <c r="E5" s="24"/>
+      <c r="F5" s="24"/>
+      <c r="G5" s="24"/>
     </row>
     <row r="6" spans="1:15" ht="18" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A6" s="4" t="s">
         <v>339</v>
       </c>
-      <c r="B6" s="15" t="s">
+      <c r="B6" s="24" t="s">
         <v>340</v>
       </c>
-      <c r="C6" s="15"/>
-      <c r="D6" s="15"/>
-      <c r="E6" s="15"/>
-      <c r="F6" s="15"/>
-      <c r="G6" s="15"/>
+      <c r="C6" s="24"/>
+      <c r="D6" s="24"/>
+      <c r="E6" s="24"/>
+      <c r="F6" s="24"/>
+      <c r="G6" s="24"/>
     </row>
     <row r="7" spans="1:15" ht="18" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A7" s="4" t="s">
         <v>464</v>
       </c>
-      <c r="B7" s="15" t="s">
+      <c r="B7" s="24" t="s">
         <v>463</v>
       </c>
-      <c r="C7" s="15"/>
-      <c r="D7" s="15"/>
-      <c r="E7" s="15"/>
-      <c r="F7" s="15"/>
-      <c r="G7" s="15"/>
+      <c r="C7" s="24"/>
+      <c r="D7" s="24"/>
+      <c r="E7" s="24"/>
+      <c r="F7" s="24"/>
+      <c r="G7" s="24"/>
     </row>
     <row r="8" spans="1:15" ht="18" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A8" s="4" t="s">
         <v>341</v>
       </c>
-      <c r="B8" s="15" t="s">
+      <c r="B8" s="24" t="s">
         <v>365</v>
       </c>
-      <c r="C8" s="15"/>
-      <c r="D8" s="15"/>
-      <c r="E8" s="15"/>
-      <c r="F8" s="15"/>
-      <c r="G8" s="15"/>
+      <c r="C8" s="24"/>
+      <c r="D8" s="24"/>
+      <c r="E8" s="24"/>
+      <c r="F8" s="24"/>
+      <c r="G8" s="24"/>
     </row>
     <row r="9" spans="1:15" ht="18" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A9" s="4" t="s">
         <v>465</v>
       </c>
-      <c r="B9" s="16">
+      <c r="B9" s="25">
         <v>46163</v>
       </c>
-      <c r="C9" s="15"/>
-      <c r="D9" s="15"/>
-      <c r="E9" s="15"/>
-      <c r="F9" s="15"/>
-      <c r="G9" s="15"/>
+      <c r="C9" s="24"/>
+      <c r="D9" s="24"/>
+      <c r="E9" s="24"/>
+      <c r="F9" s="24"/>
+      <c r="G9" s="24"/>
     </row>
     <row r="10" spans="1:15" ht="18" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A10" s="4" t="s">
         <v>466</v>
       </c>
-      <c r="B10" s="16">
-        <v>46166</v>
-      </c>
-      <c r="C10" s="15"/>
-      <c r="D10" s="15"/>
-      <c r="E10" s="15"/>
-      <c r="F10" s="15"/>
-      <c r="G10" s="15"/>
+      <c r="B10" s="25">
+        <v>46170</v>
+      </c>
+      <c r="C10" s="24"/>
+      <c r="D10" s="24"/>
+      <c r="E10" s="24"/>
+      <c r="F10" s="24"/>
+      <c r="G10" s="24"/>
     </row>
     <row r="11" spans="1:15" ht="18" customHeight="1" thickTop="1" x14ac:dyDescent="0.45"/>
     <row r="12" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="A12" s="19" t="s">
+      <c r="A12" s="22" t="s">
         <v>383</v>
       </c>
-      <c r="B12" s="19"/>
-      <c r="C12" s="19"/>
-      <c r="E12" s="17" t="s">
+      <c r="B12" s="22"/>
+      <c r="C12" s="22"/>
+      <c r="E12" s="20" t="s">
         <v>385</v>
       </c>
-      <c r="F12" s="17"/>
-      <c r="G12" s="17"/>
+      <c r="F12" s="20"/>
+      <c r="G12" s="20"/>
     </row>
     <row r="13" spans="1:15" ht="21.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A13" s="11" t="s">
         <v>342</v>
       </c>
-      <c r="B13" s="22">
+      <c r="B13" s="15">
         <v>56</v>
       </c>
-      <c r="C13" s="22"/>
+      <c r="C13" s="15"/>
       <c r="E13" s="11" t="s">
         <v>343</v>
       </c>
-      <c r="F13" s="22">
+      <c r="F13" s="15">
         <v>5</v>
       </c>
-      <c r="G13" s="22"/>
+      <c r="G13" s="15"/>
     </row>
     <row r="14" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A14" s="11" t="s">
         <v>344</v>
       </c>
-      <c r="B14" s="22">
+      <c r="B14" s="15">
         <v>50</v>
       </c>
-      <c r="C14" s="22"/>
+      <c r="C14" s="15"/>
       <c r="E14" s="11" t="s">
         <v>345</v>
       </c>
-      <c r="F14" s="24">
+      <c r="F14" s="17">
         <v>0</v>
       </c>
-      <c r="G14" s="24"/>
+      <c r="G14" s="17"/>
     </row>
     <row r="15" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A15" s="11" t="s">
         <v>346</v>
       </c>
-      <c r="B15" s="23">
+      <c r="B15" s="19">
         <v>49</v>
       </c>
-      <c r="C15" s="23"/>
+      <c r="C15" s="19"/>
       <c r="E15" s="11" t="s">
         <v>330</v>
       </c>
-      <c r="F15" s="24">
+      <c r="F15" s="17">
         <v>1</v>
       </c>
-      <c r="G15" s="24"/>
+      <c r="G15" s="17"/>
     </row>
     <row r="16" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A16" s="11" t="s">
         <v>347</v>
       </c>
-      <c r="B16" s="24">
+      <c r="B16" s="17">
         <v>1</v>
       </c>
-      <c r="C16" s="24"/>
+      <c r="C16" s="17"/>
       <c r="E16" s="11" t="s">
         <v>348</v>
       </c>
-      <c r="F16" s="26">
+      <c r="F16" s="18">
         <v>2</v>
       </c>
-      <c r="G16" s="26"/>
+      <c r="G16" s="18"/>
     </row>
     <row r="17" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A17" s="11" t="s">
         <v>349</v>
       </c>
-      <c r="B17" s="22">
+      <c r="B17" s="15">
         <v>0</v>
       </c>
-      <c r="C17" s="22"/>
+      <c r="C17" s="15"/>
       <c r="E17" s="11" t="s">
         <v>350</v>
       </c>
-      <c r="F17" s="23">
+      <c r="F17" s="19">
         <v>2</v>
       </c>
-      <c r="G17" s="23"/>
+      <c r="G17" s="19"/>
     </row>
     <row r="18" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A18" s="11" t="s">
         <v>351</v>
       </c>
-      <c r="B18" s="22">
+      <c r="B18" s="15">
         <v>0</v>
       </c>
-      <c r="C18" s="22"/>
+      <c r="C18" s="15"/>
       <c r="E18" s="11" t="s">
         <v>331</v>
       </c>
-      <c r="F18" s="22">
+      <c r="F18" s="15">
         <v>5</v>
       </c>
-      <c r="G18" s="22"/>
+      <c r="G18" s="15"/>
     </row>
     <row r="19" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A19" s="11" t="s">
         <v>352</v>
       </c>
-      <c r="B19" s="25">
+      <c r="B19" s="16">
         <v>0.98</v>
       </c>
-      <c r="C19" s="25"/>
+      <c r="C19" s="16"/>
       <c r="E19" s="11" t="s">
         <v>353</v>
       </c>
-      <c r="F19" s="22">
+      <c r="F19" s="15">
         <v>0</v>
       </c>
-      <c r="G19" s="22"/>
+      <c r="G19" s="15"/>
     </row>
     <row r="20" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.45"/>
     <row r="21" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A21" s="20" t="s">
+      <c r="A21" s="23" t="s">
         <v>384</v>
       </c>
-      <c r="B21" s="20"/>
-      <c r="C21" s="20"/>
-      <c r="D21" s="20"/>
-      <c r="E21" s="20"/>
-      <c r="F21" s="20"/>
-      <c r="G21" s="20"/>
+      <c r="B21" s="23"/>
+      <c r="C21" s="23"/>
+      <c r="D21" s="23"/>
+      <c r="E21" s="23"/>
+      <c r="F21" s="23"/>
+      <c r="G21" s="23"/>
     </row>
     <row r="22" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A22" s="5" t="s">
@@ -4935,16 +4935,6 @@
     <row r="33" ht="18" customHeight="1" x14ac:dyDescent="0.45"/>
   </sheetData>
   <mergeCells count="26">
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="F14:G14"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="F16:G16"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="F18:G18"/>
-    <mergeCell ref="F19:G19"/>
     <mergeCell ref="E12:G12"/>
     <mergeCell ref="A1:O1"/>
     <mergeCell ref="A12:C12"/>
@@ -4961,6 +4951,16 @@
     <mergeCell ref="B14:C14"/>
     <mergeCell ref="B15:C15"/>
     <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="F14:G14"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="F16:G16"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F18:G18"/>
+    <mergeCell ref="F19:G19"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
